--- a/research/traditional_assets/database/data/vietnam/vietnam_healthcare_products.xlsx
+++ b/research/traditional_assets/database/data/vietnam/vietnam_healthcare_products.xlsx
@@ -8,6 +8,8 @@
   </bookViews>
   <sheets>
     <sheet name="earnings_debt" sheetId="1" r:id="rId1"/>
+    <sheet name="cost_capital" sheetId="2" r:id="rId2"/>
+    <sheet name="hnx_amv" sheetId="3" r:id="rId3"/>
   </sheets>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -587,35 +589,32 @@
           <t>Healthcare Products</t>
         </is>
       </c>
-      <c r="D2">
-        <v>0.148</v>
-      </c>
       <c r="G2">
-        <v>0.3723618090452261</v>
+        <v>0.4113557358053302</v>
       </c>
       <c r="H2">
-        <v>0.3723618090452261</v>
+        <v>0.4113557358053302</v>
       </c>
       <c r="I2">
-        <v>-0.00170854271356784</v>
+        <v>0.1564310544611819</v>
       </c>
       <c r="J2">
-        <v>-0.00170854271356784</v>
+        <v>0.1491242960787063</v>
       </c>
       <c r="K2">
-        <v>-1.07</v>
+        <v>0.488</v>
       </c>
       <c r="L2">
-        <v>-0.05376884422110553</v>
+        <v>0.05654692931633835</v>
       </c>
       <c r="M2">
-        <v>0</v>
+        <v>0.008999999999999999</v>
       </c>
       <c r="N2">
-        <v>0</v>
+        <v>0.0004285714285714285</v>
       </c>
       <c r="O2">
-        <v>-0</v>
+        <v>0.01844262295081967</v>
       </c>
       <c r="P2">
         <v>0</v>
@@ -624,64 +623,67 @@
         <v>0</v>
       </c>
       <c r="R2">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="S2">
-        <v>0</v>
+        <v>0.008999999999999999</v>
+      </c>
+      <c r="T2">
+        <v>1</v>
       </c>
       <c r="U2">
-        <v>0.339</v>
+        <v>3.37</v>
       </c>
       <c r="V2">
-        <v>0.1181184668989547</v>
+        <v>0.1604761904761905</v>
       </c>
       <c r="X2">
-        <v>0.4564406836198319</v>
+        <v>0.1568843220769024</v>
       </c>
       <c r="AB2">
-        <v>0.1667605936486909</v>
+        <v>0.1347292372621295</v>
       </c>
       <c r="AD2">
-        <v>8.91</v>
+        <v>6.86</v>
       </c>
       <c r="AE2">
         <v>0</v>
       </c>
       <c r="AF2">
-        <v>8.91</v>
+        <v>6.86</v>
       </c>
       <c r="AG2">
-        <v>8.571</v>
+        <v>3.49</v>
       </c>
       <c r="AH2">
-        <v>0.7563667232597623</v>
+        <v>0.2462311557788945</v>
       </c>
       <c r="AI2">
-        <v>0.6832822085889572</v>
+        <v>0.08983761131482453</v>
       </c>
       <c r="AJ2">
-        <v>0.7491478017655799</v>
+        <v>0.1425071457737852</v>
       </c>
       <c r="AK2">
-        <v>0.6748287536414455</v>
+        <v>0.04781476914645842</v>
       </c>
       <c r="AL2">
-        <v>0.991</v>
+        <v>0.973</v>
       </c>
       <c r="AM2">
-        <v>0.916</v>
+        <v>0.9119999999999999</v>
       </c>
       <c r="AN2">
-        <v>2.25</v>
+        <v>3.076233183856502</v>
       </c>
       <c r="AO2">
-        <v>-0.0343087790110999</v>
+        <v>1.387461459403906</v>
       </c>
       <c r="AP2">
-        <v>2.16439393939394</v>
+        <v>1.565022421524664</v>
       </c>
       <c r="AQ2">
-        <v>-0.03711790393013101</v>
+        <v>1.480263157894737</v>
       </c>
     </row>
     <row r="3">
@@ -692,7 +694,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>DANAMECO Medical Joint Stock Corporation (HNX:DNM)</t>
+          <t>American Vietnamese Biotech Incorporation (HNX:AMV)</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -700,35 +702,32 @@
           <t>Healthcare Products</t>
         </is>
       </c>
-      <c r="D3">
-        <v>0.148</v>
-      </c>
       <c r="G3">
-        <v>0.3723618090452261</v>
+        <v>0.4113557358053302</v>
       </c>
       <c r="H3">
-        <v>0.3723618090452261</v>
+        <v>0.4113557358053302</v>
       </c>
       <c r="I3">
-        <v>-0.00170854271356784</v>
+        <v>0.1564310544611819</v>
       </c>
       <c r="J3">
-        <v>-0.00170854271356784</v>
+        <v>0.1491242960787063</v>
       </c>
       <c r="K3">
-        <v>-1.07</v>
+        <v>0.488</v>
       </c>
       <c r="L3">
-        <v>-0.05376884422110553</v>
+        <v>0.05654692931633835</v>
       </c>
       <c r="M3">
-        <v>-0</v>
+        <v>0.008999999999999999</v>
       </c>
       <c r="N3">
-        <v>-0</v>
+        <v>0.0004285714285714285</v>
       </c>
       <c r="O3">
-        <v>0</v>
+        <v>0.01844262295081967</v>
       </c>
       <c r="P3">
         <v>-0</v>
@@ -737,64 +736,8839 @@
         <v>-0</v>
       </c>
       <c r="R3">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="S3">
-        <v>0</v>
+        <v>0.008999999999999999</v>
+      </c>
+      <c r="T3">
+        <v>1</v>
       </c>
       <c r="U3">
-        <v>0.339</v>
+        <v>3.37</v>
       </c>
       <c r="V3">
-        <v>0.1181184668989547</v>
+        <v>0.1604761904761905</v>
       </c>
       <c r="X3">
-        <v>0.4564406836198319</v>
+        <v>0.1568843220769024</v>
       </c>
       <c r="AB3">
-        <v>0.1667605936486909</v>
+        <v>0.1347292372621295</v>
       </c>
       <c r="AD3">
-        <v>8.91</v>
+        <v>6.86</v>
       </c>
       <c r="AE3">
         <v>0</v>
       </c>
       <c r="AF3">
-        <v>8.91</v>
+        <v>6.86</v>
       </c>
       <c r="AG3">
-        <v>8.571</v>
+        <v>3.49</v>
       </c>
       <c r="AH3">
-        <v>0.7563667232597623</v>
+        <v>0.2462311557788945</v>
       </c>
       <c r="AI3">
-        <v>0.6832822085889572</v>
+        <v>0.08983761131482453</v>
       </c>
       <c r="AJ3">
-        <v>0.7491478017655799</v>
+        <v>0.1425071457737852</v>
       </c>
       <c r="AK3">
-        <v>0.6748287536414455</v>
+        <v>0.04781476914645842</v>
       </c>
       <c r="AL3">
-        <v>0.991</v>
+        <v>0.973</v>
       </c>
       <c r="AM3">
-        <v>0.916</v>
+        <v>0.9119999999999999</v>
       </c>
       <c r="AN3">
-        <v>2.25</v>
+        <v>3.076233183856502</v>
       </c>
       <c r="AO3">
-        <v>-0.0343087790110999</v>
+        <v>1.387461459403906</v>
       </c>
       <c r="AP3">
-        <v>2.16439393939394</v>
+        <v>1.565022421524664</v>
       </c>
       <c r="AQ3">
-        <v>-0.03711790393013101</v>
+        <v>1.480263157894737</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:AY2"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1" s="1" customFormat="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>company_name</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>exchange_ticker</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>industry_group</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>country</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>current_interest_coverage</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>optimal_interest_coverage</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>current_debt_ebitda</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>optimal_debt_ebitda</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>current_debt_capital</t>
+        </is>
+      </c>
+      <c r="J1" s="1" t="inlineStr">
+        <is>
+          <t>optimal_debt_capital</t>
+        </is>
+      </c>
+      <c r="K1" s="1" t="inlineStr">
+        <is>
+          <t>current_equity_value</t>
+        </is>
+      </c>
+      <c r="L1" s="1" t="inlineStr">
+        <is>
+          <t>optimal_equity_value</t>
+        </is>
+      </c>
+      <c r="M1" s="1" t="inlineStr">
+        <is>
+          <t>current_enterprise_value</t>
+        </is>
+      </c>
+      <c r="N1" s="1" t="inlineStr">
+        <is>
+          <t>optimal_enterprise_value</t>
+        </is>
+      </c>
+      <c r="O1" s="1" t="inlineStr">
+        <is>
+          <t>current_debt</t>
+        </is>
+      </c>
+      <c r="P1" s="1" t="inlineStr">
+        <is>
+          <t>optimal_debt</t>
+        </is>
+      </c>
+      <c r="Q1" s="1" t="inlineStr">
+        <is>
+          <t>current_cost_capital</t>
+        </is>
+      </c>
+      <c r="R1" s="1" t="inlineStr">
+        <is>
+          <t>optimal_cost_capital</t>
+        </is>
+      </c>
+      <c r="S1" s="1" t="inlineStr">
+        <is>
+          <t>current_cost_debt_after_tax</t>
+        </is>
+      </c>
+      <c r="T1" s="1" t="inlineStr">
+        <is>
+          <t>optimal_cost_debt_after_tax</t>
+        </is>
+      </c>
+      <c r="U1" s="1" t="inlineStr">
+        <is>
+          <t>current_debt_rating</t>
+        </is>
+      </c>
+      <c r="V1" s="1" t="inlineStr">
+        <is>
+          <t>optimal_debt_rating</t>
+        </is>
+      </c>
+      <c r="W1" s="1" t="inlineStr">
+        <is>
+          <t>current_cost_equity</t>
+        </is>
+      </c>
+      <c r="X1" s="1" t="inlineStr">
+        <is>
+          <t>optimal_cost_equity</t>
+        </is>
+      </c>
+      <c r="Y1" s="1" t="inlineStr">
+        <is>
+          <t>current_beta</t>
+        </is>
+      </c>
+      <c r="Z1" s="1" t="inlineStr">
+        <is>
+          <t>optimal_beta</t>
+        </is>
+      </c>
+      <c r="AA1" s="1" t="inlineStr">
+        <is>
+          <t>estimated_mv_debt</t>
+        </is>
+      </c>
+      <c r="AB1" s="1" t="inlineStr">
+        <is>
+          <t>estimated_cost_debt_pre_tax</t>
+        </is>
+      </c>
+      <c r="AC1" s="1" t="inlineStr">
+        <is>
+          <t>estimated_coverage_ratio</t>
+        </is>
+      </c>
+      <c r="AD1" s="1" t="inlineStr">
+        <is>
+          <t>adjusted_debt</t>
+        </is>
+      </c>
+      <c r="AE1" s="1" t="inlineStr">
+        <is>
+          <t>adjusted_interest_expense</t>
+        </is>
+      </c>
+      <c r="AF1" s="1" t="inlineStr">
+        <is>
+          <t>adjusted_depreciation</t>
+        </is>
+      </c>
+      <c r="AG1" s="1" t="inlineStr">
+        <is>
+          <t>adjusted_ebitda</t>
+        </is>
+      </c>
+      <c r="AH1" s="1" t="inlineStr">
+        <is>
+          <t>country_default_spread</t>
+        </is>
+      </c>
+      <c r="AI1" s="1" t="inlineStr">
+        <is>
+          <t>risk_free</t>
+        </is>
+      </c>
+      <c r="AJ1" s="1" t="inlineStr">
+        <is>
+          <t>market_capitalization</t>
+        </is>
+      </c>
+      <c r="AK1" s="1" t="inlineStr">
+        <is>
+          <t>estimated_risk_premium</t>
+        </is>
+      </c>
+      <c r="AL1" s="1" t="inlineStr">
+        <is>
+          <t>reported_debt_rating</t>
+        </is>
+      </c>
+      <c r="AM1" s="1" t="inlineStr">
+        <is>
+          <t>marginal_tax_rate</t>
+        </is>
+      </c>
+      <c r="AN1" s="1" t="inlineStr">
+        <is>
+          <t>deductions_max_percentage</t>
+        </is>
+      </c>
+      <c r="AO1" s="1" t="inlineStr">
+        <is>
+          <t>deductions_method</t>
+        </is>
+      </c>
+      <c r="AP1" s="1" t="inlineStr">
+        <is>
+          <t>estimated_drop_ebitda</t>
+        </is>
+      </c>
+      <c r="AQ1" s="1" t="inlineStr">
+        <is>
+          <t>reported_capital_spending</t>
+        </is>
+      </c>
+      <c r="AR1" s="1" t="inlineStr">
+        <is>
+          <t>reported_interest_expense</t>
+        </is>
+      </c>
+      <c r="AS1" s="1" t="inlineStr">
+        <is>
+          <t>reported_bv_debt</t>
+        </is>
+      </c>
+      <c r="AT1" s="1" t="inlineStr">
+        <is>
+          <t>reported_cash</t>
+        </is>
+      </c>
+      <c r="AU1" s="1" t="inlineStr">
+        <is>
+          <t>estimated_ev_implied_growth</t>
+        </is>
+      </c>
+      <c r="AV1" s="1" t="inlineStr">
+        <is>
+          <t>flag_bankruptcy</t>
+        </is>
+      </c>
+      <c r="AW1" s="1" t="inlineStr">
+        <is>
+          <t>flag_refinanced</t>
+        </is>
+      </c>
+      <c r="AX1" s="1" t="inlineStr">
+        <is>
+          <t>rating_firm_type</t>
+        </is>
+      </c>
+      <c r="AY1" s="1" t="inlineStr">
+        <is>
+          <t>coverage_ratio_limit</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>American Vietnamese Biotech Incorporation (HNX:AMV)</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>HNX:AMV</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>Healthcare Products</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>Vietnam</t>
+        </is>
+      </c>
+      <c r="E2">
+        <v>1.38746145940391</v>
+      </c>
+      <c r="F2">
+        <v>4.5462858052328</v>
+      </c>
+      <c r="G2">
+        <v>3.0762331838565</v>
+      </c>
+      <c r="H2">
+        <v>5.49704035874439</v>
+      </c>
+      <c r="I2">
+        <v>0.246231155778894</v>
+      </c>
+      <c r="J2">
+        <v>0.44</v>
+      </c>
+      <c r="K2">
+        <v>21</v>
+      </c>
+      <c r="L2">
+        <v>18.357837356236</v>
+      </c>
+      <c r="M2">
+        <v>24.49</v>
+      </c>
+      <c r="N2">
+        <v>27.246237356236</v>
+      </c>
+      <c r="O2">
+        <v>6.86</v>
+      </c>
+      <c r="P2">
+        <v>12.2584</v>
+      </c>
+      <c r="Q2">
+        <v>0.134729237262129</v>
+      </c>
+      <c r="R2">
+        <v>0.125025007505921</v>
+      </c>
+      <c r="S2">
+        <v>0.0669075490536408</v>
+      </c>
+      <c r="T2">
+        <v>0.04072</v>
+      </c>
+      <c r="U2" t="inlineStr">
+        <is>
+          <t>Caa/CCC</t>
+        </is>
+      </c>
+      <c r="V2" t="inlineStr">
+        <is>
+          <t>A3/A-</t>
+        </is>
+      </c>
+      <c r="W2">
+        <v>0.156884322076902</v>
+      </c>
+      <c r="X2">
+        <v>0.191264656260573</v>
+      </c>
+      <c r="Y2">
+        <v>1.31198369289605</v>
+      </c>
+      <c r="Z2">
+        <v>1.6939686762702</v>
+      </c>
+      <c r="AA2">
+        <v>6.86</v>
+      </c>
+      <c r="AB2">
+        <v>0.083634436317051</v>
+      </c>
+      <c r="AC2">
+        <v>1.387461459403906</v>
+      </c>
+      <c r="AD2">
+        <v>6.86</v>
+      </c>
+      <c r="AE2">
+        <v>0.973</v>
+      </c>
+      <c r="AF2">
+        <v>0.8799999999999999</v>
+      </c>
+      <c r="AG2">
+        <v>2.23</v>
+      </c>
+      <c r="AH2">
+        <v>0</v>
+      </c>
+      <c r="AI2">
+        <v>0.0388</v>
+      </c>
+      <c r="AJ2">
+        <v>21</v>
+      </c>
+      <c r="AK2">
+        <v>0.0900044129483385</v>
+      </c>
+      <c r="AL2" t="inlineStr">
+        <is>
+          <t>Caa/CCC</t>
+        </is>
+      </c>
+      <c r="AM2">
+        <v>0.2</v>
+      </c>
+      <c r="AN2">
+        <v>0</v>
+      </c>
+      <c r="AO2">
+        <v>2</v>
+      </c>
+      <c r="AQ2">
+        <v>0.8919999999999977</v>
+      </c>
+      <c r="AR2">
+        <v>0.973</v>
+      </c>
+      <c r="AS2">
+        <v>6.86</v>
+      </c>
+      <c r="AT2">
+        <v>3.37</v>
+      </c>
+      <c r="AV2" t="b">
+        <v>0</v>
+      </c>
+      <c r="AW2" t="b">
+        <v>1</v>
+      </c>
+      <c r="AX2">
+        <v>1</v>
+      </c>
+      <c r="AY2">
+        <v>10000000</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:Z101"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1" s="1" customFormat="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>debt_capital</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>cost_capital</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>equity_value</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>enterprise_value</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>debt_issued</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>debt</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>cash</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>marketcap</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>drop_ebitda</t>
+        </is>
+      </c>
+      <c r="J1" s="1" t="inlineStr">
+        <is>
+          <t>ebitda</t>
+        </is>
+      </c>
+      <c r="K1" s="1" t="inlineStr">
+        <is>
+          <t>depreciation</t>
+        </is>
+      </c>
+      <c r="L1" s="1" t="inlineStr">
+        <is>
+          <t>ebit</t>
+        </is>
+      </c>
+      <c r="M1" s="1" t="inlineStr">
+        <is>
+          <t>interest_expense</t>
+        </is>
+      </c>
+      <c r="N1" s="1" t="inlineStr">
+        <is>
+          <t>taxable_income</t>
+        </is>
+      </c>
+      <c r="O1" s="1" t="inlineStr">
+        <is>
+          <t>taxes</t>
+        </is>
+      </c>
+      <c r="P1" s="1" t="inlineStr">
+        <is>
+          <t>net_income</t>
+        </is>
+      </c>
+      <c r="Q1" s="1" t="inlineStr">
+        <is>
+          <t>operating_cash_flow</t>
+        </is>
+      </c>
+      <c r="R1" s="1" t="inlineStr">
+        <is>
+          <t>debt_equity</t>
+        </is>
+      </c>
+      <c r="S1" s="1" t="inlineStr">
+        <is>
+          <t>cost_equity</t>
+        </is>
+      </c>
+      <c r="T1" s="1" t="inlineStr">
+        <is>
+          <t>beta</t>
+        </is>
+      </c>
+      <c r="U1" s="1" t="inlineStr">
+        <is>
+          <t>cost_debt_pre_tax</t>
+        </is>
+      </c>
+      <c r="V1" s="1" t="inlineStr">
+        <is>
+          <t>tax_rate</t>
+        </is>
+      </c>
+      <c r="W1" s="1" t="inlineStr">
+        <is>
+          <t>cost_debt_after_tax</t>
+        </is>
+      </c>
+      <c r="X1" s="1" t="inlineStr">
+        <is>
+          <t>debt_rating</t>
+        </is>
+      </c>
+      <c r="Y1" s="1" t="inlineStr">
+        <is>
+          <t>coverage_ratio</t>
+        </is>
+      </c>
+      <c r="Z1" s="1" t="inlineStr">
+        <is>
+          <t>coverage_error</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2">
+        <v>0</v>
+      </c>
+      <c r="B2">
+        <v>0.1324186485810537</v>
+      </c>
+      <c r="C2">
+        <v>28.46443424101078</v>
+      </c>
+      <c r="D2">
+        <v>25.09443424101078</v>
+      </c>
+      <c r="E2">
+        <v>-6.86</v>
+      </c>
+      <c r="F2">
+        <v>0</v>
+      </c>
+      <c r="G2">
+        <v>3.37</v>
+      </c>
+      <c r="H2">
+        <v>21</v>
+      </c>
+      <c r="I2">
+        <v>0</v>
+      </c>
+      <c r="J2">
+        <v>3.716666666666667</v>
+      </c>
+      <c r="K2">
+        <v>0.8799999999999999</v>
+      </c>
+      <c r="L2">
+        <v>2.836666666666667</v>
+      </c>
+      <c r="M2">
+        <v>0</v>
+      </c>
+      <c r="N2">
+        <v>2.836666666666667</v>
+      </c>
+      <c r="O2">
+        <v>0.5673333333333334</v>
+      </c>
+      <c r="P2">
+        <v>2.269333333333333</v>
+      </c>
+      <c r="Q2">
+        <v>3.149333333333333</v>
+      </c>
+      <c r="R2">
+        <v>0</v>
+      </c>
+      <c r="S2">
+        <v>0.1324186485810537</v>
+      </c>
+      <c r="T2">
+        <v>1.040156204727314</v>
+      </c>
+      <c r="U2">
+        <v>0.0447</v>
+      </c>
+      <c r="V2">
+        <v>0.2</v>
+      </c>
+      <c r="W2">
+        <v>0.03576000000000001</v>
+      </c>
+      <c r="X2" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y2">
+        <v>10000000</v>
+      </c>
+      <c r="Z2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3">
+        <v>0.01</v>
+      </c>
+      <c r="B3">
+        <v>0.1322010112838916</v>
+      </c>
+      <c r="C3">
+        <v>28.24430774966933</v>
+      </c>
+      <c r="D3">
+        <v>25.15290774966933</v>
+      </c>
+      <c r="E3">
+        <v>-6.5814</v>
+      </c>
+      <c r="F3">
+        <v>0.2786</v>
+      </c>
+      <c r="G3">
+        <v>3.37</v>
+      </c>
+      <c r="H3">
+        <v>21</v>
+      </c>
+      <c r="I3">
+        <v>0</v>
+      </c>
+      <c r="J3">
+        <v>3.716666666666667</v>
+      </c>
+      <c r="K3">
+        <v>0.8799999999999999</v>
+      </c>
+      <c r="L3">
+        <v>2.836666666666667</v>
+      </c>
+      <c r="M3">
+        <v>0.01245342</v>
+      </c>
+      <c r="N3">
+        <v>2.824213246666667</v>
+      </c>
+      <c r="O3">
+        <v>0.5648426493333334</v>
+      </c>
+      <c r="P3">
+        <v>2.259370597333334</v>
+      </c>
+      <c r="Q3">
+        <v>3.139370597333333</v>
+      </c>
+      <c r="R3">
+        <v>0.0101010101010101</v>
+      </c>
+      <c r="S3">
+        <v>0.1331751629130218</v>
+      </c>
+      <c r="T3">
+        <v>1.048561507391778</v>
+      </c>
+      <c r="U3">
+        <v>0.0447</v>
+      </c>
+      <c r="V3">
+        <v>0.2</v>
+      </c>
+      <c r="W3">
+        <v>0.03576000000000001</v>
+      </c>
+      <c r="X3" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y3">
+        <v>227.7821407024469</v>
+      </c>
+      <c r="Z3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4">
+        <v>0.02</v>
+      </c>
+      <c r="B4">
+        <v>0.1319833739867295</v>
+      </c>
+      <c r="C4">
+        <v>28.02445439753364</v>
+      </c>
+      <c r="D4">
+        <v>25.21165439753364</v>
+      </c>
+      <c r="E4">
+        <v>-6.3028</v>
+      </c>
+      <c r="F4">
+        <v>0.5572</v>
+      </c>
+      <c r="G4">
+        <v>3.37</v>
+      </c>
+      <c r="H4">
+        <v>21</v>
+      </c>
+      <c r="I4">
+        <v>0</v>
+      </c>
+      <c r="J4">
+        <v>3.716666666666667</v>
+      </c>
+      <c r="K4">
+        <v>0.8799999999999999</v>
+      </c>
+      <c r="L4">
+        <v>2.836666666666667</v>
+      </c>
+      <c r="M4">
+        <v>0.02490684</v>
+      </c>
+      <c r="N4">
+        <v>2.811759826666667</v>
+      </c>
+      <c r="O4">
+        <v>0.5623519653333334</v>
+      </c>
+      <c r="P4">
+        <v>2.249407861333334</v>
+      </c>
+      <c r="Q4">
+        <v>3.129407861333334</v>
+      </c>
+      <c r="R4">
+        <v>0.02040816326530612</v>
+      </c>
+      <c r="S4">
+        <v>0.1339471163129893</v>
+      </c>
+      <c r="T4">
+        <v>1.057138346845311</v>
+      </c>
+      <c r="U4">
+        <v>0.0447</v>
+      </c>
+      <c r="V4">
+        <v>0.2</v>
+      </c>
+      <c r="W4">
+        <v>0.03576000000000001</v>
+      </c>
+      <c r="X4" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y4">
+        <v>113.8910703512235</v>
+      </c>
+      <c r="Z4">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5">
+        <v>0.03</v>
+      </c>
+      <c r="B5">
+        <v>0.1317657366895674</v>
+      </c>
+      <c r="C5">
+        <v>27.80487610290006</v>
+      </c>
+      <c r="D5">
+        <v>25.27067610290006</v>
+      </c>
+      <c r="E5">
+        <v>-6.0242</v>
+      </c>
+      <c r="F5">
+        <v>0.8358</v>
+      </c>
+      <c r="G5">
+        <v>3.37</v>
+      </c>
+      <c r="H5">
+        <v>21</v>
+      </c>
+      <c r="I5">
+        <v>0</v>
+      </c>
+      <c r="J5">
+        <v>3.716666666666667</v>
+      </c>
+      <c r="K5">
+        <v>0.8799999999999999</v>
+      </c>
+      <c r="L5">
+        <v>2.836666666666667</v>
+      </c>
+      <c r="M5">
+        <v>0.03736026</v>
+      </c>
+      <c r="N5">
+        <v>2.799306406666667</v>
+      </c>
+      <c r="O5">
+        <v>0.5598612813333335</v>
+      </c>
+      <c r="P5">
+        <v>2.239445125333334</v>
+      </c>
+      <c r="Q5">
+        <v>3.119445125333334</v>
+      </c>
+      <c r="R5">
+        <v>0.03092783505154639</v>
+      </c>
+      <c r="S5">
+        <v>0.1347349862779045</v>
+      </c>
+      <c r="T5">
+        <v>1.065892028349433</v>
+      </c>
+      <c r="U5">
+        <v>0.0447</v>
+      </c>
+      <c r="V5">
+        <v>0.2</v>
+      </c>
+      <c r="W5">
+        <v>0.03576000000000001</v>
+      </c>
+      <c r="X5" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y5">
+        <v>75.92738023414898</v>
+      </c>
+      <c r="Z5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6">
+        <v>0.04</v>
+      </c>
+      <c r="B6">
+        <v>0.1315480993924053</v>
+      </c>
+      <c r="C6">
+        <v>27.58557480207044</v>
+      </c>
+      <c r="D6">
+        <v>25.32997480207044</v>
+      </c>
+      <c r="E6">
+        <v>-5.7456</v>
+      </c>
+      <c r="F6">
+        <v>1.1144</v>
+      </c>
+      <c r="G6">
+        <v>3.37</v>
+      </c>
+      <c r="H6">
+        <v>21</v>
+      </c>
+      <c r="I6">
+        <v>0</v>
+      </c>
+      <c r="J6">
+        <v>3.716666666666667</v>
+      </c>
+      <c r="K6">
+        <v>0.8799999999999999</v>
+      </c>
+      <c r="L6">
+        <v>2.836666666666667</v>
+      </c>
+      <c r="M6">
+        <v>0.04981368000000001</v>
+      </c>
+      <c r="N6">
+        <v>2.786852986666667</v>
+      </c>
+      <c r="O6">
+        <v>0.5573705973333334</v>
+      </c>
+      <c r="P6">
+        <v>2.229482389333334</v>
+      </c>
+      <c r="Q6">
+        <v>3.109482389333333</v>
+      </c>
+      <c r="R6">
+        <v>0.04166666666666667</v>
+      </c>
+      <c r="S6">
+        <v>0.1355392702004222</v>
+      </c>
+      <c r="T6">
+        <v>1.074828078218225</v>
+      </c>
+      <c r="U6">
+        <v>0.0447</v>
+      </c>
+      <c r="V6">
+        <v>0.2</v>
+      </c>
+      <c r="W6">
+        <v>0.03576000000000001</v>
+      </c>
+      <c r="X6" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y6">
+        <v>56.94553517561172</v>
+      </c>
+      <c r="Z6">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7">
+        <v>0.05</v>
+      </c>
+      <c r="B7">
+        <v>0.1313304620952432</v>
+      </c>
+      <c r="C7">
+        <v>27.36655244956378</v>
+      </c>
+      <c r="D7">
+        <v>25.38955244956378</v>
+      </c>
+      <c r="E7">
+        <v>-5.467000000000001</v>
+      </c>
+      <c r="F7">
+        <v>1.393</v>
+      </c>
+      <c r="G7">
+        <v>3.37</v>
+      </c>
+      <c r="H7">
+        <v>21</v>
+      </c>
+      <c r="I7">
+        <v>0</v>
+      </c>
+      <c r="J7">
+        <v>3.716666666666667</v>
+      </c>
+      <c r="K7">
+        <v>0.8799999999999999</v>
+      </c>
+      <c r="L7">
+        <v>2.836666666666667</v>
+      </c>
+      <c r="M7">
+        <v>0.06226710000000001</v>
+      </c>
+      <c r="N7">
+        <v>2.774399566666667</v>
+      </c>
+      <c r="O7">
+        <v>0.5548799133333334</v>
+      </c>
+      <c r="P7">
+        <v>2.219519653333333</v>
+      </c>
+      <c r="Q7">
+        <v>3.099519653333333</v>
+      </c>
+      <c r="R7">
+        <v>0.05263157894736843</v>
+      </c>
+      <c r="S7">
+        <v>0.1363604864160455</v>
+      </c>
+      <c r="T7">
+        <v>1.083952255452675</v>
+      </c>
+      <c r="U7">
+        <v>0.0447</v>
+      </c>
+      <c r="V7">
+        <v>0.2</v>
+      </c>
+      <c r="W7">
+        <v>0.03576000000000001</v>
+      </c>
+      <c r="X7" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y7">
+        <v>45.55642814048938</v>
+      </c>
+      <c r="Z7">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8">
+        <v>0.06</v>
+      </c>
+      <c r="B8">
+        <v>0.1311128247980811</v>
+      </c>
+      <c r="C8">
+        <v>27.14781101833108</v>
+      </c>
+      <c r="D8">
+        <v>25.44941101833108</v>
+      </c>
+      <c r="E8">
+        <v>-5.188400000000001</v>
+      </c>
+      <c r="F8">
+        <v>1.6716</v>
+      </c>
+      <c r="G8">
+        <v>3.37</v>
+      </c>
+      <c r="H8">
+        <v>21</v>
+      </c>
+      <c r="I8">
+        <v>0</v>
+      </c>
+      <c r="J8">
+        <v>3.716666666666667</v>
+      </c>
+      <c r="K8">
+        <v>0.8799999999999999</v>
+      </c>
+      <c r="L8">
+        <v>2.836666666666667</v>
+      </c>
+      <c r="M8">
+        <v>0.07472052</v>
+      </c>
+      <c r="N8">
+        <v>2.761946146666667</v>
+      </c>
+      <c r="O8">
+        <v>0.5523892293333333</v>
+      </c>
+      <c r="P8">
+        <v>2.209556917333333</v>
+      </c>
+      <c r="Q8">
+        <v>3.089556917333333</v>
+      </c>
+      <c r="R8">
+        <v>0.06382978723404255</v>
+      </c>
+      <c r="S8">
+        <v>0.1371991753171075</v>
+      </c>
+      <c r="T8">
+        <v>1.093270564117645</v>
+      </c>
+      <c r="U8">
+        <v>0.0447</v>
+      </c>
+      <c r="V8">
+        <v>0.2</v>
+      </c>
+      <c r="W8">
+        <v>0.03576000000000001</v>
+      </c>
+      <c r="X8" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y8">
+        <v>37.96369011707449</v>
+      </c>
+      <c r="Z8">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9">
+        <v>0.07000000000000001</v>
+      </c>
+      <c r="B9">
+        <v>0.130895187500919</v>
+      </c>
+      <c r="C9">
+        <v>26.92935249997301</v>
+      </c>
+      <c r="D9">
+        <v>25.50955249997301</v>
+      </c>
+      <c r="E9">
+        <v>-4.909800000000001</v>
+      </c>
+      <c r="F9">
+        <v>1.9502</v>
+      </c>
+      <c r="G9">
+        <v>3.37</v>
+      </c>
+      <c r="H9">
+        <v>21</v>
+      </c>
+      <c r="I9">
+        <v>0</v>
+      </c>
+      <c r="J9">
+        <v>3.716666666666667</v>
+      </c>
+      <c r="K9">
+        <v>0.8799999999999999</v>
+      </c>
+      <c r="L9">
+        <v>2.836666666666667</v>
+      </c>
+      <c r="M9">
+        <v>0.08717394000000002</v>
+      </c>
+      <c r="N9">
+        <v>2.749492726666667</v>
+      </c>
+      <c r="O9">
+        <v>0.5498985453333334</v>
+      </c>
+      <c r="P9">
+        <v>2.199594181333334</v>
+      </c>
+      <c r="Q9">
+        <v>3.079594181333333</v>
+      </c>
+      <c r="R9">
+        <v>0.07526881720430109</v>
+      </c>
+      <c r="S9">
+        <v>0.1380559005386225</v>
+      </c>
+      <c r="T9">
+        <v>1.102789266517346</v>
+      </c>
+      <c r="U9">
+        <v>0.0447</v>
+      </c>
+      <c r="V9">
+        <v>0.2</v>
+      </c>
+      <c r="W9">
+        <v>0.03576000000000001</v>
+      </c>
+      <c r="X9" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y9">
+        <v>32.54030581463527</v>
+      </c>
+      <c r="Z9">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10">
+        <v>0.08</v>
+      </c>
+      <c r="B10">
+        <v>0.1306775502037568</v>
+      </c>
+      <c r="C10">
+        <v>26.71117890496092</v>
+      </c>
+      <c r="D10">
+        <v>25.56997890496092</v>
+      </c>
+      <c r="E10">
+        <v>-4.6312</v>
+      </c>
+      <c r="F10">
+        <v>2.2288</v>
+      </c>
+      <c r="G10">
+        <v>3.37</v>
+      </c>
+      <c r="H10">
+        <v>21</v>
+      </c>
+      <c r="I10">
+        <v>0</v>
+      </c>
+      <c r="J10">
+        <v>3.716666666666667</v>
+      </c>
+      <c r="K10">
+        <v>0.8799999999999999</v>
+      </c>
+      <c r="L10">
+        <v>2.836666666666667</v>
+      </c>
+      <c r="M10">
+        <v>0.09962736000000001</v>
+      </c>
+      <c r="N10">
+        <v>2.737039306666667</v>
+      </c>
+      <c r="O10">
+        <v>0.5474078613333334</v>
+      </c>
+      <c r="P10">
+        <v>2.189631445333334</v>
+      </c>
+      <c r="Q10">
+        <v>3.069631445333334</v>
+      </c>
+      <c r="R10">
+        <v>0.08695652173913043</v>
+      </c>
+      <c r="S10">
+        <v>0.1389312502214748</v>
+      </c>
+      <c r="T10">
+        <v>1.112514897230084</v>
+      </c>
+      <c r="U10">
+        <v>0.0447</v>
+      </c>
+      <c r="V10">
+        <v>0.2</v>
+      </c>
+      <c r="W10">
+        <v>0.03576000000000001</v>
+      </c>
+      <c r="X10" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y10">
+        <v>28.47276758780587</v>
+      </c>
+      <c r="Z10">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11">
+        <v>0.09</v>
+      </c>
+      <c r="B11">
+        <v>0.1304599129065948</v>
+      </c>
+      <c r="C11">
+        <v>26.49329226286077</v>
+      </c>
+      <c r="D11">
+        <v>25.63069226286077</v>
+      </c>
+      <c r="E11">
+        <v>-4.352600000000001</v>
+      </c>
+      <c r="F11">
+        <v>2.5074</v>
+      </c>
+      <c r="G11">
+        <v>3.37</v>
+      </c>
+      <c r="H11">
+        <v>21</v>
+      </c>
+      <c r="I11">
+        <v>0</v>
+      </c>
+      <c r="J11">
+        <v>3.716666666666667</v>
+      </c>
+      <c r="K11">
+        <v>0.8799999999999999</v>
+      </c>
+      <c r="L11">
+        <v>2.836666666666667</v>
+      </c>
+      <c r="M11">
+        <v>0.11208078</v>
+      </c>
+      <c r="N11">
+        <v>2.724585886666667</v>
+      </c>
+      <c r="O11">
+        <v>0.5449171773333334</v>
+      </c>
+      <c r="P11">
+        <v>2.179668709333334</v>
+      </c>
+      <c r="Q11">
+        <v>3.059668709333334</v>
+      </c>
+      <c r="R11">
+        <v>0.0989010989010989</v>
+      </c>
+      <c r="S11">
+        <v>0.1398258383588953</v>
+      </c>
+      <c r="T11">
+        <v>1.122454278068376</v>
+      </c>
+      <c r="U11">
+        <v>0.0447</v>
+      </c>
+      <c r="V11">
+        <v>0.2</v>
+      </c>
+      <c r="W11">
+        <v>0.03576000000000001</v>
+      </c>
+      <c r="X11" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y11">
+        <v>25.30912674471632</v>
+      </c>
+      <c r="Z11">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12">
+        <v>0.1</v>
+      </c>
+      <c r="B12">
+        <v>0.1302422756094327</v>
+      </c>
+      <c r="C12">
+        <v>26.27569462256043</v>
+      </c>
+      <c r="D12">
+        <v>25.69169462256043</v>
+      </c>
+      <c r="E12">
+        <v>-4.074</v>
+      </c>
+      <c r="F12">
+        <v>2.786</v>
+      </c>
+      <c r="G12">
+        <v>3.37</v>
+      </c>
+      <c r="H12">
+        <v>21</v>
+      </c>
+      <c r="I12">
+        <v>0</v>
+      </c>
+      <c r="J12">
+        <v>3.716666666666667</v>
+      </c>
+      <c r="K12">
+        <v>0.8799999999999999</v>
+      </c>
+      <c r="L12">
+        <v>2.836666666666667</v>
+      </c>
+      <c r="M12">
+        <v>0.1245342</v>
+      </c>
+      <c r="N12">
+        <v>2.712132466666667</v>
+      </c>
+      <c r="O12">
+        <v>0.5424264933333335</v>
+      </c>
+      <c r="P12">
+        <v>2.169705973333333</v>
+      </c>
+      <c r="Q12">
+        <v>3.049705973333333</v>
+      </c>
+      <c r="R12">
+        <v>0.1111111111111111</v>
+      </c>
+      <c r="S12">
+        <v>0.1407403062327029</v>
+      </c>
+      <c r="T12">
+        <v>1.132614534036409</v>
+      </c>
+      <c r="U12">
+        <v>0.0447</v>
+      </c>
+      <c r="V12">
+        <v>0.2</v>
+      </c>
+      <c r="W12">
+        <v>0.03576000000000001</v>
+      </c>
+      <c r="X12" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y12">
+        <v>22.77821407024469</v>
+      </c>
+      <c r="Z12">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13">
+        <v>0.11</v>
+      </c>
+      <c r="B13">
+        <v>0.1300246383122705</v>
+      </c>
+      <c r="C13">
+        <v>26.05838805250015</v>
+      </c>
+      <c r="D13">
+        <v>25.75298805250015</v>
+      </c>
+      <c r="E13">
+        <v>-3.7954</v>
+      </c>
+      <c r="F13">
+        <v>3.0646</v>
+      </c>
+      <c r="G13">
+        <v>3.37</v>
+      </c>
+      <c r="H13">
+        <v>21</v>
+      </c>
+      <c r="I13">
+        <v>0</v>
+      </c>
+      <c r="J13">
+        <v>3.716666666666667</v>
+      </c>
+      <c r="K13">
+        <v>0.8799999999999999</v>
+      </c>
+      <c r="L13">
+        <v>2.836666666666667</v>
+      </c>
+      <c r="M13">
+        <v>0.13698762</v>
+      </c>
+      <c r="N13">
+        <v>2.699679046666667</v>
+      </c>
+      <c r="O13">
+        <v>0.5399358093333334</v>
+      </c>
+      <c r="P13">
+        <v>2.159743237333333</v>
+      </c>
+      <c r="Q13">
+        <v>3.039743237333333</v>
+      </c>
+      <c r="R13">
+        <v>0.1235955056179775</v>
+      </c>
+      <c r="S13">
+        <v>0.1416753239463714</v>
+      </c>
+      <c r="T13">
+        <v>1.143003110363273</v>
+      </c>
+      <c r="U13">
+        <v>0.0447</v>
+      </c>
+      <c r="V13">
+        <v>0.2</v>
+      </c>
+      <c r="W13">
+        <v>0.03576000000000001</v>
+      </c>
+      <c r="X13" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y13">
+        <v>20.70746733658608</v>
+      </c>
+      <c r="Z13">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14">
+        <v>0.12</v>
+      </c>
+      <c r="B14">
+        <v>0.1298070010151084</v>
+      </c>
+      <c r="C14">
+        <v>25.84137464090628</v>
+      </c>
+      <c r="D14">
+        <v>25.81457464090628</v>
+      </c>
+      <c r="E14">
+        <v>-3.5168</v>
+      </c>
+      <c r="F14">
+        <v>3.3432</v>
+      </c>
+      <c r="G14">
+        <v>3.37</v>
+      </c>
+      <c r="H14">
+        <v>21</v>
+      </c>
+      <c r="I14">
+        <v>0</v>
+      </c>
+      <c r="J14">
+        <v>3.716666666666667</v>
+      </c>
+      <c r="K14">
+        <v>0.8799999999999999</v>
+      </c>
+      <c r="L14">
+        <v>2.836666666666667</v>
+      </c>
+      <c r="M14">
+        <v>0.14944104</v>
+      </c>
+      <c r="N14">
+        <v>2.687225626666667</v>
+      </c>
+      <c r="O14">
+        <v>0.5374451253333333</v>
+      </c>
+      <c r="P14">
+        <v>2.149780501333333</v>
+      </c>
+      <c r="Q14">
+        <v>3.029780501333333</v>
+      </c>
+      <c r="R14">
+        <v>0.1363636363636364</v>
+      </c>
+      <c r="S14">
+        <v>0.1426315920626232</v>
+      </c>
+      <c r="T14">
+        <v>1.153627790697567</v>
+      </c>
+      <c r="U14">
+        <v>0.0447</v>
+      </c>
+      <c r="V14">
+        <v>0.2</v>
+      </c>
+      <c r="W14">
+        <v>0.03576000000000001</v>
+      </c>
+      <c r="X14" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y14">
+        <v>18.98184505853725</v>
+      </c>
+      <c r="Z14">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15">
+        <v>0.13</v>
+      </c>
+      <c r="B15">
+        <v>0.1295893637179463</v>
+      </c>
+      <c r="C15">
+        <v>25.62465649602854</v>
+      </c>
+      <c r="D15">
+        <v>25.87645649602854</v>
+      </c>
+      <c r="E15">
+        <v>-3.2382</v>
+      </c>
+      <c r="F15">
+        <v>3.6218</v>
+      </c>
+      <c r="G15">
+        <v>3.37</v>
+      </c>
+      <c r="H15">
+        <v>21</v>
+      </c>
+      <c r="I15">
+        <v>0</v>
+      </c>
+      <c r="J15">
+        <v>3.716666666666667</v>
+      </c>
+      <c r="K15">
+        <v>0.8799999999999999</v>
+      </c>
+      <c r="L15">
+        <v>2.836666666666667</v>
+      </c>
+      <c r="M15">
+        <v>0.16189446</v>
+      </c>
+      <c r="N15">
+        <v>2.674772206666667</v>
+      </c>
+      <c r="O15">
+        <v>0.5349544413333334</v>
+      </c>
+      <c r="P15">
+        <v>2.139817765333333</v>
+      </c>
+      <c r="Q15">
+        <v>3.019817765333333</v>
+      </c>
+      <c r="R15">
+        <v>0.1494252873563219</v>
+      </c>
+      <c r="S15">
+        <v>0.1436098433539613</v>
+      </c>
+      <c r="T15">
+        <v>1.164496716556786</v>
+      </c>
+      <c r="U15">
+        <v>0.0447</v>
+      </c>
+      <c r="V15">
+        <v>0.2</v>
+      </c>
+      <c r="W15">
+        <v>0.03576000000000001</v>
+      </c>
+      <c r="X15" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y15">
+        <v>17.52170313095746</v>
+      </c>
+      <c r="Z15">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16">
+        <v>0.14</v>
+      </c>
+      <c r="B16">
+        <v>0.1293717264207842</v>
+      </c>
+      <c r="C16">
+        <v>25.40823574638052</v>
+      </c>
+      <c r="D16">
+        <v>25.93863574638052</v>
+      </c>
+      <c r="E16">
+        <v>-2.9596</v>
+      </c>
+      <c r="F16">
+        <v>3.9004</v>
+      </c>
+      <c r="G16">
+        <v>3.37</v>
+      </c>
+      <c r="H16">
+        <v>21</v>
+      </c>
+      <c r="I16">
+        <v>0</v>
+      </c>
+      <c r="J16">
+        <v>3.716666666666667</v>
+      </c>
+      <c r="K16">
+        <v>0.8799999999999999</v>
+      </c>
+      <c r="L16">
+        <v>2.836666666666667</v>
+      </c>
+      <c r="M16">
+        <v>0.17434788</v>
+      </c>
+      <c r="N16">
+        <v>2.662318786666667</v>
+      </c>
+      <c r="O16">
+        <v>0.5324637573333334</v>
+      </c>
+      <c r="P16">
+        <v>2.129855029333334</v>
+      </c>
+      <c r="Q16">
+        <v>3.009855029333333</v>
+      </c>
+      <c r="R16">
+        <v>0.1627906976744186</v>
+      </c>
+      <c r="S16">
+        <v>0.1446108446753305</v>
+      </c>
+      <c r="T16">
+        <v>1.175618408133662</v>
+      </c>
+      <c r="U16">
+        <v>0.0447</v>
+      </c>
+      <c r="V16">
+        <v>0.2</v>
+      </c>
+      <c r="W16">
+        <v>0.03576000000000001</v>
+      </c>
+      <c r="X16" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y16">
+        <v>16.27015290731764</v>
+      </c>
+      <c r="Z16">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17">
+        <v>0.15</v>
+      </c>
+      <c r="B17">
+        <v>0.1291540891236221</v>
+      </c>
+      <c r="C17">
+        <v>25.19211454098373</v>
+      </c>
+      <c r="D17">
+        <v>26.00111454098372</v>
+      </c>
+      <c r="E17">
+        <v>-2.681000000000001</v>
+      </c>
+      <c r="F17">
+        <v>4.178999999999999</v>
+      </c>
+      <c r="G17">
+        <v>3.37</v>
+      </c>
+      <c r="H17">
+        <v>21</v>
+      </c>
+      <c r="I17">
+        <v>0</v>
+      </c>
+      <c r="J17">
+        <v>3.716666666666667</v>
+      </c>
+      <c r="K17">
+        <v>0.8799999999999999</v>
+      </c>
+      <c r="L17">
+        <v>2.836666666666667</v>
+      </c>
+      <c r="M17">
+        <v>0.1868013</v>
+      </c>
+      <c r="N17">
+        <v>2.649865366666667</v>
+      </c>
+      <c r="O17">
+        <v>0.5299730733333334</v>
+      </c>
+      <c r="P17">
+        <v>2.119892293333334</v>
+      </c>
+      <c r="Q17">
+        <v>2.999892293333334</v>
+      </c>
+      <c r="R17">
+        <v>0.1764705882352941</v>
+      </c>
+      <c r="S17">
+        <v>0.1456353989689672</v>
+      </c>
+      <c r="T17">
+        <v>1.18700178657117</v>
+      </c>
+      <c r="U17">
+        <v>0.0447</v>
+      </c>
+      <c r="V17">
+        <v>0.2</v>
+      </c>
+      <c r="W17">
+        <v>0.03576000000000001</v>
+      </c>
+      <c r="X17" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y17">
+        <v>15.1854760468298</v>
+      </c>
+      <c r="Z17">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18">
+        <v>0.16</v>
+      </c>
+      <c r="B18">
+        <v>0.12893645182646</v>
+      </c>
+      <c r="C18">
+        <v>24.97629504961521</v>
+      </c>
+      <c r="D18">
+        <v>26.06389504961521</v>
+      </c>
+      <c r="E18">
+        <v>-2.4024</v>
+      </c>
+      <c r="F18">
+        <v>4.4576</v>
+      </c>
+      <c r="G18">
+        <v>3.37</v>
+      </c>
+      <c r="H18">
+        <v>21</v>
+      </c>
+      <c r="I18">
+        <v>0</v>
+      </c>
+      <c r="J18">
+        <v>3.716666666666667</v>
+      </c>
+      <c r="K18">
+        <v>0.8799999999999999</v>
+      </c>
+      <c r="L18">
+        <v>2.836666666666667</v>
+      </c>
+      <c r="M18">
+        <v>0.19925472</v>
+      </c>
+      <c r="N18">
+        <v>2.637411946666667</v>
+      </c>
+      <c r="O18">
+        <v>0.5274823893333335</v>
+      </c>
+      <c r="P18">
+        <v>2.109929557333333</v>
+      </c>
+      <c r="Q18">
+        <v>2.989929557333333</v>
+      </c>
+      <c r="R18">
+        <v>0.1904761904761905</v>
+      </c>
+      <c r="S18">
+        <v>0.1466843474124524</v>
+      </c>
+      <c r="T18">
+        <v>1.198656197828619</v>
+      </c>
+      <c r="U18">
+        <v>0.0447</v>
+      </c>
+      <c r="V18">
+        <v>0.2</v>
+      </c>
+      <c r="W18">
+        <v>0.03576000000000001</v>
+      </c>
+      <c r="X18" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y18">
+        <v>14.23638379390293</v>
+      </c>
+      <c r="Z18">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19">
+        <v>0.17</v>
+      </c>
+      <c r="B19">
+        <v>0.1287188145292979</v>
+      </c>
+      <c r="C19">
+        <v>24.76077946305871</v>
+      </c>
+      <c r="D19">
+        <v>26.12697946305871</v>
+      </c>
+      <c r="E19">
+        <v>-2.1238</v>
+      </c>
+      <c r="F19">
+        <v>4.7362</v>
+      </c>
+      <c r="G19">
+        <v>3.37</v>
+      </c>
+      <c r="H19">
+        <v>21</v>
+      </c>
+      <c r="I19">
+        <v>0</v>
+      </c>
+      <c r="J19">
+        <v>3.716666666666667</v>
+      </c>
+      <c r="K19">
+        <v>0.8799999999999999</v>
+      </c>
+      <c r="L19">
+        <v>2.836666666666667</v>
+      </c>
+      <c r="M19">
+        <v>0.21170814</v>
+      </c>
+      <c r="N19">
+        <v>2.624958526666667</v>
+      </c>
+      <c r="O19">
+        <v>0.5249917053333334</v>
+      </c>
+      <c r="P19">
+        <v>2.099966821333334</v>
+      </c>
+      <c r="Q19">
+        <v>2.979966821333333</v>
+      </c>
+      <c r="R19">
+        <v>0.2048192771084338</v>
+      </c>
+      <c r="S19">
+        <v>0.1477585717220457</v>
+      </c>
+      <c r="T19">
+        <v>1.210591438272995</v>
+      </c>
+      <c r="U19">
+        <v>0.0447</v>
+      </c>
+      <c r="V19">
+        <v>0.2</v>
+      </c>
+      <c r="W19">
+        <v>0.03576000000000001</v>
+      </c>
+      <c r="X19" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y19">
+        <v>13.39894945308511</v>
+      </c>
+      <c r="Z19">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20">
+        <v>0.18</v>
+      </c>
+      <c r="B20">
+        <v>0.1286595772321358</v>
+      </c>
+      <c r="C20">
+        <v>24.49940290984171</v>
+      </c>
+      <c r="D20">
+        <v>26.14420290984171</v>
+      </c>
+      <c r="E20">
+        <v>-1.8452</v>
+      </c>
+      <c r="F20">
+        <v>5.0148</v>
+      </c>
+      <c r="G20">
+        <v>3.37</v>
+      </c>
+      <c r="H20">
+        <v>21</v>
+      </c>
+      <c r="I20">
+        <v>0</v>
+      </c>
+      <c r="J20">
+        <v>3.716666666666667</v>
+      </c>
+      <c r="K20">
+        <v>0.8799999999999999</v>
+      </c>
+      <c r="L20">
+        <v>2.836666666666667</v>
+      </c>
+      <c r="M20">
+        <v>0.22967784</v>
+      </c>
+      <c r="N20">
+        <v>2.606988826666667</v>
+      </c>
+      <c r="O20">
+        <v>0.5213977653333334</v>
+      </c>
+      <c r="P20">
+        <v>2.085591061333333</v>
+      </c>
+      <c r="Q20">
+        <v>2.965591061333333</v>
+      </c>
+      <c r="R20">
+        <v>0.2195121951219512</v>
+      </c>
+      <c r="S20">
+        <v>0.1488589966245558</v>
+      </c>
+      <c r="T20">
+        <v>1.222817782142843</v>
+      </c>
+      <c r="U20">
+        <v>0.0458</v>
+      </c>
+      <c r="V20">
+        <v>0.2</v>
+      </c>
+      <c r="W20">
+        <v>0.03664</v>
+      </c>
+      <c r="X20" t="inlineStr">
+        <is>
+          <t>Aa2/AA</t>
+        </is>
+      </c>
+      <c r="Y20">
+        <v>12.35063281101332</v>
+      </c>
+      <c r="Z20">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21">
+        <v>0.19</v>
+      </c>
+      <c r="B21">
+        <v>0.1284507399349737</v>
+      </c>
+      <c r="C21">
+        <v>24.28170463442434</v>
+      </c>
+      <c r="D21">
+        <v>26.20510463442434</v>
+      </c>
+      <c r="E21">
+        <v>-1.5666</v>
+      </c>
+      <c r="F21">
+        <v>5.2934</v>
+      </c>
+      <c r="G21">
+        <v>3.37</v>
+      </c>
+      <c r="H21">
+        <v>21</v>
+      </c>
+      <c r="I21">
+        <v>0</v>
+      </c>
+      <c r="J21">
+        <v>3.716666666666667</v>
+      </c>
+      <c r="K21">
+        <v>0.8799999999999999</v>
+      </c>
+      <c r="L21">
+        <v>2.836666666666667</v>
+      </c>
+      <c r="M21">
+        <v>0.24243772</v>
+      </c>
+      <c r="N21">
+        <v>2.594228946666667</v>
+      </c>
+      <c r="O21">
+        <v>0.5188457893333335</v>
+      </c>
+      <c r="P21">
+        <v>2.075383157333333</v>
+      </c>
+      <c r="Q21">
+        <v>2.955383157333333</v>
+      </c>
+      <c r="R21">
+        <v>0.2345679012345679</v>
+      </c>
+      <c r="S21">
+        <v>0.1499865925123132</v>
+      </c>
+      <c r="T21">
+        <v>1.235346011046514</v>
+      </c>
+      <c r="U21">
+        <v>0.0458</v>
+      </c>
+      <c r="V21">
+        <v>0.2</v>
+      </c>
+      <c r="W21">
+        <v>0.03664</v>
+      </c>
+      <c r="X21" t="inlineStr">
+        <is>
+          <t>Aa2/AA</t>
+        </is>
+      </c>
+      <c r="Y21">
+        <v>11.70059950517051</v>
+      </c>
+      <c r="Z21">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22">
+        <v>0.2</v>
+      </c>
+      <c r="B22">
+        <v>0.1282419026378116</v>
+      </c>
+      <c r="C22">
+        <v>24.06429075706156</v>
+      </c>
+      <c r="D22">
+        <v>26.26629075706156</v>
+      </c>
+      <c r="E22">
+        <v>-1.288</v>
+      </c>
+      <c r="F22">
+        <v>5.572</v>
+      </c>
+      <c r="G22">
+        <v>3.37</v>
+      </c>
+      <c r="H22">
+        <v>21</v>
+      </c>
+      <c r="I22">
+        <v>0</v>
+      </c>
+      <c r="J22">
+        <v>3.716666666666667</v>
+      </c>
+      <c r="K22">
+        <v>0.8799999999999999</v>
+      </c>
+      <c r="L22">
+        <v>2.836666666666667</v>
+      </c>
+      <c r="M22">
+        <v>0.2551976</v>
+      </c>
+      <c r="N22">
+        <v>2.581469066666667</v>
+      </c>
+      <c r="O22">
+        <v>0.5162938133333335</v>
+      </c>
+      <c r="P22">
+        <v>2.065175253333334</v>
+      </c>
+      <c r="Q22">
+        <v>2.945175253333334</v>
+      </c>
+      <c r="R22">
+        <v>0.25</v>
+      </c>
+      <c r="S22">
+        <v>0.1511423782972645</v>
+      </c>
+      <c r="T22">
+        <v>1.248187445672777</v>
+      </c>
+      <c r="U22">
+        <v>0.0458</v>
+      </c>
+      <c r="V22">
+        <v>0.2</v>
+      </c>
+      <c r="W22">
+        <v>0.03664</v>
+      </c>
+      <c r="X22" t="inlineStr">
+        <is>
+          <t>Aa2/AA</t>
+        </is>
+      </c>
+      <c r="Y22">
+        <v>11.11556952991199</v>
+      </c>
+      <c r="Z22">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23">
+        <v>0.21</v>
+      </c>
+      <c r="B23">
+        <v>0.1280330653406495</v>
+      </c>
+      <c r="C23">
+        <v>23.84716327453295</v>
+      </c>
+      <c r="D23">
+        <v>26.32776327453294</v>
+      </c>
+      <c r="E23">
+        <v>-1.0094</v>
+      </c>
+      <c r="F23">
+        <v>5.8506</v>
+      </c>
+      <c r="G23">
+        <v>3.37</v>
+      </c>
+      <c r="H23">
+        <v>21</v>
+      </c>
+      <c r="I23">
+        <v>0</v>
+      </c>
+      <c r="J23">
+        <v>3.716666666666667</v>
+      </c>
+      <c r="K23">
+        <v>0.8799999999999999</v>
+      </c>
+      <c r="L23">
+        <v>2.836666666666667</v>
+      </c>
+      <c r="M23">
+        <v>0.26795748</v>
+      </c>
+      <c r="N23">
+        <v>2.568709186666667</v>
+      </c>
+      <c r="O23">
+        <v>0.5137418373333333</v>
+      </c>
+      <c r="P23">
+        <v>2.054967349333333</v>
+      </c>
+      <c r="Q23">
+        <v>2.934967349333333</v>
+      </c>
+      <c r="R23">
+        <v>0.2658227848101266</v>
+      </c>
+      <c r="S23">
+        <v>0.1523274244818348</v>
+      </c>
+      <c r="T23">
+        <v>1.261353979909832</v>
+      </c>
+      <c r="U23">
+        <v>0.0458</v>
+      </c>
+      <c r="V23">
+        <v>0.2</v>
+      </c>
+      <c r="W23">
+        <v>0.03664</v>
+      </c>
+      <c r="X23" t="inlineStr">
+        <is>
+          <t>Aa2/AA</t>
+        </is>
+      </c>
+      <c r="Y23">
+        <v>10.58625669515427</v>
+      </c>
+      <c r="Z23">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24">
+        <v>0.22</v>
+      </c>
+      <c r="B24">
+        <v>0.1278242280434874</v>
+      </c>
+      <c r="C24">
+        <v>23.63032420235466</v>
+      </c>
+      <c r="D24">
+        <v>26.38952420235466</v>
+      </c>
+      <c r="E24">
+        <v>-0.7308000000000003</v>
+      </c>
+      <c r="F24">
+        <v>6.1292</v>
+      </c>
+      <c r="G24">
+        <v>3.37</v>
+      </c>
+      <c r="H24">
+        <v>21</v>
+      </c>
+      <c r="I24">
+        <v>0</v>
+      </c>
+      <c r="J24">
+        <v>3.716666666666667</v>
+      </c>
+      <c r="K24">
+        <v>0.8799999999999999</v>
+      </c>
+      <c r="L24">
+        <v>2.836666666666667</v>
+      </c>
+      <c r="M24">
+        <v>0.28071736</v>
+      </c>
+      <c r="N24">
+        <v>2.555949306666667</v>
+      </c>
+      <c r="O24">
+        <v>0.5111898613333333</v>
+      </c>
+      <c r="P24">
+        <v>2.044759445333333</v>
+      </c>
+      <c r="Q24">
+        <v>2.924759445333333</v>
+      </c>
+      <c r="R24">
+        <v>0.282051282051282</v>
+      </c>
+      <c r="S24">
+        <v>0.1535428564660094</v>
+      </c>
+      <c r="T24">
+        <v>1.274858117588862</v>
+      </c>
+      <c r="U24">
+        <v>0.0458</v>
+      </c>
+      <c r="V24">
+        <v>0.2</v>
+      </c>
+      <c r="W24">
+        <v>0.03664</v>
+      </c>
+      <c r="X24" t="inlineStr">
+        <is>
+          <t>Aa2/AA</t>
+        </is>
+      </c>
+      <c r="Y24">
+        <v>10.1050632090109</v>
+      </c>
+      <c r="Z24">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25">
+        <v>0.23</v>
+      </c>
+      <c r="B25">
+        <v>0.1280201907463253</v>
+      </c>
+      <c r="C25">
+        <v>23.29376240641989</v>
+      </c>
+      <c r="D25">
+        <v>26.33156240641989</v>
+      </c>
+      <c r="E25">
+        <v>-0.4522000000000004</v>
+      </c>
+      <c r="F25">
+        <v>6.4078</v>
+      </c>
+      <c r="G25">
+        <v>3.37</v>
+      </c>
+      <c r="H25">
+        <v>21</v>
+      </c>
+      <c r="I25">
+        <v>0</v>
+      </c>
+      <c r="J25">
+        <v>3.716666666666667</v>
+      </c>
+      <c r="K25">
+        <v>0.8799999999999999</v>
+      </c>
+      <c r="L25">
+        <v>2.836666666666667</v>
+      </c>
+      <c r="M25">
+        <v>0.3075744</v>
+      </c>
+      <c r="N25">
+        <v>2.529092266666667</v>
+      </c>
+      <c r="O25">
+        <v>0.5058184533333334</v>
+      </c>
+      <c r="P25">
+        <v>2.023273813333334</v>
+      </c>
+      <c r="Q25">
+        <v>2.903273813333334</v>
+      </c>
+      <c r="R25">
+        <v>0.2987012987012987</v>
+      </c>
+      <c r="S25">
+        <v>0.1547898581121107</v>
+      </c>
+      <c r="T25">
+        <v>1.288713012090725</v>
+      </c>
+      <c r="U25">
+        <v>0.048</v>
+      </c>
+      <c r="V25">
+        <v>0.2</v>
+      </c>
+      <c r="W25">
+        <v>0.0384</v>
+      </c>
+      <c r="X25" t="inlineStr">
+        <is>
+          <t>A1/A+</t>
+        </is>
+      </c>
+      <c r="Y25">
+        <v>9.222700805615379</v>
+      </c>
+      <c r="Z25">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26">
+        <v>0.24</v>
+      </c>
+      <c r="B26">
+        <v>0.1278289534491631</v>
+      </c>
+      <c r="C26">
+        <v>23.07172352086156</v>
+      </c>
+      <c r="D26">
+        <v>26.38812352086156</v>
+      </c>
+      <c r="E26">
+        <v>-0.1736000000000004</v>
+      </c>
+      <c r="F26">
+        <v>6.6864</v>
+      </c>
+      <c r="G26">
+        <v>3.37</v>
+      </c>
+      <c r="H26">
+        <v>21</v>
+      </c>
+      <c r="I26">
+        <v>0</v>
+      </c>
+      <c r="J26">
+        <v>3.716666666666667</v>
+      </c>
+      <c r="K26">
+        <v>0.8799999999999999</v>
+      </c>
+      <c r="L26">
+        <v>2.836666666666667</v>
+      </c>
+      <c r="M26">
+        <v>0.3209472</v>
+      </c>
+      <c r="N26">
+        <v>2.515719466666667</v>
+      </c>
+      <c r="O26">
+        <v>0.5031438933333334</v>
+      </c>
+      <c r="P26">
+        <v>2.012575573333334</v>
+      </c>
+      <c r="Q26">
+        <v>2.892575573333334</v>
+      </c>
+      <c r="R26">
+        <v>0.3157894736842105</v>
+      </c>
+      <c r="S26">
+        <v>0.1560696755910041</v>
+      </c>
+      <c r="T26">
+        <v>1.302932509079478</v>
+      </c>
+      <c r="U26">
+        <v>0.048</v>
+      </c>
+      <c r="V26">
+        <v>0.2</v>
+      </c>
+      <c r="W26">
+        <v>0.0384</v>
+      </c>
+      <c r="X26" t="inlineStr">
+        <is>
+          <t>A1/A+</t>
+        </is>
+      </c>
+      <c r="Y26">
+        <v>8.838421605381406</v>
+      </c>
+      <c r="Z26">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27">
+        <v>0.25</v>
+      </c>
+      <c r="B27">
+        <v>0.127637716152001</v>
+      </c>
+      <c r="C27">
+        <v>22.84992814887197</v>
+      </c>
+      <c r="D27">
+        <v>26.44492814887197</v>
+      </c>
+      <c r="E27">
+        <v>0.1049999999999995</v>
+      </c>
+      <c r="F27">
+        <v>6.965</v>
+      </c>
+      <c r="G27">
+        <v>3.37</v>
+      </c>
+      <c r="H27">
+        <v>21</v>
+      </c>
+      <c r="I27">
+        <v>0</v>
+      </c>
+      <c r="J27">
+        <v>3.716666666666667</v>
+      </c>
+      <c r="K27">
+        <v>0.8799999999999999</v>
+      </c>
+      <c r="L27">
+        <v>2.836666666666667</v>
+      </c>
+      <c r="M27">
+        <v>0.33432</v>
+      </c>
+      <c r="N27">
+        <v>2.502346666666667</v>
+      </c>
+      <c r="O27">
+        <v>0.5004693333333334</v>
+      </c>
+      <c r="P27">
+        <v>2.001877333333334</v>
+      </c>
+      <c r="Q27">
+        <v>2.881877333333334</v>
+      </c>
+      <c r="R27">
+        <v>0.3333333333333333</v>
+      </c>
+      <c r="S27">
+        <v>0.1573836215360014</v>
+      </c>
+      <c r="T27">
+        <v>1.317531192654598</v>
+      </c>
+      <c r="U27">
+        <v>0.048</v>
+      </c>
+      <c r="V27">
+        <v>0.2</v>
+      </c>
+      <c r="W27">
+        <v>0.0384</v>
+      </c>
+      <c r="X27" t="inlineStr">
+        <is>
+          <t>A1/A+</t>
+        </is>
+      </c>
+      <c r="Y27">
+        <v>8.484884741166148</v>
+      </c>
+      <c r="Z27">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28">
+        <v>0.26</v>
+      </c>
+      <c r="B28">
+        <v>0.1274464788548389</v>
+      </c>
+      <c r="C28">
+        <v>22.62837786644866</v>
+      </c>
+      <c r="D28">
+        <v>26.50197786644866</v>
+      </c>
+      <c r="E28">
+        <v>0.3835999999999995</v>
+      </c>
+      <c r="F28">
+        <v>7.2436</v>
+      </c>
+      <c r="G28">
+        <v>3.37</v>
+      </c>
+      <c r="H28">
+        <v>21</v>
+      </c>
+      <c r="I28">
+        <v>0</v>
+      </c>
+      <c r="J28">
+        <v>3.716666666666667</v>
+      </c>
+      <c r="K28">
+        <v>0.8799999999999999</v>
+      </c>
+      <c r="L28">
+        <v>2.836666666666667</v>
+      </c>
+      <c r="M28">
+        <v>0.3476928</v>
+      </c>
+      <c r="N28">
+        <v>2.488973866666667</v>
+      </c>
+      <c r="O28">
+        <v>0.4977947733333334</v>
+      </c>
+      <c r="P28">
+        <v>1.991179093333334</v>
+      </c>
+      <c r="Q28">
+        <v>2.871179093333334</v>
+      </c>
+      <c r="R28">
+        <v>0.3513513513513514</v>
+      </c>
+      <c r="S28">
+        <v>0.1587330795335661</v>
+      </c>
+      <c r="T28">
+        <v>1.332524435245262</v>
+      </c>
+      <c r="U28">
+        <v>0.048</v>
+      </c>
+      <c r="V28">
+        <v>0.2</v>
+      </c>
+      <c r="W28">
+        <v>0.0384</v>
+      </c>
+      <c r="X28" t="inlineStr">
+        <is>
+          <t>A1/A+</t>
+        </is>
+      </c>
+      <c r="Y28">
+        <v>8.158543020352067</v>
+      </c>
+      <c r="Z28">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29">
+        <v>0.27</v>
+      </c>
+      <c r="B29">
+        <v>0.1272552415576768</v>
+      </c>
+      <c r="C29">
+        <v>22.40707426321815</v>
+      </c>
+      <c r="D29">
+        <v>26.55927426321815</v>
+      </c>
+      <c r="E29">
+        <v>0.6622000000000003</v>
+      </c>
+      <c r="F29">
+        <v>7.522200000000001</v>
+      </c>
+      <c r="G29">
+        <v>3.37</v>
+      </c>
+      <c r="H29">
+        <v>21</v>
+      </c>
+      <c r="I29">
+        <v>0</v>
+      </c>
+      <c r="J29">
+        <v>3.716666666666667</v>
+      </c>
+      <c r="K29">
+        <v>0.8799999999999999</v>
+      </c>
+      <c r="L29">
+        <v>2.836666666666667</v>
+      </c>
+      <c r="M29">
+        <v>0.3610656</v>
+      </c>
+      <c r="N29">
+        <v>2.475601066666667</v>
+      </c>
+      <c r="O29">
+        <v>0.4951202133333334</v>
+      </c>
+      <c r="P29">
+        <v>1.980480853333334</v>
+      </c>
+      <c r="Q29">
+        <v>2.860480853333334</v>
+      </c>
+      <c r="R29">
+        <v>0.3698630136986302</v>
+      </c>
+      <c r="S29">
+        <v>0.1601195089831189</v>
+      </c>
+      <c r="T29">
+        <v>1.347928451605533</v>
+      </c>
+      <c r="U29">
+        <v>0.048</v>
+      </c>
+      <c r="V29">
+        <v>0.2</v>
+      </c>
+      <c r="W29">
+        <v>0.0384</v>
+      </c>
+      <c r="X29" t="inlineStr">
+        <is>
+          <t>A1/A+</t>
+        </is>
+      </c>
+      <c r="Y29">
+        <v>7.856374760339026</v>
+      </c>
+      <c r="Z29">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30">
+        <v>0.28</v>
+      </c>
+      <c r="B30">
+        <v>0.1274000042605147</v>
+      </c>
+      <c r="C30">
+        <v>22.08507931803901</v>
+      </c>
+      <c r="D30">
+        <v>26.51587931803902</v>
+      </c>
+      <c r="E30">
+        <v>0.9408000000000003</v>
+      </c>
+      <c r="F30">
+        <v>7.800800000000001</v>
+      </c>
+      <c r="G30">
+        <v>3.37</v>
+      </c>
+      <c r="H30">
+        <v>21</v>
+      </c>
+      <c r="I30">
+        <v>0</v>
+      </c>
+      <c r="J30">
+        <v>3.716666666666667</v>
+      </c>
+      <c r="K30">
+        <v>0.8799999999999999</v>
+      </c>
+      <c r="L30">
+        <v>2.836666666666667</v>
+      </c>
+      <c r="M30">
+        <v>0.3861396</v>
+      </c>
+      <c r="N30">
+        <v>2.450527066666667</v>
+      </c>
+      <c r="O30">
+        <v>0.4901054133333334</v>
+      </c>
+      <c r="P30">
+        <v>1.960421653333334</v>
+      </c>
+      <c r="Q30">
+        <v>2.840421653333333</v>
+      </c>
+      <c r="R30">
+        <v>0.388888888888889</v>
+      </c>
+      <c r="S30">
+        <v>0.161544450361826</v>
+      </c>
+      <c r="T30">
+        <v>1.363760357309145</v>
+      </c>
+      <c r="U30">
+        <v>0.0495</v>
+      </c>
+      <c r="V30">
+        <v>0.2</v>
+      </c>
+      <c r="W30">
+        <v>0.0396</v>
+      </c>
+      <c r="X30" t="inlineStr">
+        <is>
+          <t>A2/A</t>
+        </is>
+      </c>
+      <c r="Y30">
+        <v>7.346220555122207</v>
+      </c>
+      <c r="Z30">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31">
+        <v>0.29</v>
+      </c>
+      <c r="B31">
+        <v>0.1272207669633526</v>
+      </c>
+      <c r="C31">
+        <v>21.86022952519128</v>
+      </c>
+      <c r="D31">
+        <v>26.56962952519128</v>
+      </c>
+      <c r="E31">
+        <v>1.219399999999999</v>
+      </c>
+      <c r="F31">
+        <v>8.0794</v>
+      </c>
+      <c r="G31">
+        <v>3.37</v>
+      </c>
+      <c r="H31">
+        <v>21</v>
+      </c>
+      <c r="I31">
+        <v>0</v>
+      </c>
+      <c r="J31">
+        <v>3.716666666666667</v>
+      </c>
+      <c r="K31">
+        <v>0.8799999999999999</v>
+      </c>
+      <c r="L31">
+        <v>2.836666666666667</v>
+      </c>
+      <c r="M31">
+        <v>0.3999303</v>
+      </c>
+      <c r="N31">
+        <v>2.436736366666667</v>
+      </c>
+      <c r="O31">
+        <v>0.4873472733333334</v>
+      </c>
+      <c r="P31">
+        <v>1.949389093333334</v>
+      </c>
+      <c r="Q31">
+        <v>2.829389093333333</v>
+      </c>
+      <c r="R31">
+        <v>0.4084507042253521</v>
+      </c>
+      <c r="S31">
+        <v>0.1630095309342994</v>
+      </c>
+      <c r="T31">
+        <v>1.380038232187507</v>
+      </c>
+      <c r="U31">
+        <v>0.0495</v>
+      </c>
+      <c r="V31">
+        <v>0.2</v>
+      </c>
+      <c r="W31">
+        <v>0.0396</v>
+      </c>
+      <c r="X31" t="inlineStr">
+        <is>
+          <t>A2/A</t>
+        </is>
+      </c>
+      <c r="Y31">
+        <v>7.092902604945579</v>
+      </c>
+      <c r="Z31">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32">
+        <v>0.3</v>
+      </c>
+      <c r="B32">
+        <v>0.1270415296661905</v>
+      </c>
+      <c r="C32">
+        <v>21.63559808852771</v>
+      </c>
+      <c r="D32">
+        <v>26.62359808852771</v>
+      </c>
+      <c r="E32">
+        <v>1.497999999999998</v>
+      </c>
+      <c r="F32">
+        <v>8.357999999999999</v>
+      </c>
+      <c r="G32">
+        <v>3.37</v>
+      </c>
+      <c r="H32">
+        <v>21</v>
+      </c>
+      <c r="I32">
+        <v>0</v>
+      </c>
+      <c r="J32">
+        <v>3.716666666666667</v>
+      </c>
+      <c r="K32">
+        <v>0.8799999999999999</v>
+      </c>
+      <c r="L32">
+        <v>2.836666666666667</v>
+      </c>
+      <c r="M32">
+        <v>0.4137209999999999</v>
+      </c>
+      <c r="N32">
+        <v>2.422945666666667</v>
+      </c>
+      <c r="O32">
+        <v>0.4845891333333334</v>
+      </c>
+      <c r="P32">
+        <v>1.938356533333334</v>
+      </c>
+      <c r="Q32">
+        <v>2.818356533333334</v>
+      </c>
+      <c r="R32">
+        <v>0.4285714285714286</v>
+      </c>
+      <c r="S32">
+        <v>0.1645164709517007</v>
+      </c>
+      <c r="T32">
+        <v>1.396781189205251</v>
+      </c>
+      <c r="U32">
+        <v>0.0495</v>
+      </c>
+      <c r="V32">
+        <v>0.2</v>
+      </c>
+      <c r="W32">
+        <v>0.0396</v>
+      </c>
+      <c r="X32" t="inlineStr">
+        <is>
+          <t>A2/A</t>
+        </is>
+      </c>
+      <c r="Y32">
+        <v>6.856472518114061</v>
+      </c>
+      <c r="Z32">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33">
+        <v>0.31</v>
+      </c>
+      <c r="B33">
+        <v>0.1268622923690284</v>
+      </c>
+      <c r="C33">
+        <v>21.41118634133995</v>
+      </c>
+      <c r="D33">
+        <v>26.67778634133995</v>
+      </c>
+      <c r="E33">
+        <v>1.776599999999999</v>
+      </c>
+      <c r="F33">
+        <v>8.6366</v>
+      </c>
+      <c r="G33">
+        <v>3.37</v>
+      </c>
+      <c r="H33">
+        <v>21</v>
+      </c>
+      <c r="I33">
+        <v>0</v>
+      </c>
+      <c r="J33">
+        <v>3.716666666666667</v>
+      </c>
+      <c r="K33">
+        <v>0.8799999999999999</v>
+      </c>
+      <c r="L33">
+        <v>2.836666666666667</v>
+      </c>
+      <c r="M33">
+        <v>0.4275117</v>
+      </c>
+      <c r="N33">
+        <v>2.409154966666667</v>
+      </c>
+      <c r="O33">
+        <v>0.4818309933333333</v>
+      </c>
+      <c r="P33">
+        <v>1.927323973333333</v>
+      </c>
+      <c r="Q33">
+        <v>2.807323973333333</v>
+      </c>
+      <c r="R33">
+        <v>0.4492753623188406</v>
+      </c>
+      <c r="S33">
+        <v>0.1660670903898962</v>
+      </c>
+      <c r="T33">
+        <v>1.414009449324958</v>
+      </c>
+      <c r="U33">
+        <v>0.0495</v>
+      </c>
+      <c r="V33">
+        <v>0.2</v>
+      </c>
+      <c r="W33">
+        <v>0.0396</v>
+      </c>
+      <c r="X33" t="inlineStr">
+        <is>
+          <t>A2/A</t>
+        </is>
+      </c>
+      <c r="Y33">
+        <v>6.635295985271671</v>
+      </c>
+      <c r="Z33">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34">
+        <v>0.32</v>
+      </c>
+      <c r="B34">
+        <v>0.1266830550718663</v>
+      </c>
+      <c r="C34">
+        <v>21.1869956277966</v>
+      </c>
+      <c r="D34">
+        <v>26.7321956277966</v>
+      </c>
+      <c r="E34">
+        <v>2.0552</v>
+      </c>
+      <c r="F34">
+        <v>8.9152</v>
+      </c>
+      <c r="G34">
+        <v>3.37</v>
+      </c>
+      <c r="H34">
+        <v>21</v>
+      </c>
+      <c r="I34">
+        <v>0</v>
+      </c>
+      <c r="J34">
+        <v>3.716666666666667</v>
+      </c>
+      <c r="K34">
+        <v>0.8799999999999999</v>
+      </c>
+      <c r="L34">
+        <v>2.836666666666667</v>
+      </c>
+      <c r="M34">
+        <v>0.4413024</v>
+      </c>
+      <c r="N34">
+        <v>2.395364266666667</v>
+      </c>
+      <c r="O34">
+        <v>0.4790728533333334</v>
+      </c>
+      <c r="P34">
+        <v>1.916291413333334</v>
+      </c>
+      <c r="Q34">
+        <v>2.796291413333333</v>
+      </c>
+      <c r="R34">
+        <v>0.4705882352941177</v>
+      </c>
+      <c r="S34">
+        <v>0.1676633162821563</v>
+      </c>
+      <c r="T34">
+        <v>1.431744422977597</v>
+      </c>
+      <c r="U34">
+        <v>0.0495</v>
+      </c>
+      <c r="V34">
+        <v>0.2</v>
+      </c>
+      <c r="W34">
+        <v>0.0396</v>
+      </c>
+      <c r="X34" t="inlineStr">
+        <is>
+          <t>A2/A</t>
+        </is>
+      </c>
+      <c r="Y34">
+        <v>6.427942985731931</v>
+      </c>
+      <c r="Z34">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35">
+        <v>0.33</v>
+      </c>
+      <c r="B35">
+        <v>0.1265038177747042</v>
+      </c>
+      <c r="C35">
+        <v>20.96302730305437</v>
+      </c>
+      <c r="D35">
+        <v>26.78682730305437</v>
+      </c>
+      <c r="E35">
+        <v>2.333799999999999</v>
+      </c>
+      <c r="F35">
+        <v>9.1938</v>
+      </c>
+      <c r="G35">
+        <v>3.37</v>
+      </c>
+      <c r="H35">
+        <v>21</v>
+      </c>
+      <c r="I35">
+        <v>0</v>
+      </c>
+      <c r="J35">
+        <v>3.716666666666667</v>
+      </c>
+      <c r="K35">
+        <v>0.8799999999999999</v>
+      </c>
+      <c r="L35">
+        <v>2.836666666666667</v>
+      </c>
+      <c r="M35">
+        <v>0.4550931</v>
+      </c>
+      <c r="N35">
+        <v>2.381573566666667</v>
+      </c>
+      <c r="O35">
+        <v>0.4763147133333334</v>
+      </c>
+      <c r="P35">
+        <v>1.905258853333333</v>
+      </c>
+      <c r="Q35">
+        <v>2.785258853333334</v>
+      </c>
+      <c r="R35">
+        <v>0.4925373134328359</v>
+      </c>
+      <c r="S35">
+        <v>0.1693071907085137</v>
+      </c>
+      <c r="T35">
+        <v>1.450008798828823</v>
+      </c>
+      <c r="U35">
+        <v>0.0495</v>
+      </c>
+      <c r="V35">
+        <v>0.2</v>
+      </c>
+      <c r="W35">
+        <v>0.0396</v>
+      </c>
+      <c r="X35" t="inlineStr">
+        <is>
+          <t>A2/A</t>
+        </is>
+      </c>
+      <c r="Y35">
+        <v>6.233156834649145</v>
+      </c>
+      <c r="Z35">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36">
+        <v>0.34</v>
+      </c>
+      <c r="B36">
+        <v>0.126705380477542</v>
+      </c>
+      <c r="C36">
+        <v>20.62300642890168</v>
+      </c>
+      <c r="D36">
+        <v>26.72540642890168</v>
+      </c>
+      <c r="E36">
+        <v>2.6124</v>
+      </c>
+      <c r="F36">
+        <v>9.4724</v>
+      </c>
+      <c r="G36">
+        <v>3.37</v>
+      </c>
+      <c r="H36">
+        <v>21</v>
+      </c>
+      <c r="I36">
+        <v>0</v>
+      </c>
+      <c r="J36">
+        <v>3.716666666666667</v>
+      </c>
+      <c r="K36">
+        <v>0.8799999999999999</v>
+      </c>
+      <c r="L36">
+        <v>2.836666666666667</v>
+      </c>
+      <c r="M36">
+        <v>0.48214516</v>
+      </c>
+      <c r="N36">
+        <v>2.354521506666667</v>
+      </c>
+      <c r="O36">
+        <v>0.4709043013333334</v>
+      </c>
+      <c r="P36">
+        <v>1.883617205333334</v>
+      </c>
+      <c r="Q36">
+        <v>2.763617205333333</v>
+      </c>
+      <c r="R36">
+        <v>0.5151515151515152</v>
+      </c>
+      <c r="S36">
+        <v>0.1710008795114274</v>
+      </c>
+      <c r="T36">
+        <v>1.468826640614935</v>
+      </c>
+      <c r="U36">
+        <v>0.0509</v>
+      </c>
+      <c r="V36">
+        <v>0.2</v>
+      </c>
+      <c r="W36">
+        <v>0.04072000000000001</v>
+      </c>
+      <c r="X36" t="inlineStr">
+        <is>
+          <t>A3/A-</t>
+        </is>
+      </c>
+      <c r="Y36">
+        <v>5.8834286891248</v>
+      </c>
+      <c r="Z36">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37">
+        <v>0.35</v>
+      </c>
+      <c r="B37">
+        <v>0.12653734318038</v>
+      </c>
+      <c r="C37">
+        <v>20.39559176115682</v>
+      </c>
+      <c r="D37">
+        <v>26.77659176115682</v>
+      </c>
+      <c r="E37">
+        <v>2.891000000000001</v>
+      </c>
+      <c r="F37">
+        <v>9.751000000000001</v>
+      </c>
+      <c r="G37">
+        <v>3.37</v>
+      </c>
+      <c r="H37">
+        <v>21</v>
+      </c>
+      <c r="I37">
+        <v>0</v>
+      </c>
+      <c r="J37">
+        <v>3.716666666666667</v>
+      </c>
+      <c r="K37">
+        <v>0.8799999999999999</v>
+      </c>
+      <c r="L37">
+        <v>2.836666666666667</v>
+      </c>
+      <c r="M37">
+        <v>0.4963259000000001</v>
+      </c>
+      <c r="N37">
+        <v>2.340340766666667</v>
+      </c>
+      <c r="O37">
+        <v>0.4680681533333334</v>
+      </c>
+      <c r="P37">
+        <v>1.872272613333334</v>
+      </c>
+      <c r="Q37">
+        <v>2.752272613333334</v>
+      </c>
+      <c r="R37">
+        <v>0.5384615384615385</v>
+      </c>
+      <c r="S37">
+        <v>0.1727466818159692</v>
+      </c>
+      <c r="T37">
+        <v>1.488223492917542</v>
+      </c>
+      <c r="U37">
+        <v>0.0509</v>
+      </c>
+      <c r="V37">
+        <v>0.2</v>
+      </c>
+      <c r="W37">
+        <v>0.04072000000000001</v>
+      </c>
+      <c r="X37" t="inlineStr">
+        <is>
+          <t>A3/A-</t>
+        </is>
+      </c>
+      <c r="Y37">
+        <v>5.715330726578376</v>
+      </c>
+      <c r="Z37">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38">
+        <v>0.36</v>
+      </c>
+      <c r="B38">
+        <v>0.1263693058832178</v>
+      </c>
+      <c r="C38">
+        <v>20.16837353313019</v>
+      </c>
+      <c r="D38">
+        <v>26.82797353313019</v>
+      </c>
+      <c r="E38">
+        <v>3.1696</v>
+      </c>
+      <c r="F38">
+        <v>10.0296</v>
+      </c>
+      <c r="G38">
+        <v>3.37</v>
+      </c>
+      <c r="H38">
+        <v>21</v>
+      </c>
+      <c r="I38">
+        <v>0</v>
+      </c>
+      <c r="J38">
+        <v>3.716666666666667</v>
+      </c>
+      <c r="K38">
+        <v>0.8799999999999999</v>
+      </c>
+      <c r="L38">
+        <v>2.836666666666667</v>
+      </c>
+      <c r="M38">
+        <v>0.51050664</v>
+      </c>
+      <c r="N38">
+        <v>2.326160026666667</v>
+      </c>
+      <c r="O38">
+        <v>0.4652320053333334</v>
+      </c>
+      <c r="P38">
+        <v>1.860928021333333</v>
+      </c>
+      <c r="Q38">
+        <v>2.740928021333334</v>
+      </c>
+      <c r="R38">
+        <v>0.5625</v>
+      </c>
+      <c r="S38">
+        <v>0.1745470404425279</v>
+      </c>
+      <c r="T38">
+        <v>1.508226496854606</v>
+      </c>
+      <c r="U38">
+        <v>0.0509</v>
+      </c>
+      <c r="V38">
+        <v>0.2</v>
+      </c>
+      <c r="W38">
+        <v>0.04072000000000001</v>
+      </c>
+      <c r="X38" t="inlineStr">
+        <is>
+          <t>A3/A-</t>
+        </is>
+      </c>
+      <c r="Y38">
+        <v>5.556571539728978</v>
+      </c>
+      <c r="Z38">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39">
+        <v>0.37</v>
+      </c>
+      <c r="B39">
+        <v>0.1262012685860557</v>
+      </c>
+      <c r="C39">
+        <v>19.94135287784422</v>
+      </c>
+      <c r="D39">
+        <v>26.87955287784422</v>
+      </c>
+      <c r="E39">
+        <v>3.448199999999999</v>
+      </c>
+      <c r="F39">
+        <v>10.3082</v>
+      </c>
+      <c r="G39">
+        <v>3.37</v>
+      </c>
+      <c r="H39">
+        <v>21</v>
+      </c>
+      <c r="I39">
+        <v>0</v>
+      </c>
+      <c r="J39">
+        <v>3.716666666666667</v>
+      </c>
+      <c r="K39">
+        <v>0.8799999999999999</v>
+      </c>
+      <c r="L39">
+        <v>2.836666666666667</v>
+      </c>
+      <c r="M39">
+        <v>0.5246873799999999</v>
+      </c>
+      <c r="N39">
+        <v>2.311979286666667</v>
+      </c>
+      <c r="O39">
+        <v>0.4623958573333334</v>
+      </c>
+      <c r="P39">
+        <v>1.849583429333334</v>
+      </c>
+      <c r="Q39">
+        <v>2.729583429333333</v>
+      </c>
+      <c r="R39">
+        <v>0.5873015873015873</v>
+      </c>
+      <c r="S39">
+        <v>0.1764045533111996</v>
+      </c>
+      <c r="T39">
+        <v>1.528864516789672</v>
+      </c>
+      <c r="U39">
+        <v>0.0509</v>
+      </c>
+      <c r="V39">
+        <v>0.2</v>
+      </c>
+      <c r="W39">
+        <v>0.04072000000000001</v>
+      </c>
+      <c r="X39" t="inlineStr">
+        <is>
+          <t>A3/A-</t>
+        </is>
+      </c>
+      <c r="Y39">
+        <v>5.406393930547114</v>
+      </c>
+      <c r="Z39">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40">
+        <v>0.38</v>
+      </c>
+      <c r="B40">
+        <v>0.1260332312888936</v>
+      </c>
+      <c r="C40">
+        <v>19.71453093705151</v>
+      </c>
+      <c r="D40">
+        <v>26.93133093705151</v>
+      </c>
+      <c r="E40">
+        <v>3.7268</v>
+      </c>
+      <c r="F40">
+        <v>10.5868</v>
+      </c>
+      <c r="G40">
+        <v>3.37</v>
+      </c>
+      <c r="H40">
+        <v>21</v>
+      </c>
+      <c r="I40">
+        <v>0</v>
+      </c>
+      <c r="J40">
+        <v>3.716666666666667</v>
+      </c>
+      <c r="K40">
+        <v>0.8799999999999999</v>
+      </c>
+      <c r="L40">
+        <v>2.836666666666667</v>
+      </c>
+      <c r="M40">
+        <v>0.5388681200000001</v>
+      </c>
+      <c r="N40">
+        <v>2.297798546666667</v>
+      </c>
+      <c r="O40">
+        <v>0.4595597093333334</v>
+      </c>
+      <c r="P40">
+        <v>1.838238837333333</v>
+      </c>
+      <c r="Q40">
+        <v>2.718238837333333</v>
+      </c>
+      <c r="R40">
+        <v>0.6129032258064516</v>
+      </c>
+      <c r="S40">
+        <v>0.1783219859498284</v>
+      </c>
+      <c r="T40">
+        <v>1.550168279303288</v>
+      </c>
+      <c r="U40">
+        <v>0.0509</v>
+      </c>
+      <c r="V40">
+        <v>0.2</v>
+      </c>
+      <c r="W40">
+        <v>0.04072000000000001</v>
+      </c>
+      <c r="X40" t="inlineStr">
+        <is>
+          <t>A3/A-</t>
+        </is>
+      </c>
+      <c r="Y40">
+        <v>5.264120406059031</v>
+      </c>
+      <c r="Z40">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41">
+        <v>0.39</v>
+      </c>
+      <c r="B41">
+        <v>0.1258651939917315</v>
+      </c>
+      <c r="C41">
+        <v>19.48790886131904</v>
+      </c>
+      <c r="D41">
+        <v>26.98330886131904</v>
+      </c>
+      <c r="E41">
+        <v>4.005399999999999</v>
+      </c>
+      <c r="F41">
+        <v>10.8654</v>
+      </c>
+      <c r="G41">
+        <v>3.37</v>
+      </c>
+      <c r="H41">
+        <v>21</v>
+      </c>
+      <c r="I41">
+        <v>0</v>
+      </c>
+      <c r="J41">
+        <v>3.716666666666667</v>
+      </c>
+      <c r="K41">
+        <v>0.8799999999999999</v>
+      </c>
+      <c r="L41">
+        <v>2.836666666666667</v>
+      </c>
+      <c r="M41">
+        <v>0.55304886</v>
+      </c>
+      <c r="N41">
+        <v>2.283617806666667</v>
+      </c>
+      <c r="O41">
+        <v>0.4567235613333334</v>
+      </c>
+      <c r="P41">
+        <v>1.826894245333333</v>
+      </c>
+      <c r="Q41">
+        <v>2.706894245333333</v>
+      </c>
+      <c r="R41">
+        <v>0.639344262295082</v>
+      </c>
+      <c r="S41">
+        <v>0.1803022852323468</v>
+      </c>
+      <c r="T41">
+        <v>1.572170525833744</v>
+      </c>
+      <c r="U41">
+        <v>0.0509</v>
+      </c>
+      <c r="V41">
+        <v>0.2</v>
+      </c>
+      <c r="W41">
+        <v>0.04072000000000001</v>
+      </c>
+      <c r="X41" t="inlineStr">
+        <is>
+          <t>A3/A-</t>
+        </is>
+      </c>
+      <c r="Y41">
+        <v>5.129142959749825</v>
+      </c>
+      <c r="Z41">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42">
+        <v>0.4</v>
+      </c>
+      <c r="B42">
+        <v>0.1256971566945694</v>
+      </c>
+      <c r="C42">
+        <v>19.26148781011345</v>
+      </c>
+      <c r="D42">
+        <v>27.03548781011345</v>
+      </c>
+      <c r="E42">
+        <v>4.284</v>
+      </c>
+      <c r="F42">
+        <v>11.144</v>
+      </c>
+      <c r="G42">
+        <v>3.37</v>
+      </c>
+      <c r="H42">
+        <v>21</v>
+      </c>
+      <c r="I42">
+        <v>0</v>
+      </c>
+      <c r="J42">
+        <v>3.716666666666667</v>
+      </c>
+      <c r="K42">
+        <v>0.8799999999999999</v>
+      </c>
+      <c r="L42">
+        <v>2.836666666666667</v>
+      </c>
+      <c r="M42">
+        <v>0.5672296</v>
+      </c>
+      <c r="N42">
+        <v>2.269437066666667</v>
+      </c>
+      <c r="O42">
+        <v>0.4538874133333334</v>
+      </c>
+      <c r="P42">
+        <v>1.815549653333334</v>
+      </c>
+      <c r="Q42">
+        <v>2.695549653333333</v>
+      </c>
+      <c r="R42">
+        <v>0.6666666666666667</v>
+      </c>
+      <c r="S42">
+        <v>0.182348594490949</v>
+      </c>
+      <c r="T42">
+        <v>1.594906180581882</v>
+      </c>
+      <c r="U42">
+        <v>0.0509</v>
+      </c>
+      <c r="V42">
+        <v>0.2</v>
+      </c>
+      <c r="W42">
+        <v>0.04072000000000001</v>
+      </c>
+      <c r="X42" t="inlineStr">
+        <is>
+          <t>A3/A-</t>
+        </is>
+      </c>
+      <c r="Y42">
+        <v>5.000914385756079</v>
+      </c>
+      <c r="Z42">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43">
+        <v>0.41</v>
+      </c>
+      <c r="B43">
+        <v>0.1255291193974073</v>
+      </c>
+      <c r="C43">
+        <v>19.03526895188724</v>
+      </c>
+      <c r="D43">
+        <v>27.08786895188724</v>
+      </c>
+      <c r="E43">
+        <v>4.562600000000001</v>
+      </c>
+      <c r="F43">
+        <v>11.4226</v>
+      </c>
+      <c r="G43">
+        <v>3.37</v>
+      </c>
+      <c r="H43">
+        <v>21</v>
+      </c>
+      <c r="I43">
+        <v>0</v>
+      </c>
+      <c r="J43">
+        <v>3.716666666666667</v>
+      </c>
+      <c r="K43">
+        <v>0.8799999999999999</v>
+      </c>
+      <c r="L43">
+        <v>2.836666666666667</v>
+      </c>
+      <c r="M43">
+        <v>0.58141034</v>
+      </c>
+      <c r="N43">
+        <v>2.255256326666667</v>
+      </c>
+      <c r="O43">
+        <v>0.4510512653333334</v>
+      </c>
+      <c r="P43">
+        <v>1.804205061333333</v>
+      </c>
+      <c r="Q43">
+        <v>2.684205061333333</v>
+      </c>
+      <c r="R43">
+        <v>0.6949152542372882</v>
+      </c>
+      <c r="S43">
+        <v>0.1844642701650971</v>
+      </c>
+      <c r="T43">
+        <v>1.618412535490974</v>
+      </c>
+      <c r="U43">
+        <v>0.0509</v>
+      </c>
+      <c r="V43">
+        <v>0.2</v>
+      </c>
+      <c r="W43">
+        <v>0.04072000000000001</v>
+      </c>
+      <c r="X43" t="inlineStr">
+        <is>
+          <t>A3/A-</t>
+        </is>
+      </c>
+      <c r="Y43">
+        <v>4.878940864152272</v>
+      </c>
+      <c r="Z43">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44">
+        <v>0.42</v>
+      </c>
+      <c r="B44">
+        <v>0.1253610821002452</v>
+      </c>
+      <c r="C44">
+        <v>18.80925346416591</v>
+      </c>
+      <c r="D44">
+        <v>27.14045346416591</v>
+      </c>
+      <c r="E44">
+        <v>4.8412</v>
+      </c>
+      <c r="F44">
+        <v>11.7012</v>
+      </c>
+      <c r="G44">
+        <v>3.37</v>
+      </c>
+      <c r="H44">
+        <v>21</v>
+      </c>
+      <c r="I44">
+        <v>0</v>
+      </c>
+      <c r="J44">
+        <v>3.716666666666667</v>
+      </c>
+      <c r="K44">
+        <v>0.8799999999999999</v>
+      </c>
+      <c r="L44">
+        <v>2.836666666666667</v>
+      </c>
+      <c r="M44">
+        <v>0.5955910800000001</v>
+      </c>
+      <c r="N44">
+        <v>2.241075586666667</v>
+      </c>
+      <c r="O44">
+        <v>0.4482151173333334</v>
+      </c>
+      <c r="P44">
+        <v>1.792860469333333</v>
+      </c>
+      <c r="Q44">
+        <v>2.672860469333333</v>
+      </c>
+      <c r="R44">
+        <v>0.7241379310344827</v>
+      </c>
+      <c r="S44">
+        <v>0.1866529001728366</v>
+      </c>
+      <c r="T44">
+        <v>1.642729454362448</v>
+      </c>
+      <c r="U44">
+        <v>0.0509</v>
+      </c>
+      <c r="V44">
+        <v>0.2</v>
+      </c>
+      <c r="W44">
+        <v>0.04072000000000001</v>
+      </c>
+      <c r="X44" t="inlineStr">
+        <is>
+          <t>A3/A-</t>
+        </is>
+      </c>
+      <c r="Y44">
+        <v>4.762775605481981</v>
+      </c>
+      <c r="Z44">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45">
+        <v>0.43</v>
+      </c>
+      <c r="B45">
+        <v>0.1251930448030831</v>
+      </c>
+      <c r="C45">
+        <v>18.58344253363634</v>
+      </c>
+      <c r="D45">
+        <v>27.19324253363634</v>
+      </c>
+      <c r="E45">
+        <v>5.119799999999999</v>
+      </c>
+      <c r="F45">
+        <v>11.9798</v>
+      </c>
+      <c r="G45">
+        <v>3.37</v>
+      </c>
+      <c r="H45">
+        <v>21</v>
+      </c>
+      <c r="I45">
+        <v>0</v>
+      </c>
+      <c r="J45">
+        <v>3.716666666666667</v>
+      </c>
+      <c r="K45">
+        <v>0.8799999999999999</v>
+      </c>
+      <c r="L45">
+        <v>2.836666666666667</v>
+      </c>
+      <c r="M45">
+        <v>0.60977182</v>
+      </c>
+      <c r="N45">
+        <v>2.226894846666667</v>
+      </c>
+      <c r="O45">
+        <v>0.4453789693333334</v>
+      </c>
+      <c r="P45">
+        <v>1.781515877333334</v>
+      </c>
+      <c r="Q45">
+        <v>2.661515877333334</v>
+      </c>
+      <c r="R45">
+        <v>0.7543859649122806</v>
+      </c>
+      <c r="S45">
+        <v>0.1889183242159353</v>
+      </c>
+      <c r="T45">
+        <v>1.667899598457483</v>
+      </c>
+      <c r="U45">
+        <v>0.0509</v>
+      </c>
+      <c r="V45">
+        <v>0.2</v>
+      </c>
+      <c r="W45">
+        <v>0.04072000000000001</v>
+      </c>
+      <c r="X45" t="inlineStr">
+        <is>
+          <t>A3/A-</t>
+        </is>
+      </c>
+      <c r="Y45">
+        <v>4.65201338209868</v>
+      </c>
+      <c r="Z45">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46">
+        <v>0.44</v>
+      </c>
+      <c r="B46">
+        <v>0.125025007505921</v>
+      </c>
+      <c r="C46">
+        <v>18.35783735623596</v>
+      </c>
+      <c r="D46">
+        <v>27.24623735623596</v>
+      </c>
+      <c r="E46">
+        <v>5.3984</v>
+      </c>
+      <c r="F46">
+        <v>12.2584</v>
+      </c>
+      <c r="G46">
+        <v>3.37</v>
+      </c>
+      <c r="H46">
+        <v>21</v>
+      </c>
+      <c r="I46">
+        <v>0</v>
+      </c>
+      <c r="J46">
+        <v>3.716666666666667</v>
+      </c>
+      <c r="K46">
+        <v>0.8799999999999999</v>
+      </c>
+      <c r="L46">
+        <v>2.836666666666667</v>
+      </c>
+      <c r="M46">
+        <v>0.62395256</v>
+      </c>
+      <c r="N46">
+        <v>2.212714106666667</v>
+      </c>
+      <c r="O46">
+        <v>0.4425428213333333</v>
+      </c>
+      <c r="P46">
+        <v>1.770171285333333</v>
+      </c>
+      <c r="Q46">
+        <v>2.650171285333333</v>
+      </c>
+      <c r="R46">
+        <v>0.7857142857142857</v>
+      </c>
+      <c r="S46">
+        <v>0.1912646562605732</v>
+      </c>
+      <c r="T46">
+        <v>1.693968676270198</v>
+      </c>
+      <c r="U46">
+        <v>0.0509</v>
+      </c>
+      <c r="V46">
+        <v>0.2</v>
+      </c>
+      <c r="W46">
+        <v>0.04072000000000001</v>
+      </c>
+      <c r="X46" t="inlineStr">
+        <is>
+          <t>A3/A-</t>
+        </is>
+      </c>
+      <c r="Y46">
+        <v>4.5462858052328</v>
+      </c>
+      <c r="Z46">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47">
+        <v>0.45</v>
+      </c>
+      <c r="B47">
+        <v>0.1257929702087589</v>
+      </c>
+      <c r="C47">
+        <v>17.83871109265345</v>
+      </c>
+      <c r="D47">
+        <v>27.00571109265345</v>
+      </c>
+      <c r="E47">
+        <v>5.677</v>
+      </c>
+      <c r="F47">
+        <v>12.537</v>
+      </c>
+      <c r="G47">
+        <v>3.37</v>
+      </c>
+      <c r="H47">
+        <v>21</v>
+      </c>
+      <c r="I47">
+        <v>0</v>
+      </c>
+      <c r="J47">
+        <v>3.716666666666667</v>
+      </c>
+      <c r="K47">
+        <v>0.8799999999999999</v>
+      </c>
+      <c r="L47">
+        <v>2.836666666666667</v>
+      </c>
+      <c r="M47">
+        <v>0.6707295</v>
+      </c>
+      <c r="N47">
+        <v>2.165937166666667</v>
+      </c>
+      <c r="O47">
+        <v>0.4331874333333334</v>
+      </c>
+      <c r="P47">
+        <v>1.732749733333333</v>
+      </c>
+      <c r="Q47">
+        <v>2.612749733333333</v>
+      </c>
+      <c r="R47">
+        <v>0.8181818181818181</v>
+      </c>
+      <c r="S47">
+        <v>0.1936963094704707</v>
+      </c>
+      <c r="T47">
+        <v>1.720985720548829</v>
+      </c>
+      <c r="U47">
+        <v>0.0535</v>
+      </c>
+      <c r="V47">
+        <v>0.2</v>
+      </c>
+      <c r="W47">
+        <v>0.0428</v>
+      </c>
+      <c r="X47" t="inlineStr">
+        <is>
+          <t>Baa2/BBB</t>
+        </is>
+      </c>
+      <c r="Y47">
+        <v>4.229226039210541</v>
+      </c>
+      <c r="Z47">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48">
+        <v>0.46</v>
+      </c>
+      <c r="B48">
+        <v>0.1256457329115968</v>
+      </c>
+      <c r="C48">
+        <v>17.60589627720902</v>
+      </c>
+      <c r="D48">
+        <v>27.05149627720902</v>
+      </c>
+      <c r="E48">
+        <v>5.9556</v>
+      </c>
+      <c r="F48">
+        <v>12.8156</v>
+      </c>
+      <c r="G48">
+        <v>3.37</v>
+      </c>
+      <c r="H48">
+        <v>21</v>
+      </c>
+      <c r="I48">
+        <v>0</v>
+      </c>
+      <c r="J48">
+        <v>3.716666666666667</v>
+      </c>
+      <c r="K48">
+        <v>0.8799999999999999</v>
+      </c>
+      <c r="L48">
+        <v>2.836666666666667</v>
+      </c>
+      <c r="M48">
+        <v>0.6856346</v>
+      </c>
+      <c r="N48">
+        <v>2.151032066666667</v>
+      </c>
+      <c r="O48">
+        <v>0.4302064133333334</v>
+      </c>
+      <c r="P48">
+        <v>1.720825653333333</v>
+      </c>
+      <c r="Q48">
+        <v>2.600825653333333</v>
+      </c>
+      <c r="R48">
+        <v>0.8518518518518519</v>
+      </c>
+      <c r="S48">
+        <v>0.1962180239103644</v>
+      </c>
+      <c r="T48">
+        <v>1.74900339609704</v>
+      </c>
+      <c r="U48">
+        <v>0.0535</v>
+      </c>
+      <c r="V48">
+        <v>0.2</v>
+      </c>
+      <c r="W48">
+        <v>0.0428</v>
+      </c>
+      <c r="X48" t="inlineStr">
+        <is>
+          <t>Baa2/BBB</t>
+        </is>
+      </c>
+      <c r="Y48">
+        <v>4.137286342705965</v>
+      </c>
+      <c r="Z48">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49">
+        <v>0.47</v>
+      </c>
+      <c r="B49">
+        <v>0.1254984956144347</v>
+      </c>
+      <c r="C49">
+        <v>17.37323697280956</v>
+      </c>
+      <c r="D49">
+        <v>27.09743697280956</v>
+      </c>
+      <c r="E49">
+        <v>6.2342</v>
+      </c>
+      <c r="F49">
+        <v>13.0942</v>
+      </c>
+      <c r="G49">
+        <v>3.37</v>
+      </c>
+      <c r="H49">
+        <v>21</v>
+      </c>
+      <c r="I49">
+        <v>0</v>
+      </c>
+      <c r="J49">
+        <v>3.716666666666667</v>
+      </c>
+      <c r="K49">
+        <v>0.8799999999999999</v>
+      </c>
+      <c r="L49">
+        <v>2.836666666666667</v>
+      </c>
+      <c r="M49">
+        <v>0.7005397</v>
+      </c>
+      <c r="N49">
+        <v>2.136126966666667</v>
+      </c>
+      <c r="O49">
+        <v>0.4272253933333334</v>
+      </c>
+      <c r="P49">
+        <v>1.708901573333333</v>
+      </c>
+      <c r="Q49">
+        <v>2.588901573333333</v>
+      </c>
+      <c r="R49">
+        <v>0.8867924528301887</v>
+      </c>
+      <c r="S49">
+        <v>0.1988348973857258</v>
+      </c>
+      <c r="T49">
+        <v>1.778078342420654</v>
+      </c>
+      <c r="U49">
+        <v>0.0535</v>
+      </c>
+      <c r="V49">
+        <v>0.2</v>
+      </c>
+      <c r="W49">
+        <v>0.0428</v>
+      </c>
+      <c r="X49" t="inlineStr">
+        <is>
+          <t>Baa2/BBB</t>
+        </is>
+      </c>
+      <c r="Y49">
+        <v>4.04925897371222</v>
+      </c>
+      <c r="Z49">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50">
+        <v>0.48</v>
+      </c>
+      <c r="B50">
+        <v>0.1263880583172726</v>
+      </c>
+      <c r="C50">
+        <v>16.81942971583172</v>
+      </c>
+      <c r="D50">
+        <v>26.82222971583172</v>
+      </c>
+      <c r="E50">
+        <v>6.512799999999999</v>
+      </c>
+      <c r="F50">
+        <v>13.3728</v>
+      </c>
+      <c r="G50">
+        <v>3.37</v>
+      </c>
+      <c r="H50">
+        <v>21</v>
+      </c>
+      <c r="I50">
+        <v>0</v>
+      </c>
+      <c r="J50">
+        <v>3.716666666666667</v>
+      </c>
+      <c r="K50">
+        <v>0.8799999999999999</v>
+      </c>
+      <c r="L50">
+        <v>2.836666666666667</v>
+      </c>
+      <c r="M50">
+        <v>0.75155136</v>
+      </c>
+      <c r="N50">
+        <v>2.085115306666667</v>
+      </c>
+      <c r="O50">
+        <v>0.4170230613333334</v>
+      </c>
+      <c r="P50">
+        <v>1.668092245333333</v>
+      </c>
+      <c r="Q50">
+        <v>2.548092245333333</v>
+      </c>
+      <c r="R50">
+        <v>0.923076923076923</v>
+      </c>
+      <c r="S50">
+        <v>0.2015524198409088</v>
+      </c>
+      <c r="T50">
+        <v>1.808271555910562</v>
+      </c>
+      <c r="U50">
+        <v>0.0562</v>
+      </c>
+      <c r="V50">
+        <v>0.2</v>
+      </c>
+      <c r="W50">
+        <v>0.04496</v>
+      </c>
+      <c r="X50" t="inlineStr">
+        <is>
+          <t>Ba1/BB+</t>
+        </is>
+      </c>
+      <c r="Y50">
+        <v>3.774414920447575</v>
+      </c>
+      <c r="Z50">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51">
+        <v>0.49</v>
+      </c>
+      <c r="B51">
+        <v>0.1262624210201105</v>
+      </c>
+      <c r="C51">
+        <v>16.57935909114577</v>
+      </c>
+      <c r="D51">
+        <v>26.86075909114577</v>
+      </c>
+      <c r="E51">
+        <v>6.791399999999999</v>
+      </c>
+      <c r="F51">
+        <v>13.6514</v>
+      </c>
+      <c r="G51">
+        <v>3.37</v>
+      </c>
+      <c r="H51">
+        <v>21</v>
+      </c>
+      <c r="I51">
+        <v>0</v>
+      </c>
+      <c r="J51">
+        <v>3.716666666666667</v>
+      </c>
+      <c r="K51">
+        <v>0.8799999999999999</v>
+      </c>
+      <c r="L51">
+        <v>2.836666666666667</v>
+      </c>
+      <c r="M51">
+        <v>0.76720868</v>
+      </c>
+      <c r="N51">
+        <v>2.069457986666667</v>
+      </c>
+      <c r="O51">
+        <v>0.4138915973333334</v>
+      </c>
+      <c r="P51">
+        <v>1.655566389333333</v>
+      </c>
+      <c r="Q51">
+        <v>2.535566389333333</v>
+      </c>
+      <c r="R51">
+        <v>0.9607843137254901</v>
+      </c>
+      <c r="S51">
+        <v>0.2043765118041381</v>
+      </c>
+      <c r="T51">
+        <v>1.839648816988309</v>
+      </c>
+      <c r="U51">
+        <v>0.0562</v>
+      </c>
+      <c r="V51">
+        <v>0.2</v>
+      </c>
+      <c r="W51">
+        <v>0.04496</v>
+      </c>
+      <c r="X51" t="inlineStr">
+        <is>
+          <t>Ba1/BB+</t>
+        </is>
+      </c>
+      <c r="Y51">
+        <v>3.697386044520074</v>
+      </c>
+      <c r="Z51">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52">
+        <v>0.5</v>
+      </c>
+      <c r="B52">
+        <v>0.1261367837229483</v>
+      </c>
+      <c r="C52">
+        <v>16.33939931841403</v>
+      </c>
+      <c r="D52">
+        <v>26.89939931841403</v>
+      </c>
+      <c r="E52">
+        <v>7.069999999999999</v>
+      </c>
+      <c r="F52">
+        <v>13.93</v>
+      </c>
+      <c r="G52">
+        <v>3.37</v>
+      </c>
+      <c r="H52">
+        <v>21</v>
+      </c>
+      <c r="I52">
+        <v>0</v>
+      </c>
+      <c r="J52">
+        <v>3.716666666666667</v>
+      </c>
+      <c r="K52">
+        <v>0.8799999999999999</v>
+      </c>
+      <c r="L52">
+        <v>2.836666666666667</v>
+      </c>
+      <c r="M52">
+        <v>0.782866</v>
+      </c>
+      <c r="N52">
+        <v>2.053800666666667</v>
+      </c>
+      <c r="O52">
+        <v>0.4107601333333334</v>
+      </c>
+      <c r="P52">
+        <v>1.643040533333334</v>
+      </c>
+      <c r="Q52">
+        <v>2.523040533333333</v>
+      </c>
+      <c r="R52">
+        <v>1</v>
+      </c>
+      <c r="S52">
+        <v>0.2073135674458967</v>
+      </c>
+      <c r="T52">
+        <v>1.872281168509166</v>
+      </c>
+      <c r="U52">
+        <v>0.0562</v>
+      </c>
+      <c r="V52">
+        <v>0.2</v>
+      </c>
+      <c r="W52">
+        <v>0.04496</v>
+      </c>
+      <c r="X52" t="inlineStr">
+        <is>
+          <t>Ba1/BB+</t>
+        </is>
+      </c>
+      <c r="Y52">
+        <v>3.623438323629673</v>
+      </c>
+      <c r="Z52">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53">
+        <v>0.51</v>
+      </c>
+      <c r="B53">
+        <v>0.1260111464257863</v>
+      </c>
+      <c r="C53">
+        <v>16.09955087672</v>
+      </c>
+      <c r="D53">
+        <v>26.93815087672</v>
+      </c>
+      <c r="E53">
+        <v>7.3486</v>
+      </c>
+      <c r="F53">
+        <v>14.2086</v>
+      </c>
+      <c r="G53">
+        <v>3.37</v>
+      </c>
+      <c r="H53">
+        <v>21</v>
+      </c>
+      <c r="I53">
+        <v>0</v>
+      </c>
+      <c r="J53">
+        <v>3.716666666666667</v>
+      </c>
+      <c r="K53">
+        <v>0.8799999999999999</v>
+      </c>
+      <c r="L53">
+        <v>2.836666666666667</v>
+      </c>
+      <c r="M53">
+        <v>0.79852332</v>
+      </c>
+      <c r="N53">
+        <v>2.038143346666667</v>
+      </c>
+      <c r="O53">
+        <v>0.4076286693333334</v>
+      </c>
+      <c r="P53">
+        <v>1.630514677333333</v>
+      </c>
+      <c r="Q53">
+        <v>2.510514677333333</v>
+      </c>
+      <c r="R53">
+        <v>1.040816326530612</v>
+      </c>
+      <c r="S53">
+        <v>0.2103705029097679</v>
+      </c>
+      <c r="T53">
+        <v>1.90624545274516</v>
+      </c>
+      <c r="U53">
+        <v>0.0562</v>
+      </c>
+      <c r="V53">
+        <v>0.2</v>
+      </c>
+      <c r="W53">
+        <v>0.04496</v>
+      </c>
+      <c r="X53" t="inlineStr">
+        <is>
+          <t>Ba1/BB+</t>
+        </is>
+      </c>
+      <c r="Y53">
+        <v>3.552390513362423</v>
+      </c>
+      <c r="Z53">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54">
+        <v>0.52</v>
+      </c>
+      <c r="B54">
+        <v>0.1278407091286241</v>
+      </c>
+      <c r="C54">
+        <v>15.26743960519282</v>
+      </c>
+      <c r="D54">
+        <v>26.38463960519282</v>
+      </c>
+      <c r="E54">
+        <v>7.627199999999999</v>
+      </c>
+      <c r="F54">
+        <v>14.4872</v>
+      </c>
+      <c r="G54">
+        <v>3.37</v>
+      </c>
+      <c r="H54">
+        <v>21</v>
+      </c>
+      <c r="I54">
+        <v>0</v>
+      </c>
+      <c r="J54">
+        <v>3.716666666666667</v>
+      </c>
+      <c r="K54">
+        <v>0.8799999999999999</v>
+      </c>
+      <c r="L54">
+        <v>2.836666666666667</v>
+      </c>
+      <c r="M54">
+        <v>0.88227048</v>
+      </c>
+      <c r="N54">
+        <v>1.954396186666667</v>
+      </c>
+      <c r="O54">
+        <v>0.3908792373333334</v>
+      </c>
+      <c r="P54">
+        <v>1.563516949333334</v>
+      </c>
+      <c r="Q54">
+        <v>2.443516949333334</v>
+      </c>
+      <c r="R54">
+        <v>1.083333333333333</v>
+      </c>
+      <c r="S54">
+        <v>0.2135548106846336</v>
+      </c>
+      <c r="T54">
+        <v>1.941624915490987</v>
+      </c>
+      <c r="U54">
+        <v>0.0609</v>
+      </c>
+      <c r="V54">
+        <v>0.2</v>
+      </c>
+      <c r="W54">
+        <v>0.04872000000000001</v>
+      </c>
+      <c r="X54" t="inlineStr">
+        <is>
+          <t>Ba2/BB</t>
+        </is>
+      </c>
+      <c r="Y54">
+        <v>3.21518936762643</v>
+      </c>
+      <c r="Z54">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55">
+        <v>0.53</v>
+      </c>
+      <c r="B55">
+        <v>0.127752671831462</v>
+      </c>
+      <c r="C55">
+        <v>15.01495273152857</v>
+      </c>
+      <c r="D55">
+        <v>26.41075273152857</v>
+      </c>
+      <c r="E55">
+        <v>7.9058</v>
+      </c>
+      <c r="F55">
+        <v>14.7658</v>
+      </c>
+      <c r="G55">
+        <v>3.37</v>
+      </c>
+      <c r="H55">
+        <v>21</v>
+      </c>
+      <c r="I55">
+        <v>0</v>
+      </c>
+      <c r="J55">
+        <v>3.716666666666667</v>
+      </c>
+      <c r="K55">
+        <v>0.8799999999999999</v>
+      </c>
+      <c r="L55">
+        <v>2.836666666666667</v>
+      </c>
+      <c r="M55">
+        <v>0.8992372200000001</v>
+      </c>
+      <c r="N55">
+        <v>1.937429446666667</v>
+      </c>
+      <c r="O55">
+        <v>0.3874858893333334</v>
+      </c>
+      <c r="P55">
+        <v>1.549943557333334</v>
+      </c>
+      <c r="Q55">
+        <v>2.429943557333333</v>
+      </c>
+      <c r="R55">
+        <v>1.127659574468085</v>
+      </c>
+      <c r="S55">
+        <v>0.2168746209180043</v>
+      </c>
+      <c r="T55">
+        <v>1.978509887289828</v>
+      </c>
+      <c r="U55">
+        <v>0.0609</v>
+      </c>
+      <c r="V55">
+        <v>0.2</v>
+      </c>
+      <c r="W55">
+        <v>0.04872000000000001</v>
+      </c>
+      <c r="X55" t="inlineStr">
+        <is>
+          <t>Ba2/BB</t>
+        </is>
+      </c>
+      <c r="Y55">
+        <v>3.154525417293855</v>
+      </c>
+      <c r="Z55">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56">
+        <v>0.54</v>
+      </c>
+      <c r="B56">
+        <v>0.1276646345342999</v>
+      </c>
+      <c r="C56">
+        <v>14.7625175978861</v>
+      </c>
+      <c r="D56">
+        <v>26.4369175978861</v>
+      </c>
+      <c r="E56">
+        <v>8.1844</v>
+      </c>
+      <c r="F56">
+        <v>15.0444</v>
+      </c>
+      <c r="G56">
+        <v>3.37</v>
+      </c>
+      <c r="H56">
+        <v>21</v>
+      </c>
+      <c r="I56">
+        <v>0</v>
+      </c>
+      <c r="J56">
+        <v>3.716666666666667</v>
+      </c>
+      <c r="K56">
+        <v>0.8799999999999999</v>
+      </c>
+      <c r="L56">
+        <v>2.836666666666667</v>
+      </c>
+      <c r="M56">
+        <v>0.9162039600000002</v>
+      </c>
+      <c r="N56">
+        <v>1.920462706666667</v>
+      </c>
+      <c r="O56">
+        <v>0.3840925413333334</v>
+      </c>
+      <c r="P56">
+        <v>1.536370165333333</v>
+      </c>
+      <c r="Q56">
+        <v>2.416370165333333</v>
+      </c>
+      <c r="R56">
+        <v>1.173913043478261</v>
+      </c>
+      <c r="S56">
+        <v>0.220338770726739</v>
+      </c>
+      <c r="T56">
+        <v>2.016998553514705</v>
+      </c>
+      <c r="U56">
+        <v>0.0609</v>
+      </c>
+      <c r="V56">
+        <v>0.2</v>
+      </c>
+      <c r="W56">
+        <v>0.04872000000000001</v>
+      </c>
+      <c r="X56" t="inlineStr">
+        <is>
+          <t>Ba2/BB</t>
+        </is>
+      </c>
+      <c r="Y56">
+        <v>3.096108279936562</v>
+      </c>
+      <c r="Z56">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57">
+        <v>0.55</v>
+      </c>
+      <c r="B57">
+        <v>0.1275765972371378</v>
+      </c>
+      <c r="C57">
+        <v>14.51013435819285</v>
+      </c>
+      <c r="D57">
+        <v>26.46313435819285</v>
+      </c>
+      <c r="E57">
+        <v>8.463000000000001</v>
+      </c>
+      <c r="F57">
+        <v>15.323</v>
+      </c>
+      <c r="G57">
+        <v>3.37</v>
+      </c>
+      <c r="H57">
+        <v>21</v>
+      </c>
+      <c r="I57">
+        <v>0</v>
+      </c>
+      <c r="J57">
+        <v>3.716666666666667</v>
+      </c>
+      <c r="K57">
+        <v>0.8799999999999999</v>
+      </c>
+      <c r="L57">
+        <v>2.836666666666667</v>
+      </c>
+      <c r="M57">
+        <v>0.9331707</v>
+      </c>
+      <c r="N57">
+        <v>1.903495966666667</v>
+      </c>
+      <c r="O57">
+        <v>0.3806991933333334</v>
+      </c>
+      <c r="P57">
+        <v>1.522796773333333</v>
+      </c>
+      <c r="Q57">
+        <v>2.402796773333333</v>
+      </c>
+      <c r="R57">
+        <v>1.222222222222223</v>
+      </c>
+      <c r="S57">
+        <v>0.2239568827491952</v>
+      </c>
+      <c r="T57">
+        <v>2.057197827127355</v>
+      </c>
+      <c r="U57">
+        <v>0.0609</v>
+      </c>
+      <c r="V57">
+        <v>0.2</v>
+      </c>
+      <c r="W57">
+        <v>0.04872000000000001</v>
+      </c>
+      <c r="X57" t="inlineStr">
+        <is>
+          <t>Ba2/BB</t>
+        </is>
+      </c>
+      <c r="Y57">
+        <v>3.039815402119534</v>
+      </c>
+      <c r="Z57">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58">
+        <v>0.5600000000000001</v>
+      </c>
+      <c r="B58">
+        <v>0.1316549599399757</v>
+      </c>
+      <c r="C58">
+        <v>13.06922423241812</v>
+      </c>
+      <c r="D58">
+        <v>25.30082423241812</v>
+      </c>
+      <c r="E58">
+        <v>8.741600000000002</v>
+      </c>
+      <c r="F58">
+        <v>15.6016</v>
+      </c>
+      <c r="G58">
+        <v>3.37</v>
+      </c>
+      <c r="H58">
+        <v>21</v>
+      </c>
+      <c r="I58">
+        <v>0</v>
+      </c>
+      <c r="J58">
+        <v>3.716666666666667</v>
+      </c>
+      <c r="K58">
+        <v>0.8799999999999999</v>
+      </c>
+      <c r="L58">
+        <v>2.836666666666667</v>
+      </c>
+      <c r="M58">
+        <v>1.09523232</v>
+      </c>
+      <c r="N58">
+        <v>1.741434346666667</v>
+      </c>
+      <c r="O58">
+        <v>0.3482868693333334</v>
+      </c>
+      <c r="P58">
+        <v>1.393147477333333</v>
+      </c>
+      <c r="Q58">
+        <v>2.273147477333334</v>
+      </c>
+      <c r="R58">
+        <v>1.272727272727273</v>
+      </c>
+      <c r="S58">
+        <v>0.2277394544090357</v>
+      </c>
+      <c r="T58">
+        <v>2.099224340449671</v>
+      </c>
+      <c r="U58">
+        <v>0.0702</v>
+      </c>
+      <c r="V58">
+        <v>0.2</v>
+      </c>
+      <c r="W58">
+        <v>0.05616</v>
+      </c>
+      <c r="X58" t="inlineStr">
+        <is>
+          <t>B1/B+</t>
+        </is>
+      </c>
+      <c r="Y58">
+        <v>2.590013657254624</v>
+      </c>
+      <c r="Z58">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59">
+        <v>0.5700000000000001</v>
+      </c>
+      <c r="B59">
+        <v>0.1316413226428136</v>
+      </c>
+      <c r="C59">
+        <v>12.79434062560039</v>
+      </c>
+      <c r="D59">
+        <v>25.3045406256004</v>
+      </c>
+      <c r="E59">
+        <v>9.020200000000003</v>
+      </c>
+      <c r="F59">
+        <v>15.8802</v>
+      </c>
+      <c r="G59">
+        <v>3.37</v>
+      </c>
+      <c r="H59">
+        <v>21</v>
+      </c>
+      <c r="I59">
+        <v>0</v>
+      </c>
+      <c r="J59">
+        <v>3.716666666666667</v>
+      </c>
+      <c r="K59">
+        <v>0.8799999999999999</v>
+      </c>
+      <c r="L59">
+        <v>2.836666666666667</v>
+      </c>
+      <c r="M59">
+        <v>1.11479004</v>
+      </c>
+      <c r="N59">
+        <v>1.721876626666667</v>
+      </c>
+      <c r="O59">
+        <v>0.3443753253333334</v>
+      </c>
+      <c r="P59">
+        <v>1.377501301333333</v>
+      </c>
+      <c r="Q59">
+        <v>2.257501301333333</v>
+      </c>
+      <c r="R59">
+        <v>1.325581395348838</v>
+      </c>
+      <c r="S59">
+        <v>0.2316979596344502</v>
+      </c>
+      <c r="T59">
+        <v>2.143205575321862</v>
+      </c>
+      <c r="U59">
+        <v>0.0702</v>
+      </c>
+      <c r="V59">
+        <v>0.2</v>
+      </c>
+      <c r="W59">
+        <v>0.05616</v>
+      </c>
+      <c r="X59" t="inlineStr">
+        <is>
+          <t>B1/B+</t>
+        </is>
+      </c>
+      <c r="Y59">
+        <v>2.544574821162437</v>
+      </c>
+      <c r="Z59">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60">
+        <v>0.58</v>
+      </c>
+      <c r="B60">
+        <v>0.1316276853456515</v>
+      </c>
+      <c r="C60">
+        <v>12.51945811073188</v>
+      </c>
+      <c r="D60">
+        <v>25.30825811073187</v>
+      </c>
+      <c r="E60">
+        <v>9.2988</v>
+      </c>
+      <c r="F60">
+        <v>16.1588</v>
+      </c>
+      <c r="G60">
+        <v>3.37</v>
+      </c>
+      <c r="H60">
+        <v>21</v>
+      </c>
+      <c r="I60">
+        <v>0</v>
+      </c>
+      <c r="J60">
+        <v>3.716666666666667</v>
+      </c>
+      <c r="K60">
+        <v>0.8799999999999999</v>
+      </c>
+      <c r="L60">
+        <v>2.836666666666667</v>
+      </c>
+      <c r="M60">
+        <v>1.13434776</v>
+      </c>
+      <c r="N60">
+        <v>1.702318906666667</v>
+      </c>
+      <c r="O60">
+        <v>0.3404637813333334</v>
+      </c>
+      <c r="P60">
+        <v>1.361855125333334</v>
+      </c>
+      <c r="Q60">
+        <v>2.241855125333333</v>
+      </c>
+      <c r="R60">
+        <v>1.380952380952381</v>
+      </c>
+      <c r="S60">
+        <v>0.235844965108694</v>
+      </c>
+      <c r="T60">
+        <v>2.189281154711775</v>
+      </c>
+      <c r="U60">
+        <v>0.0702</v>
+      </c>
+      <c r="V60">
+        <v>0.2</v>
+      </c>
+      <c r="W60">
+        <v>0.05616</v>
+      </c>
+      <c r="X60" t="inlineStr">
+        <is>
+          <t>B1/B+</t>
+        </is>
+      </c>
+      <c r="Y60">
+        <v>2.500702841487223</v>
+      </c>
+      <c r="Z60">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61">
+        <v>0.59</v>
+      </c>
+      <c r="B61">
+        <v>0.1338324480484894</v>
+      </c>
+      <c r="C61">
+        <v>11.65370388391593</v>
+      </c>
+      <c r="D61">
+        <v>24.72110388391593</v>
+      </c>
+      <c r="E61">
+        <v>9.577400000000001</v>
+      </c>
+      <c r="F61">
+        <v>16.4374</v>
+      </c>
+      <c r="G61">
+        <v>3.37</v>
+      </c>
+      <c r="H61">
+        <v>21</v>
+      </c>
+      <c r="I61">
+        <v>0</v>
+      </c>
+      <c r="J61">
+        <v>3.716666666666667</v>
+      </c>
+      <c r="K61">
+        <v>0.8799999999999999</v>
+      </c>
+      <c r="L61">
+        <v>2.836666666666667</v>
+      </c>
+      <c r="M61">
+        <v>1.23116126</v>
+      </c>
+      <c r="N61">
+        <v>1.605505406666667</v>
+      </c>
+      <c r="O61">
+        <v>0.3211010813333334</v>
+      </c>
+      <c r="P61">
+        <v>1.284404325333333</v>
+      </c>
+      <c r="Q61">
+        <v>2.164404325333333</v>
+      </c>
+      <c r="R61">
+        <v>1.439024390243902</v>
+      </c>
+      <c r="S61">
+        <v>0.2401942635329009</v>
+      </c>
+      <c r="T61">
+        <v>2.237604323340223</v>
+      </c>
+      <c r="U61">
+        <v>0.07489999999999999</v>
+      </c>
+      <c r="V61">
+        <v>0.2</v>
+      </c>
+      <c r="W61">
+        <v>0.05992</v>
+      </c>
+      <c r="X61" t="inlineStr">
+        <is>
+          <t>B2/B</t>
+        </is>
+      </c>
+      <c r="Y61">
+        <v>2.304057769545695</v>
+      </c>
+      <c r="Z61">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62">
+        <v>0.6</v>
+      </c>
+      <c r="B62">
+        <v>0.1338564107513273</v>
+      </c>
+      <c r="C62">
+        <v>11.36887195845702</v>
+      </c>
+      <c r="D62">
+        <v>24.71487195845701</v>
+      </c>
+      <c r="E62">
+        <v>9.855999999999998</v>
+      </c>
+      <c r="F62">
+        <v>16.716</v>
+      </c>
+      <c r="G62">
+        <v>3.37</v>
+      </c>
+      <c r="H62">
+        <v>21</v>
+      </c>
+      <c r="I62">
+        <v>0</v>
+      </c>
+      <c r="J62">
+        <v>3.716666666666667</v>
+      </c>
+      <c r="K62">
+        <v>0.8799999999999999</v>
+      </c>
+      <c r="L62">
+        <v>2.836666666666667</v>
+      </c>
+      <c r="M62">
+        <v>1.2520284</v>
+      </c>
+      <c r="N62">
+        <v>1.584638266666667</v>
+      </c>
+      <c r="O62">
+        <v>0.3169276533333334</v>
+      </c>
+      <c r="P62">
+        <v>1.267710613333334</v>
+      </c>
+      <c r="Q62">
+        <v>2.147710613333333</v>
+      </c>
+      <c r="R62">
+        <v>1.5</v>
+      </c>
+      <c r="S62">
+        <v>0.2447610268783182</v>
+      </c>
+      <c r="T62">
+        <v>2.288343650400092</v>
+      </c>
+      <c r="U62">
+        <v>0.07489999999999999</v>
+      </c>
+      <c r="V62">
+        <v>0.2</v>
+      </c>
+      <c r="W62">
+        <v>0.05992</v>
+      </c>
+      <c r="X62" t="inlineStr">
+        <is>
+          <t>B2/B</t>
+        </is>
+      </c>
+      <c r="Y62">
+        <v>2.265656806719933</v>
+      </c>
+      <c r="Z62">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63">
+        <v>0.61</v>
+      </c>
+      <c r="B63">
+        <v>0.1338803734541652</v>
+      </c>
+      <c r="C63">
+        <v>11.08404317420952</v>
+      </c>
+      <c r="D63">
+        <v>24.70864317420952</v>
+      </c>
+      <c r="E63">
+        <v>10.1346</v>
+      </c>
+      <c r="F63">
+        <v>16.9946</v>
+      </c>
+      <c r="G63">
+        <v>3.37</v>
+      </c>
+      <c r="H63">
+        <v>21</v>
+      </c>
+      <c r="I63">
+        <v>0</v>
+      </c>
+      <c r="J63">
+        <v>3.716666666666667</v>
+      </c>
+      <c r="K63">
+        <v>0.8799999999999999</v>
+      </c>
+      <c r="L63">
+        <v>2.836666666666667</v>
+      </c>
+      <c r="M63">
+        <v>1.27289554</v>
+      </c>
+      <c r="N63">
+        <v>1.563771126666667</v>
+      </c>
+      <c r="O63">
+        <v>0.3127542253333335</v>
+      </c>
+      <c r="P63">
+        <v>1.251016901333334</v>
+      </c>
+      <c r="Q63">
+        <v>2.131016901333334</v>
+      </c>
+      <c r="R63">
+        <v>1.564102564102564</v>
+      </c>
+      <c r="S63">
+        <v>0.2495619832158081</v>
+      </c>
+      <c r="T63">
+        <v>2.341684994232261</v>
+      </c>
+      <c r="U63">
+        <v>0.07489999999999999</v>
+      </c>
+      <c r="V63">
+        <v>0.2</v>
+      </c>
+      <c r="W63">
+        <v>0.05992</v>
+      </c>
+      <c r="X63" t="inlineStr">
+        <is>
+          <t>B2/B</t>
+        </is>
+      </c>
+      <c r="Y63">
+        <v>2.228514891855673</v>
+      </c>
+      <c r="Z63">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64">
+        <v>0.62</v>
+      </c>
+      <c r="B64">
+        <v>0.1339043361570031</v>
+      </c>
+      <c r="C64">
+        <v>10.79921752879906</v>
+      </c>
+      <c r="D64">
+        <v>24.70241752879906</v>
+      </c>
+      <c r="E64">
+        <v>10.4132</v>
+      </c>
+      <c r="F64">
+        <v>17.2732</v>
+      </c>
+      <c r="G64">
+        <v>3.37</v>
+      </c>
+      <c r="H64">
+        <v>21</v>
+      </c>
+      <c r="I64">
+        <v>0</v>
+      </c>
+      <c r="J64">
+        <v>3.716666666666667</v>
+      </c>
+      <c r="K64">
+        <v>0.8799999999999999</v>
+      </c>
+      <c r="L64">
+        <v>2.836666666666667</v>
+      </c>
+      <c r="M64">
+        <v>1.29376268</v>
+      </c>
+      <c r="N64">
+        <v>1.542903986666667</v>
+      </c>
+      <c r="O64">
+        <v>0.3085807973333334</v>
+      </c>
+      <c r="P64">
+        <v>1.234323189333334</v>
+      </c>
+      <c r="Q64">
+        <v>2.114323189333334</v>
+      </c>
+      <c r="R64">
+        <v>1.631578947368421</v>
+      </c>
+      <c r="S64">
+        <v>0.2546156214657975</v>
+      </c>
+      <c r="T64">
+        <v>2.397833777213493</v>
+      </c>
+      <c r="U64">
+        <v>0.07489999999999999</v>
+      </c>
+      <c r="V64">
+        <v>0.2</v>
+      </c>
+      <c r="W64">
+        <v>0.05992</v>
+      </c>
+      <c r="X64" t="inlineStr">
+        <is>
+          <t>B2/B</t>
+        </is>
+      </c>
+      <c r="Y64">
+        <v>2.192571103277355</v>
+      </c>
+      <c r="Z64">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65">
+        <v>0.63</v>
+      </c>
+      <c r="B65">
+        <v>0.1339282988598409</v>
+      </c>
+      <c r="C65">
+        <v>10.51439501985362</v>
+      </c>
+      <c r="D65">
+        <v>24.69619501985362</v>
+      </c>
+      <c r="E65">
+        <v>10.6918</v>
+      </c>
+      <c r="F65">
+        <v>17.5518</v>
+      </c>
+      <c r="G65">
+        <v>3.37</v>
+      </c>
+      <c r="H65">
+        <v>21</v>
+      </c>
+      <c r="I65">
+        <v>0</v>
+      </c>
+      <c r="J65">
+        <v>3.716666666666667</v>
+      </c>
+      <c r="K65">
+        <v>0.8799999999999999</v>
+      </c>
+      <c r="L65">
+        <v>2.836666666666667</v>
+      </c>
+      <c r="M65">
+        <v>1.31462982</v>
+      </c>
+      <c r="N65">
+        <v>1.522036846666667</v>
+      </c>
+      <c r="O65">
+        <v>0.3044073693333334</v>
+      </c>
+      <c r="P65">
+        <v>1.217629477333334</v>
+      </c>
+      <c r="Q65">
+        <v>2.097629477333333</v>
+      </c>
+      <c r="R65">
+        <v>1.702702702702703</v>
+      </c>
+      <c r="S65">
+        <v>0.2599424293509215</v>
+      </c>
+      <c r="T65">
+        <v>2.457017629545061</v>
+      </c>
+      <c r="U65">
+        <v>0.07489999999999999</v>
+      </c>
+      <c r="V65">
+        <v>0.2</v>
+      </c>
+      <c r="W65">
+        <v>0.05992</v>
+      </c>
+      <c r="X65" t="inlineStr">
+        <is>
+          <t>B2/B</t>
+        </is>
+      </c>
+      <c r="Y65">
+        <v>2.157768387352317</v>
+      </c>
+      <c r="Z65">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66">
+        <v>0.64</v>
+      </c>
+      <c r="B66">
+        <v>0.1339522615626789</v>
+      </c>
+      <c r="C66">
+        <v>10.22957564500357</v>
+      </c>
+      <c r="D66">
+        <v>24.68997564500357</v>
+      </c>
+      <c r="E66">
+        <v>10.9704</v>
+      </c>
+      <c r="F66">
+        <v>17.8304</v>
+      </c>
+      <c r="G66">
+        <v>3.37</v>
+      </c>
+      <c r="H66">
+        <v>21</v>
+      </c>
+      <c r="I66">
+        <v>0</v>
+      </c>
+      <c r="J66">
+        <v>3.716666666666667</v>
+      </c>
+      <c r="K66">
+        <v>0.8799999999999999</v>
+      </c>
+      <c r="L66">
+        <v>2.836666666666667</v>
+      </c>
+      <c r="M66">
+        <v>1.33549696</v>
+      </c>
+      <c r="N66">
+        <v>1.501169706666667</v>
+      </c>
+      <c r="O66">
+        <v>0.3002339413333334</v>
+      </c>
+      <c r="P66">
+        <v>1.200935765333333</v>
+      </c>
+      <c r="Q66">
+        <v>2.080935765333333</v>
+      </c>
+      <c r="R66">
+        <v>1.777777777777778</v>
+      </c>
+      <c r="S66">
+        <v>0.2655651710074413</v>
+      </c>
+      <c r="T66">
+        <v>2.519489473672828</v>
+      </c>
+      <c r="U66">
+        <v>0.07489999999999999</v>
+      </c>
+      <c r="V66">
+        <v>0.2</v>
+      </c>
+      <c r="W66">
+        <v>0.05992</v>
+      </c>
+      <c r="X66" t="inlineStr">
+        <is>
+          <t>B2/B</t>
+        </is>
+      </c>
+      <c r="Y66">
+        <v>2.124053256299937</v>
+      </c>
+      <c r="Z66">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67">
+        <v>0.65</v>
+      </c>
+      <c r="B67">
+        <v>0.1339762242655168</v>
+      </c>
+      <c r="C67">
+        <v>9.944759401881701</v>
+      </c>
+      <c r="D67">
+        <v>24.6837594018817</v>
+      </c>
+      <c r="E67">
+        <v>11.249</v>
+      </c>
+      <c r="F67">
+        <v>18.109</v>
+      </c>
+      <c r="G67">
+        <v>3.37</v>
+      </c>
+      <c r="H67">
+        <v>21</v>
+      </c>
+      <c r="I67">
+        <v>0</v>
+      </c>
+      <c r="J67">
+        <v>3.716666666666667</v>
+      </c>
+      <c r="K67">
+        <v>0.8799999999999999</v>
+      </c>
+      <c r="L67">
+        <v>2.836666666666667</v>
+      </c>
+      <c r="M67">
+        <v>1.3563641</v>
+      </c>
+      <c r="N67">
+        <v>1.480302566666667</v>
+      </c>
+      <c r="O67">
+        <v>0.2960605133333334</v>
+      </c>
+      <c r="P67">
+        <v>1.184242053333334</v>
+      </c>
+      <c r="Q67">
+        <v>2.064242053333333</v>
+      </c>
+      <c r="R67">
+        <v>1.857142857142857</v>
+      </c>
+      <c r="S67">
+        <v>0.2715092121871907</v>
+      </c>
+      <c r="T67">
+        <v>2.585531137465038</v>
+      </c>
+      <c r="U67">
+        <v>0.07489999999999999</v>
+      </c>
+      <c r="V67">
+        <v>0.2</v>
+      </c>
+      <c r="W67">
+        <v>0.05992</v>
+      </c>
+      <c r="X67" t="inlineStr">
+        <is>
+          <t>B2/B</t>
+        </is>
+      </c>
+      <c r="Y67">
+        <v>2.091375513895323</v>
+      </c>
+      <c r="Z67">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68">
+        <v>0.66</v>
+      </c>
+      <c r="B68">
+        <v>0.1340001869683546</v>
+      </c>
+      <c r="C68">
+        <v>9.659946288123155</v>
+      </c>
+      <c r="D68">
+        <v>24.67754628812315</v>
+      </c>
+      <c r="E68">
+        <v>11.5276</v>
+      </c>
+      <c r="F68">
+        <v>18.3876</v>
+      </c>
+      <c r="G68">
+        <v>3.37</v>
+      </c>
+      <c r="H68">
+        <v>21</v>
+      </c>
+      <c r="I68">
+        <v>0</v>
+      </c>
+      <c r="J68">
+        <v>3.716666666666667</v>
+      </c>
+      <c r="K68">
+        <v>0.8799999999999999</v>
+      </c>
+      <c r="L68">
+        <v>2.836666666666667</v>
+      </c>
+      <c r="M68">
+        <v>1.37723124</v>
+      </c>
+      <c r="N68">
+        <v>1.459435426666667</v>
+      </c>
+      <c r="O68">
+        <v>0.2918870853333335</v>
+      </c>
+      <c r="P68">
+        <v>1.167548341333334</v>
+      </c>
+      <c r="Q68">
+        <v>2.047548341333334</v>
+      </c>
+      <c r="R68">
+        <v>1.941176470588236</v>
+      </c>
+      <c r="S68">
+        <v>0.2778029028481019</v>
+      </c>
+      <c r="T68">
+        <v>2.655457605009732</v>
+      </c>
+      <c r="U68">
+        <v>0.07489999999999999</v>
+      </c>
+      <c r="V68">
+        <v>0.2</v>
+      </c>
+      <c r="W68">
+        <v>0.05992</v>
+      </c>
+      <c r="X68" t="inlineStr">
+        <is>
+          <t>B2/B</t>
+        </is>
+      </c>
+      <c r="Y68">
+        <v>2.05968800610903</v>
+      </c>
+      <c r="Z68">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69">
+        <v>0.67</v>
+      </c>
+      <c r="B69">
+        <v>0.1340241496711925</v>
+      </c>
+      <c r="C69">
+        <v>9.375136301365462</v>
+      </c>
+      <c r="D69">
+        <v>24.67133630136546</v>
+      </c>
+      <c r="E69">
+        <v>11.8062</v>
+      </c>
+      <c r="F69">
+        <v>18.6662</v>
+      </c>
+      <c r="G69">
+        <v>3.37</v>
+      </c>
+      <c r="H69">
+        <v>21</v>
+      </c>
+      <c r="I69">
+        <v>0</v>
+      </c>
+      <c r="J69">
+        <v>3.716666666666667</v>
+      </c>
+      <c r="K69">
+        <v>0.8799999999999999</v>
+      </c>
+      <c r="L69">
+        <v>2.836666666666667</v>
+      </c>
+      <c r="M69">
+        <v>1.39809838</v>
+      </c>
+      <c r="N69">
+        <v>1.438568286666667</v>
+      </c>
+      <c r="O69">
+        <v>0.2877136573333334</v>
+      </c>
+      <c r="P69">
+        <v>1.150854629333333</v>
+      </c>
+      <c r="Q69">
+        <v>2.030854629333334</v>
+      </c>
+      <c r="R69">
+        <v>2.030303030303031</v>
+      </c>
+      <c r="S69">
+        <v>0.2844780293066441</v>
+      </c>
+      <c r="T69">
+        <v>2.729622040284407</v>
+      </c>
+      <c r="U69">
+        <v>0.07489999999999999</v>
+      </c>
+      <c r="V69">
+        <v>0.2</v>
+      </c>
+      <c r="W69">
+        <v>0.05992</v>
+      </c>
+      <c r="X69" t="inlineStr">
+        <is>
+          <t>B2/B</t>
+        </is>
+      </c>
+      <c r="Y69">
+        <v>2.028946394077552</v>
+      </c>
+      <c r="Z69">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70">
+        <v>0.68</v>
+      </c>
+      <c r="B70">
+        <v>0.1429153123740304</v>
+      </c>
+      <c r="C70">
+        <v>6.989671709115669</v>
+      </c>
+      <c r="D70">
+        <v>22.56447170911567</v>
+      </c>
+      <c r="E70">
+        <v>12.0848</v>
+      </c>
+      <c r="F70">
+        <v>18.9448</v>
+      </c>
+      <c r="G70">
+        <v>3.37</v>
+      </c>
+      <c r="H70">
+        <v>21</v>
+      </c>
+      <c r="I70">
+        <v>0</v>
+      </c>
+      <c r="J70">
+        <v>3.716666666666667</v>
+      </c>
+      <c r="K70">
+        <v>0.8799999999999999</v>
+      </c>
+      <c r="L70">
+        <v>2.836666666666667</v>
+      </c>
+      <c r="M70">
+        <v>1.72776576</v>
+      </c>
+      <c r="N70">
+        <v>1.108900906666667</v>
+      </c>
+      <c r="O70">
+        <v>0.2217801813333334</v>
+      </c>
+      <c r="P70">
+        <v>0.8871207253333335</v>
+      </c>
+      <c r="Q70">
+        <v>1.767120725333333</v>
+      </c>
+      <c r="R70">
+        <v>2.125</v>
+      </c>
+      <c r="S70">
+        <v>0.2915703511688451</v>
+      </c>
+      <c r="T70">
+        <v>2.808421752763749</v>
+      </c>
+      <c r="U70">
+        <v>0.0912</v>
+      </c>
+      <c r="V70">
+        <v>0.2</v>
+      </c>
+      <c r="W70">
+        <v>0.07296000000000001</v>
+      </c>
+      <c r="X70" t="inlineStr">
+        <is>
+          <t>B3/B-</t>
+        </is>
+      </c>
+      <c r="Y70">
+        <v>1.641812062919146</v>
+      </c>
+      <c r="Z70">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71">
+        <v>0.6900000000000001</v>
+      </c>
+      <c r="B71">
+        <v>0.1430696750768683</v>
+      </c>
+      <c r="C71">
+        <v>6.677666859253428</v>
+      </c>
+      <c r="D71">
+        <v>22.53106685925343</v>
+      </c>
+      <c r="E71">
+        <v>12.3634</v>
+      </c>
+      <c r="F71">
+        <v>19.2234</v>
+      </c>
+      <c r="G71">
+        <v>3.37</v>
+      </c>
+      <c r="H71">
+        <v>21</v>
+      </c>
+      <c r="I71">
+        <v>0</v>
+      </c>
+      <c r="J71">
+        <v>3.716666666666667</v>
+      </c>
+      <c r="K71">
+        <v>0.8799999999999999</v>
+      </c>
+      <c r="L71">
+        <v>2.836666666666667</v>
+      </c>
+      <c r="M71">
+        <v>1.75317408</v>
+      </c>
+      <c r="N71">
+        <v>1.083492586666667</v>
+      </c>
+      <c r="O71">
+        <v>0.2166985173333333</v>
+      </c>
+      <c r="P71">
+        <v>0.8667940693333334</v>
+      </c>
+      <c r="Q71">
+        <v>1.746794069333333</v>
+      </c>
+      <c r="R71">
+        <v>2.225806451612904</v>
+      </c>
+      <c r="S71">
+        <v>0.2991202421834462</v>
+      </c>
+      <c r="T71">
+        <v>2.892305317661113</v>
+      </c>
+      <c r="U71">
+        <v>0.0912</v>
+      </c>
+      <c r="V71">
+        <v>0.2</v>
+      </c>
+      <c r="W71">
+        <v>0.07296000000000001</v>
+      </c>
+      <c r="X71" t="inlineStr">
+        <is>
+          <t>B3/B-</t>
+        </is>
+      </c>
+      <c r="Y71">
+        <v>1.61801768519568</v>
+      </c>
+      <c r="Z71">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72">
+        <v>0.7000000000000001</v>
+      </c>
+      <c r="B72">
+        <v>0.1432240377797062</v>
+      </c>
+      <c r="C72">
+        <v>6.365760769466391</v>
+      </c>
+      <c r="D72">
+        <v>22.49776076946639</v>
+      </c>
+      <c r="E72">
+        <v>12.642</v>
+      </c>
+      <c r="F72">
+        <v>19.502</v>
+      </c>
+      <c r="G72">
+        <v>3.37</v>
+      </c>
+      <c r="H72">
+        <v>21</v>
+      </c>
+      <c r="I72">
+        <v>0</v>
+      </c>
+      <c r="J72">
+        <v>3.716666666666667</v>
+      </c>
+      <c r="K72">
+        <v>0.8799999999999999</v>
+      </c>
+      <c r="L72">
+        <v>2.836666666666667</v>
+      </c>
+      <c r="M72">
+        <v>1.7785824</v>
+      </c>
+      <c r="N72">
+        <v>1.058084266666667</v>
+      </c>
+      <c r="O72">
+        <v>0.2116168533333333</v>
+      </c>
+      <c r="P72">
+        <v>0.8464674133333332</v>
+      </c>
+      <c r="Q72">
+        <v>1.726467413333333</v>
+      </c>
+      <c r="R72">
+        <v>2.333333333333334</v>
+      </c>
+      <c r="S72">
+        <v>0.3071734592656873</v>
+      </c>
+      <c r="T72">
+        <v>2.981781120218301</v>
+      </c>
+      <c r="U72">
+        <v>0.0912</v>
+      </c>
+      <c r="V72">
+        <v>0.2</v>
+      </c>
+      <c r="W72">
+        <v>0.07296000000000001</v>
+      </c>
+      <c r="X72" t="inlineStr">
+        <is>
+          <t>B3/B-</t>
+        </is>
+      </c>
+      <c r="Y72">
+        <v>1.594903146835742</v>
+      </c>
+      <c r="Z72">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73">
+        <v>0.71</v>
+      </c>
+      <c r="B73">
+        <v>0.1433784004825441</v>
+      </c>
+      <c r="C73">
+        <v>6.053953002430841</v>
+      </c>
+      <c r="D73">
+        <v>22.46455300243084</v>
+      </c>
+      <c r="E73">
+        <v>12.9206</v>
+      </c>
+      <c r="F73">
+        <v>19.7806</v>
+      </c>
+      <c r="G73">
+        <v>3.37</v>
+      </c>
+      <c r="H73">
+        <v>21</v>
+      </c>
+      <c r="I73">
+        <v>0</v>
+      </c>
+      <c r="J73">
+        <v>3.716666666666667</v>
+      </c>
+      <c r="K73">
+        <v>0.8799999999999999</v>
+      </c>
+      <c r="L73">
+        <v>2.836666666666667</v>
+      </c>
+      <c r="M73">
+        <v>1.80399072</v>
+      </c>
+      <c r="N73">
+        <v>1.032675946666667</v>
+      </c>
+      <c r="O73">
+        <v>0.2065351893333334</v>
+      </c>
+      <c r="P73">
+        <v>0.8261407573333335</v>
+      </c>
+      <c r="Q73">
+        <v>1.706140757333333</v>
+      </c>
+      <c r="R73">
+        <v>2.448275862068965</v>
+      </c>
+      <c r="S73">
+        <v>0.3157820706294623</v>
+      </c>
+      <c r="T73">
+        <v>3.077427667779433</v>
+      </c>
+      <c r="U73">
+        <v>0.0912</v>
+      </c>
+      <c r="V73">
+        <v>0.2</v>
+      </c>
+      <c r="W73">
+        <v>0.07296000000000001</v>
+      </c>
+      <c r="X73" t="inlineStr">
+        <is>
+          <t>B3/B-</t>
+        </is>
+      </c>
+      <c r="Y73">
+        <v>1.572439722232422</v>
+      </c>
+      <c r="Z73">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74">
+        <v>0.72</v>
+      </c>
+      <c r="B74">
+        <v>0.143532763185382</v>
+      </c>
+      <c r="C74">
+        <v>5.742243123401266</v>
+      </c>
+      <c r="D74">
+        <v>22.43144312340127</v>
+      </c>
+      <c r="E74">
+        <v>13.1992</v>
+      </c>
+      <c r="F74">
+        <v>20.0592</v>
+      </c>
+      <c r="G74">
+        <v>3.37</v>
+      </c>
+      <c r="H74">
+        <v>21</v>
+      </c>
+      <c r="I74">
+        <v>0</v>
+      </c>
+      <c r="J74">
+        <v>3.716666666666667</v>
+      </c>
+      <c r="K74">
+        <v>0.8799999999999999</v>
+      </c>
+      <c r="L74">
+        <v>2.836666666666667</v>
+      </c>
+      <c r="M74">
+        <v>1.82939904</v>
+      </c>
+      <c r="N74">
+        <v>1.007267626666667</v>
+      </c>
+      <c r="O74">
+        <v>0.2014535253333334</v>
+      </c>
+      <c r="P74">
+        <v>0.8058141013333333</v>
+      </c>
+      <c r="Q74">
+        <v>1.685814101333333</v>
+      </c>
+      <c r="R74">
+        <v>2.571428571428571</v>
+      </c>
+      <c r="S74">
+        <v>0.3250055828049356</v>
+      </c>
+      <c r="T74">
+        <v>3.179906111594932</v>
+      </c>
+      <c r="U74">
+        <v>0.0912</v>
+      </c>
+      <c r="V74">
+        <v>0.2</v>
+      </c>
+      <c r="W74">
+        <v>0.07296000000000001</v>
+      </c>
+      <c r="X74" t="inlineStr">
+        <is>
+          <t>B3/B-</t>
+        </is>
+      </c>
+      <c r="Y74">
+        <v>1.55060028164586</v>
+      </c>
+      <c r="Z74">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75">
+        <v>0.73</v>
+      </c>
+      <c r="B75">
+        <v>0.1436871258882199</v>
+      </c>
+      <c r="C75">
+        <v>5.430630700191465</v>
+      </c>
+      <c r="D75">
+        <v>22.39843070019146</v>
+      </c>
+      <c r="E75">
+        <v>13.4778</v>
+      </c>
+      <c r="F75">
+        <v>20.3378</v>
+      </c>
+      <c r="G75">
+        <v>3.37</v>
+      </c>
+      <c r="H75">
+        <v>21</v>
+      </c>
+      <c r="I75">
+        <v>0</v>
+      </c>
+      <c r="J75">
+        <v>3.716666666666667</v>
+      </c>
+      <c r="K75">
+        <v>0.8799999999999999</v>
+      </c>
+      <c r="L75">
+        <v>2.836666666666667</v>
+      </c>
+      <c r="M75">
+        <v>1.85480736</v>
+      </c>
+      <c r="N75">
+        <v>0.981859306666667</v>
+      </c>
+      <c r="O75">
+        <v>0.1963718613333334</v>
+      </c>
+      <c r="P75">
+        <v>0.7854874453333336</v>
+      </c>
+      <c r="Q75">
+        <v>1.665487445333333</v>
+      </c>
+      <c r="R75">
+        <v>2.703703703703703</v>
+      </c>
+      <c r="S75">
+        <v>0.334912318104518</v>
+      </c>
+      <c r="T75">
+        <v>3.289975551248616</v>
+      </c>
+      <c r="U75">
+        <v>0.0912</v>
+      </c>
+      <c r="V75">
+        <v>0.2</v>
+      </c>
+      <c r="W75">
+        <v>0.07296000000000001</v>
+      </c>
+      <c r="X75" t="inlineStr">
+        <is>
+          <t>B3/B-</t>
+        </is>
+      </c>
+      <c r="Y75">
+        <v>1.529359181897287</v>
+      </c>
+      <c r="Z75">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76">
+        <v>0.74</v>
+      </c>
+      <c r="B76">
+        <v>0.1438414885910578</v>
+      </c>
+      <c r="C76">
+        <v>5.119115303155635</v>
+      </c>
+      <c r="D76">
+        <v>22.36551530315563</v>
+      </c>
+      <c r="E76">
+        <v>13.7564</v>
+      </c>
+      <c r="F76">
+        <v>20.6164</v>
+      </c>
+      <c r="G76">
+        <v>3.37</v>
+      </c>
+      <c r="H76">
+        <v>21</v>
+      </c>
+      <c r="I76">
+        <v>0</v>
+      </c>
+      <c r="J76">
+        <v>3.716666666666667</v>
+      </c>
+      <c r="K76">
+        <v>0.8799999999999999</v>
+      </c>
+      <c r="L76">
+        <v>2.836666666666667</v>
+      </c>
+      <c r="M76">
+        <v>1.88021568</v>
+      </c>
+      <c r="N76">
+        <v>0.9564509866666668</v>
+      </c>
+      <c r="O76">
+        <v>0.1912901973333334</v>
+      </c>
+      <c r="P76">
+        <v>0.7651607893333334</v>
+      </c>
+      <c r="Q76">
+        <v>1.645160789333333</v>
+      </c>
+      <c r="R76">
+        <v>2.846153846153846</v>
+      </c>
+      <c r="S76">
+        <v>0.3455811099656068</v>
+      </c>
+      <c r="T76">
+        <v>3.408511870875661</v>
+      </c>
+      <c r="U76">
+        <v>0.0912</v>
+      </c>
+      <c r="V76">
+        <v>0.2</v>
+      </c>
+      <c r="W76">
+        <v>0.07296000000000001</v>
+      </c>
+      <c r="X76" t="inlineStr">
+        <is>
+          <t>B3/B-</t>
+        </is>
+      </c>
+      <c r="Y76">
+        <v>1.508692165925702</v>
+      </c>
+      <c r="Z76">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77">
+        <v>0.75</v>
+      </c>
+      <c r="B77">
+        <v>0.1882310793350676</v>
+      </c>
+      <c r="C77">
+        <v>-1.80332395373571</v>
+      </c>
+      <c r="D77">
+        <v>15.72167604626429</v>
+      </c>
+      <c r="E77">
+        <v>14.035</v>
+      </c>
+      <c r="F77">
+        <v>20.895</v>
+      </c>
+      <c r="G77">
+        <v>3.37</v>
+      </c>
+      <c r="H77">
+        <v>21</v>
+      </c>
+      <c r="I77">
+        <v>0</v>
+      </c>
+      <c r="J77">
+        <v>3.716666666666667</v>
+      </c>
+      <c r="K77">
+        <v>0.8799999999999999</v>
+      </c>
+      <c r="L77">
+        <v>2.836666666666667</v>
+      </c>
+      <c r="M77">
+        <v>3.272157</v>
+      </c>
+      <c r="N77">
+        <v>-0.4354903333333335</v>
+      </c>
+      <c r="O77">
+        <v>-0.08709806666666671</v>
+      </c>
+      <c r="P77">
+        <v>-0.3483922666666668</v>
+      </c>
+      <c r="Q77">
+        <v>0.5316077333333331</v>
+      </c>
+      <c r="R77">
+        <v>3</v>
+      </c>
+      <c r="S77">
+        <v>0.3645792108554652</v>
+      </c>
+      <c r="T77">
+        <v>3.619591530944807</v>
+      </c>
+      <c r="U77">
+        <v>0.1566</v>
+      </c>
+      <c r="V77">
+        <v>0.1733820636764475</v>
+      </c>
+      <c r="W77">
+        <v>0.1294483688282684</v>
+      </c>
+      <c r="X77" t="inlineStr">
+        <is>
+          <t>Ca2/CC</t>
+        </is>
+      </c>
+      <c r="Y77">
+        <v>0.8669103183822373</v>
+      </c>
+      <c r="Z77">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78">
+        <v>0.76</v>
+      </c>
+      <c r="B78">
+        <v>0.1894090793350676</v>
+      </c>
+      <c r="C78">
+        <v>-2.204892200167233</v>
+      </c>
+      <c r="D78">
+        <v>15.59870779983277</v>
+      </c>
+      <c r="E78">
+        <v>14.3136</v>
+      </c>
+      <c r="F78">
+        <v>21.1736</v>
+      </c>
+      <c r="G78">
+        <v>3.37</v>
+      </c>
+      <c r="H78">
+        <v>21</v>
+      </c>
+      <c r="I78">
+        <v>0</v>
+      </c>
+      <c r="J78">
+        <v>3.716666666666667</v>
+      </c>
+      <c r="K78">
+        <v>0.8799999999999999</v>
+      </c>
+      <c r="L78">
+        <v>2.836666666666667</v>
+      </c>
+      <c r="M78">
+        <v>3.31578576</v>
+      </c>
+      <c r="N78">
+        <v>-0.4791190933333334</v>
+      </c>
+      <c r="O78">
+        <v>-0.09582381866666667</v>
+      </c>
+      <c r="P78">
+        <v>-0.3832952746666667</v>
+      </c>
+      <c r="Q78">
+        <v>0.4967047253333332</v>
+      </c>
+      <c r="R78">
+        <v>3.166666666666667</v>
+      </c>
+      <c r="S78">
+        <v>0.3781533446411096</v>
+      </c>
+      <c r="T78">
+        <v>3.770407844734175</v>
+      </c>
+      <c r="U78">
+        <v>0.1566</v>
+      </c>
+      <c r="V78">
+        <v>0.1711007207333363</v>
+      </c>
+      <c r="W78">
+        <v>0.1298056271331595</v>
+      </c>
+      <c r="X78" t="inlineStr">
+        <is>
+          <t>Ca2/CC</t>
+        </is>
+      </c>
+      <c r="Y78">
+        <v>0.8555036036666817</v>
+      </c>
+      <c r="Z78">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79">
+        <v>0.77</v>
+      </c>
+      <c r="B79">
+        <v>0.1905870793350675</v>
+      </c>
+      <c r="C79">
+        <v>-2.604551765109779</v>
+      </c>
+      <c r="D79">
+        <v>15.47764823489022</v>
+      </c>
+      <c r="E79">
+        <v>14.5922</v>
+      </c>
+      <c r="F79">
+        <v>21.4522</v>
+      </c>
+      <c r="G79">
+        <v>3.37</v>
+      </c>
+      <c r="H79">
+        <v>21</v>
+      </c>
+      <c r="I79">
+        <v>0</v>
+      </c>
+      <c r="J79">
+        <v>3.716666666666667</v>
+      </c>
+      <c r="K79">
+        <v>0.8799999999999999</v>
+      </c>
+      <c r="L79">
+        <v>2.836666666666667</v>
+      </c>
+      <c r="M79">
+        <v>3.359414520000001</v>
+      </c>
+      <c r="N79">
+        <v>-0.5227478533333336</v>
+      </c>
+      <c r="O79">
+        <v>-0.1045495706666667</v>
+      </c>
+      <c r="P79">
+        <v>-0.4181982826666669</v>
+      </c>
+      <c r="Q79">
+        <v>0.461801717333333</v>
+      </c>
+      <c r="R79">
+        <v>3.347826086956522</v>
+      </c>
+      <c r="S79">
+        <v>0.3929078378863752</v>
+      </c>
+      <c r="T79">
+        <v>3.934338620592182</v>
+      </c>
+      <c r="U79">
+        <v>0.1566</v>
+      </c>
+      <c r="V79">
+        <v>0.1688786334510852</v>
+      </c>
+      <c r="W79">
+        <v>0.1301536060015601</v>
+      </c>
+      <c r="X79" t="inlineStr">
+        <is>
+          <t>Ca2/CC</t>
+        </is>
+      </c>
+      <c r="Y79">
+        <v>0.8443931672554259</v>
+      </c>
+      <c r="Z79">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80">
+        <v>0.78</v>
+      </c>
+      <c r="B80">
+        <v>0.1917650793350676</v>
+      </c>
+      <c r="C80">
+        <v>-3.002346745427882</v>
+      </c>
+      <c r="D80">
+        <v>15.35845325457212</v>
+      </c>
+      <c r="E80">
+        <v>14.8708</v>
+      </c>
+      <c r="F80">
+        <v>21.7308</v>
+      </c>
+      <c r="G80">
+        <v>3.37</v>
+      </c>
+      <c r="H80">
+        <v>21</v>
+      </c>
+      <c r="I80">
+        <v>0</v>
+      </c>
+      <c r="J80">
+        <v>3.716666666666667</v>
+      </c>
+      <c r="K80">
+        <v>0.8799999999999999</v>
+      </c>
+      <c r="L80">
+        <v>2.836666666666667</v>
+      </c>
+      <c r="M80">
+        <v>3.40304328</v>
+      </c>
+      <c r="N80">
+        <v>-0.5663766133333334</v>
+      </c>
+      <c r="O80">
+        <v>-0.1132753226666667</v>
+      </c>
+      <c r="P80">
+        <v>-0.4531012906666668</v>
+      </c>
+      <c r="Q80">
+        <v>0.4268987093333331</v>
+      </c>
+      <c r="R80">
+        <v>3.545454545454546</v>
+      </c>
+      <c r="S80">
+        <v>0.4090036486993923</v>
+      </c>
+      <c r="T80">
+        <v>4.113172194255464</v>
+      </c>
+      <c r="U80">
+        <v>0.1566</v>
+      </c>
+      <c r="V80">
+        <v>0.1667135227658149</v>
+      </c>
+      <c r="W80">
+        <v>0.1304926623348734</v>
+      </c>
+      <c r="X80" t="inlineStr">
+        <is>
+          <t>Ca2/CC</t>
+        </is>
+      </c>
+      <c r="Y80">
+        <v>0.8335676138290744</v>
+      </c>
+      <c r="Z80">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81">
+        <v>0.79</v>
+      </c>
+      <c r="B81">
+        <v>0.1929430793350675</v>
+      </c>
+      <c r="C81">
+        <v>-3.398319889988969</v>
+      </c>
+      <c r="D81">
+        <v>15.24108011001103</v>
+      </c>
+      <c r="E81">
+        <v>15.1494</v>
+      </c>
+      <c r="F81">
+        <v>22.0094</v>
+      </c>
+      <c r="G81">
+        <v>3.37</v>
+      </c>
+      <c r="H81">
+        <v>21</v>
+      </c>
+      <c r="I81">
+        <v>0</v>
+      </c>
+      <c r="J81">
+        <v>3.716666666666667</v>
+      </c>
+      <c r="K81">
+        <v>0.8799999999999999</v>
+      </c>
+      <c r="L81">
+        <v>2.836666666666667</v>
+      </c>
+      <c r="M81">
+        <v>3.44667204</v>
+      </c>
+      <c r="N81">
+        <v>-0.6100053733333333</v>
+      </c>
+      <c r="O81">
+        <v>-0.1220010746666667</v>
+      </c>
+      <c r="P81">
+        <v>-0.4880042986666666</v>
+      </c>
+      <c r="Q81">
+        <v>0.3919957013333333</v>
+      </c>
+      <c r="R81">
+        <v>3.761904761904763</v>
+      </c>
+      <c r="S81">
+        <v>0.4266323938755539</v>
+      </c>
+      <c r="T81">
+        <v>4.309037536839058</v>
+      </c>
+      <c r="U81">
+        <v>0.1566</v>
+      </c>
+      <c r="V81">
+        <v>0.1646032250092856</v>
+      </c>
+      <c r="W81">
+        <v>0.1308231349635459</v>
+      </c>
+      <c r="X81" t="inlineStr">
+        <is>
+          <t>Ca2/CC</t>
+        </is>
+      </c>
+      <c r="Y81">
+        <v>0.8230161250464278</v>
+      </c>
+      <c r="Z81">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82">
+        <v>0.8</v>
+      </c>
+      <c r="B82">
+        <v>0.1941210793350676</v>
+      </c>
+      <c r="C82">
+        <v>-3.792512650781351</v>
+      </c>
+      <c r="D82">
+        <v>15.12548734921865</v>
+      </c>
+      <c r="E82">
+        <v>15.428</v>
+      </c>
+      <c r="F82">
+        <v>22.288</v>
+      </c>
+      <c r="G82">
+        <v>3.37</v>
+      </c>
+      <c r="H82">
+        <v>21</v>
+      </c>
+      <c r="I82">
+        <v>0</v>
+      </c>
+      <c r="J82">
+        <v>3.716666666666667</v>
+      </c>
+      <c r="K82">
+        <v>0.8799999999999999</v>
+      </c>
+      <c r="L82">
+        <v>2.836666666666667</v>
+      </c>
+      <c r="M82">
+        <v>3.4903008</v>
+      </c>
+      <c r="N82">
+        <v>-0.6536341333333335</v>
+      </c>
+      <c r="O82">
+        <v>-0.1307268266666667</v>
+      </c>
+      <c r="P82">
+        <v>-0.5229073066666668</v>
+      </c>
+      <c r="Q82">
+        <v>0.357092693333333</v>
+      </c>
+      <c r="R82">
+        <v>4.000000000000001</v>
+      </c>
+      <c r="S82">
+        <v>0.4460240135693316</v>
+      </c>
+      <c r="T82">
+        <v>4.52448941368101</v>
+      </c>
+      <c r="U82">
+        <v>0.1566</v>
+      </c>
+      <c r="V82">
+        <v>0.1625456846966695</v>
+      </c>
+      <c r="W82">
+        <v>0.1311453457765016</v>
+      </c>
+      <c r="X82" t="inlineStr">
+        <is>
+          <t>Ca2/CC</t>
+        </is>
+      </c>
+      <c r="Y82">
+        <v>0.8127284234833475</v>
+      </c>
+      <c r="Z82">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83">
+        <v>0.8100000000000001</v>
+      </c>
+      <c r="B83">
+        <v>0.1952990793350676</v>
+      </c>
+      <c r="C83">
+        <v>-4.184965231723581</v>
+      </c>
+      <c r="D83">
+        <v>15.01163476827642</v>
+      </c>
+      <c r="E83">
+        <v>15.7066</v>
+      </c>
+      <c r="F83">
+        <v>22.5666</v>
+      </c>
+      <c r="G83">
+        <v>3.37</v>
+      </c>
+      <c r="H83">
+        <v>21</v>
+      </c>
+      <c r="I83">
+        <v>0</v>
+      </c>
+      <c r="J83">
+        <v>3.716666666666667</v>
+      </c>
+      <c r="K83">
+        <v>0.8799999999999999</v>
+      </c>
+      <c r="L83">
+        <v>2.836666666666667</v>
+      </c>
+      <c r="M83">
+        <v>3.533929560000001</v>
+      </c>
+      <c r="N83">
+        <v>-0.6972628933333338</v>
+      </c>
+      <c r="O83">
+        <v>-0.1394525786666668</v>
+      </c>
+      <c r="P83">
+        <v>-0.5578103146666671</v>
+      </c>
+      <c r="Q83">
+        <v>0.3221896853333328</v>
+      </c>
+      <c r="R83">
+        <v>4.263157894736843</v>
+      </c>
+      <c r="S83">
+        <v>0.4674568563887701</v>
+      </c>
+      <c r="T83">
+        <v>4.762620435453695</v>
+      </c>
+      <c r="U83">
+        <v>0.1566</v>
+      </c>
+      <c r="V83">
+        <v>0.1605389478485625</v>
+      </c>
+      <c r="W83">
+        <v>0.1314596007669151</v>
+      </c>
+      <c r="X83" t="inlineStr">
+        <is>
+          <t>Ca2/CC</t>
+        </is>
+      </c>
+      <c r="Y83">
+        <v>0.8026947392428123</v>
+      </c>
+      <c r="Z83">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84">
+        <v>0.8200000000000001</v>
+      </c>
+      <c r="B84">
+        <v>0.2423245408018644</v>
+      </c>
+      <c r="C84">
+        <v>-7.932085782453864</v>
+      </c>
+      <c r="D84">
+        <v>11.54311421754614</v>
+      </c>
+      <c r="E84">
+        <v>15.9852</v>
+      </c>
+      <c r="F84">
+        <v>22.8452</v>
+      </c>
+      <c r="G84">
+        <v>3.37</v>
+      </c>
+      <c r="H84">
+        <v>21</v>
+      </c>
+      <c r="I84">
+        <v>0</v>
+      </c>
+      <c r="J84">
+        <v>3.716666666666667</v>
+      </c>
+      <c r="K84">
+        <v>0.8799999999999999</v>
+      </c>
+      <c r="L84">
+        <v>2.836666666666667</v>
+      </c>
+      <c r="M84">
+        <v>4.77007776</v>
+      </c>
+      <c r="N84">
+        <v>-1.933411093333333</v>
+      </c>
+      <c r="O84">
+        <v>-0.3866822186666667</v>
+      </c>
+      <c r="P84">
+        <v>-1.546728874666667</v>
+      </c>
+      <c r="Q84">
+        <v>-0.6667288746666669</v>
+      </c>
+      <c r="R84">
+        <v>4.555555555555557</v>
+      </c>
+      <c r="S84">
+        <v>0.5081792454481289</v>
+      </c>
+      <c r="T84">
+        <v>5.21506924018878</v>
+      </c>
+      <c r="U84">
+        <v>0.2088</v>
+      </c>
+      <c r="V84">
+        <v>0.1189358668512216</v>
+      </c>
+      <c r="W84">
+        <v>0.1839661910014649</v>
+      </c>
+      <c r="X84" t="inlineStr">
+        <is>
+          <t>C2/C</t>
+        </is>
+      </c>
+      <c r="Y84">
+        <v>0.594679334256108</v>
+      </c>
+      <c r="Z84">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85">
+        <v>0.8300000000000001</v>
+      </c>
+      <c r="B85">
+        <v>0.2440245408018644</v>
+      </c>
+      <c r="C85">
+        <v>-8.306304435530905</v>
+      </c>
+      <c r="D85">
+        <v>11.4474955644691</v>
+      </c>
+      <c r="E85">
+        <v>16.2638</v>
+      </c>
+      <c r="F85">
+        <v>23.1238</v>
+      </c>
+      <c r="G85">
+        <v>3.37</v>
+      </c>
+      <c r="H85">
+        <v>21</v>
+      </c>
+      <c r="I85">
+        <v>0</v>
+      </c>
+      <c r="J85">
+        <v>3.716666666666667</v>
+      </c>
+      <c r="K85">
+        <v>0.8799999999999999</v>
+      </c>
+      <c r="L85">
+        <v>2.836666666666667</v>
+      </c>
+      <c r="M85">
+        <v>4.828249440000001</v>
+      </c>
+      <c r="N85">
+        <v>-1.991582773333334</v>
+      </c>
+      <c r="O85">
+        <v>-0.3983165546666669</v>
+      </c>
+      <c r="P85">
+        <v>-1.593266218666668</v>
+      </c>
+      <c r="Q85">
+        <v>-0.7132662186666676</v>
+      </c>
+      <c r="R85">
+        <v>4.882352941176473</v>
+      </c>
+      <c r="S85">
+        <v>0.5357897892980188</v>
+      </c>
+      <c r="T85">
+        <v>5.521838019023414</v>
+      </c>
+      <c r="U85">
+        <v>0.2088</v>
+      </c>
+      <c r="V85">
+        <v>0.117502904600002</v>
+      </c>
+      <c r="W85">
+        <v>0.1842653935195196</v>
+      </c>
+      <c r="X85" t="inlineStr">
+        <is>
+          <t>C2/C</t>
+        </is>
+      </c>
+      <c r="Y85">
+        <v>0.5875145230000102</v>
+      </c>
+      <c r="Z85">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86">
+        <v>0.84</v>
+      </c>
+      <c r="B86">
+        <v>0.2457245408018644</v>
+      </c>
+      <c r="C86">
+        <v>-8.678951967951097</v>
+      </c>
+      <c r="D86">
+        <v>11.3534480320489</v>
+      </c>
+      <c r="E86">
+        <v>16.5424</v>
+      </c>
+      <c r="F86">
+        <v>23.4024</v>
+      </c>
+      <c r="G86">
+        <v>3.37</v>
+      </c>
+      <c r="H86">
+        <v>21</v>
+      </c>
+      <c r="I86">
+        <v>0</v>
+      </c>
+      <c r="J86">
+        <v>3.716666666666667</v>
+      </c>
+      <c r="K86">
+        <v>0.8799999999999999</v>
+      </c>
+      <c r="L86">
+        <v>2.836666666666667</v>
+      </c>
+      <c r="M86">
+        <v>4.886421120000001</v>
+      </c>
+      <c r="N86">
+        <v>-2.049754453333334</v>
+      </c>
+      <c r="O86">
+        <v>-0.4099508906666667</v>
+      </c>
+      <c r="P86">
+        <v>-1.639803562666667</v>
+      </c>
+      <c r="Q86">
+        <v>-0.759803562666667</v>
+      </c>
+      <c r="R86">
+        <v>5.249999999999999</v>
+      </c>
+      <c r="S86">
+        <v>0.5668516511291446</v>
+      </c>
+      <c r="T86">
+        <v>5.866952895212375</v>
+      </c>
+      <c r="U86">
+        <v>0.2088</v>
+      </c>
+      <c r="V86">
+        <v>0.1161040604976211</v>
+      </c>
+      <c r="W86">
+        <v>0.1845574721680967</v>
+      </c>
+      <c r="X86" t="inlineStr">
+        <is>
+          <t>C2/C</t>
+        </is>
+      </c>
+      <c r="Y86">
+        <v>0.5805203024881054</v>
+      </c>
+      <c r="Z86">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87">
+        <v>0.85</v>
+      </c>
+      <c r="B87">
+        <v>0.2474245408018644</v>
+      </c>
+      <c r="C87">
+        <v>-9.050066787062491</v>
+      </c>
+      <c r="D87">
+        <v>11.26093321293751</v>
+      </c>
+      <c r="E87">
+        <v>16.821</v>
+      </c>
+      <c r="F87">
+        <v>23.681</v>
+      </c>
+      <c r="G87">
+        <v>3.37</v>
+      </c>
+      <c r="H87">
+        <v>21</v>
+      </c>
+      <c r="I87">
+        <v>0</v>
+      </c>
+      <c r="J87">
+        <v>3.716666666666667</v>
+      </c>
+      <c r="K87">
+        <v>0.8799999999999999</v>
+      </c>
+      <c r="L87">
+        <v>2.836666666666667</v>
+      </c>
+      <c r="M87">
+        <v>4.9445928</v>
+      </c>
+      <c r="N87">
+        <v>-2.107926133333333</v>
+      </c>
+      <c r="O87">
+        <v>-0.4215852266666666</v>
+      </c>
+      <c r="P87">
+        <v>-1.686340906666666</v>
+      </c>
+      <c r="Q87">
+        <v>-0.8063409066666662</v>
+      </c>
+      <c r="R87">
+        <v>5.666666666666666</v>
+      </c>
+      <c r="S87">
+        <v>0.6020550945377543</v>
+      </c>
+      <c r="T87">
+        <v>6.258083088226533</v>
+      </c>
+      <c r="U87">
+        <v>0.2088</v>
+      </c>
+      <c r="V87">
+        <v>0.1147381303741197</v>
+      </c>
+      <c r="W87">
+        <v>0.1848426783778838</v>
+      </c>
+      <c r="X87" t="inlineStr">
+        <is>
+          <t>C2/C</t>
+        </is>
+      </c>
+      <c r="Y87">
+        <v>0.5736906518705983</v>
+      </c>
+      <c r="Z87">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88">
+        <v>0.86</v>
+      </c>
+      <c r="B88">
+        <v>0.2491245408018644</v>
+      </c>
+      <c r="C88">
+        <v>-9.419686058465675</v>
+      </c>
+      <c r="D88">
+        <v>11.16991394153432</v>
+      </c>
+      <c r="E88">
+        <v>17.0996</v>
+      </c>
+      <c r="F88">
+        <v>23.9596</v>
+      </c>
+      <c r="G88">
+        <v>3.37</v>
+      </c>
+      <c r="H88">
+        <v>21</v>
+      </c>
+      <c r="I88">
+        <v>0</v>
+      </c>
+      <c r="J88">
+        <v>3.716666666666667</v>
+      </c>
+      <c r="K88">
+        <v>0.8799999999999999</v>
+      </c>
+      <c r="L88">
+        <v>2.836666666666667</v>
+      </c>
+      <c r="M88">
+        <v>5.00276448</v>
+      </c>
+      <c r="N88">
+        <v>-2.166097813333333</v>
+      </c>
+      <c r="O88">
+        <v>-0.4332195626666666</v>
+      </c>
+      <c r="P88">
+        <v>-1.732878250666666</v>
+      </c>
+      <c r="Q88">
+        <v>-0.8528782506666663</v>
+      </c>
+      <c r="R88">
+        <v>6.142857142857142</v>
+      </c>
+      <c r="S88">
+        <v>0.642287601290451</v>
+      </c>
+      <c r="T88">
+        <v>6.705089023099856</v>
+      </c>
+      <c r="U88">
+        <v>0.2088</v>
+      </c>
+      <c r="V88">
+        <v>0.1134039660674439</v>
+      </c>
+      <c r="W88">
+        <v>0.1851212518851177</v>
+      </c>
+      <c r="X88" t="inlineStr">
+        <is>
+          <t>C2/C</t>
+        </is>
+      </c>
+      <c r="Y88">
+        <v>0.5670198303372193</v>
+      </c>
+      <c r="Z88">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89">
+        <v>0.87</v>
+      </c>
+      <c r="B89">
+        <v>0.2508245408018644</v>
+      </c>
+      <c r="C89">
+        <v>-9.787845755795018</v>
+      </c>
+      <c r="D89">
+        <v>11.08035424420498</v>
+      </c>
+      <c r="E89">
+        <v>17.3782</v>
+      </c>
+      <c r="F89">
+        <v>24.2382</v>
+      </c>
+      <c r="G89">
+        <v>3.37</v>
+      </c>
+      <c r="H89">
+        <v>21</v>
+      </c>
+      <c r="I89">
+        <v>0</v>
+      </c>
+      <c r="J89">
+        <v>3.716666666666667</v>
+      </c>
+      <c r="K89">
+        <v>0.8799999999999999</v>
+      </c>
+      <c r="L89">
+        <v>2.836666666666667</v>
+      </c>
+      <c r="M89">
+        <v>5.06093616</v>
+      </c>
+      <c r="N89">
+        <v>-2.224269493333333</v>
+      </c>
+      <c r="O89">
+        <v>-0.4448538986666666</v>
+      </c>
+      <c r="P89">
+        <v>-1.779415594666666</v>
+      </c>
+      <c r="Q89">
+        <v>-0.8994155946666664</v>
+      </c>
+      <c r="R89">
+        <v>6.692307692307692</v>
+      </c>
+      <c r="S89">
+        <v>0.6887097244666396</v>
+      </c>
+      <c r="T89">
+        <v>7.220865101799846</v>
+      </c>
+      <c r="U89">
+        <v>0.2088</v>
+      </c>
+      <c r="V89">
+        <v>0.1121004722045997</v>
+      </c>
+      <c r="W89">
+        <v>0.1853934214036796</v>
+      </c>
+      <c r="X89" t="inlineStr">
+        <is>
+          <t>C2/C</t>
+        </is>
+      </c>
+      <c r="Y89">
+        <v>0.5605023610229984</v>
+      </c>
+      <c r="Z89">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90">
+        <v>0.88</v>
+      </c>
+      <c r="B90">
+        <v>0.2525245408018644</v>
+      </c>
+      <c r="C90">
+        <v>-10.1545807081242</v>
+      </c>
+      <c r="D90">
+        <v>10.9922192918758</v>
+      </c>
+      <c r="E90">
+        <v>17.6568</v>
+      </c>
+      <c r="F90">
+        <v>24.5168</v>
+      </c>
+      <c r="G90">
+        <v>3.37</v>
+      </c>
+      <c r="H90">
+        <v>21</v>
+      </c>
+      <c r="I90">
+        <v>0</v>
+      </c>
+      <c r="J90">
+        <v>3.716666666666667</v>
+      </c>
+      <c r="K90">
+        <v>0.8799999999999999</v>
+      </c>
+      <c r="L90">
+        <v>2.836666666666667</v>
+      </c>
+      <c r="M90">
+        <v>5.119107840000001</v>
+      </c>
+      <c r="N90">
+        <v>-2.282441173333334</v>
+      </c>
+      <c r="O90">
+        <v>-0.4564882346666668</v>
+      </c>
+      <c r="P90">
+        <v>-1.825952938666667</v>
+      </c>
+      <c r="Q90">
+        <v>-0.9459529386666672</v>
+      </c>
+      <c r="R90">
+        <v>7.333333333333334</v>
+      </c>
+      <c r="S90">
+        <v>0.7428688681721931</v>
+      </c>
+      <c r="T90">
+        <v>7.822603860283167</v>
+      </c>
+      <c r="U90">
+        <v>0.2088</v>
+      </c>
+      <c r="V90">
+        <v>0.1108266032022747</v>
+      </c>
+      <c r="W90">
+        <v>0.1856594052513651</v>
+      </c>
+      <c r="X90" t="inlineStr">
+        <is>
+          <t>C2/C</t>
+        </is>
+      </c>
+      <c r="Y90">
+        <v>0.5541330160113733</v>
+      </c>
+      <c r="Z90">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91">
+        <v>0.89</v>
+      </c>
+      <c r="B91">
+        <v>0.2542245408018644</v>
+      </c>
+      <c r="C91">
+        <v>-10.51992464512707</v>
+      </c>
+      <c r="D91">
+        <v>10.90547535487293</v>
+      </c>
+      <c r="E91">
+        <v>17.9354</v>
+      </c>
+      <c r="F91">
+        <v>24.7954</v>
+      </c>
+      <c r="G91">
+        <v>3.37</v>
+      </c>
+      <c r="H91">
+        <v>21</v>
+      </c>
+      <c r="I91">
+        <v>0</v>
+      </c>
+      <c r="J91">
+        <v>3.716666666666667</v>
+      </c>
+      <c r="K91">
+        <v>0.8799999999999999</v>
+      </c>
+      <c r="L91">
+        <v>2.836666666666667</v>
+      </c>
+      <c r="M91">
+        <v>5.177279520000001</v>
+      </c>
+      <c r="N91">
+        <v>-2.340612853333334</v>
+      </c>
+      <c r="O91">
+        <v>-0.4681225706666668</v>
+      </c>
+      <c r="P91">
+        <v>-1.872490282666667</v>
+      </c>
+      <c r="Q91">
+        <v>-0.9924902826666673</v>
+      </c>
+      <c r="R91">
+        <v>8.090909090909092</v>
+      </c>
+      <c r="S91">
+        <v>0.8068751289151197</v>
+      </c>
+      <c r="T91">
+        <v>8.533749665763455</v>
+      </c>
+      <c r="U91">
+        <v>0.2088</v>
+      </c>
+      <c r="V91">
+        <v>0.1095813604696648</v>
+      </c>
+      <c r="W91">
+        <v>0.185919411933934</v>
+      </c>
+      <c r="X91" t="inlineStr">
+        <is>
+          <t>C2/C</t>
+        </is>
+      </c>
+      <c r="Y91">
+        <v>0.5479068023483241</v>
+      </c>
+      <c r="Z91">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92">
+        <v>0.9</v>
+      </c>
+      <c r="B92">
+        <v>0.2559245408018644</v>
+      </c>
+      <c r="C92">
+        <v>-10.88391024011701</v>
+      </c>
+      <c r="D92">
+        <v>10.82008975988299</v>
+      </c>
+      <c r="E92">
+        <v>18.214</v>
+      </c>
+      <c r="F92">
+        <v>25.074</v>
+      </c>
+      <c r="G92">
+        <v>3.37</v>
+      </c>
+      <c r="H92">
+        <v>21</v>
+      </c>
+      <c r="I92">
+        <v>0</v>
+      </c>
+      <c r="J92">
+        <v>3.716666666666667</v>
+      </c>
+      <c r="K92">
+        <v>0.8799999999999999</v>
+      </c>
+      <c r="L92">
+        <v>2.836666666666667</v>
+      </c>
+      <c r="M92">
+        <v>5.235451200000001</v>
+      </c>
+      <c r="N92">
+        <v>-2.398784533333334</v>
+      </c>
+      <c r="O92">
+        <v>-0.4797569066666668</v>
+      </c>
+      <c r="P92">
+        <v>-1.919027626666667</v>
+      </c>
+      <c r="Q92">
+        <v>-1.039027626666667</v>
+      </c>
+      <c r="R92">
+        <v>9.000000000000002</v>
+      </c>
+      <c r="S92">
+        <v>0.8836826418066317</v>
+      </c>
+      <c r="T92">
+        <v>9.387124632339802</v>
+      </c>
+      <c r="U92">
+        <v>0.2088</v>
+      </c>
+      <c r="V92">
+        <v>0.1083637897977797</v>
+      </c>
+      <c r="W92">
+        <v>0.1861736406902236</v>
+      </c>
+      <c r="X92" t="inlineStr">
+        <is>
+          <t>C2/C</t>
+        </is>
+      </c>
+      <c r="Y92">
+        <v>0.5418189489888983</v>
+      </c>
+      <c r="Z92">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93">
+        <v>0.91</v>
+      </c>
+      <c r="B93">
+        <v>0.2576245408018644</v>
+      </c>
+      <c r="C93">
+        <v>-11.24656915108008</v>
+      </c>
+      <c r="D93">
+        <v>10.73603084891992</v>
+      </c>
+      <c r="E93">
+        <v>18.4926</v>
+      </c>
+      <c r="F93">
+        <v>25.3526</v>
+      </c>
+      <c r="G93">
+        <v>3.37</v>
+      </c>
+      <c r="H93">
+        <v>21</v>
+      </c>
+      <c r="I93">
+        <v>0</v>
+      </c>
+      <c r="J93">
+        <v>3.716666666666667</v>
+      </c>
+      <c r="K93">
+        <v>0.8799999999999999</v>
+      </c>
+      <c r="L93">
+        <v>2.836666666666667</v>
+      </c>
+      <c r="M93">
+        <v>5.29362288</v>
+      </c>
+      <c r="N93">
+        <v>-2.456956213333333</v>
+      </c>
+      <c r="O93">
+        <v>-0.4913912426666667</v>
+      </c>
+      <c r="P93">
+        <v>-1.965564970666666</v>
+      </c>
+      <c r="Q93">
+        <v>-1.085564970666667</v>
+      </c>
+      <c r="R93">
+        <v>10.11111111111111</v>
+      </c>
+      <c r="S93">
+        <v>0.9775584908962576</v>
+      </c>
+      <c r="T93">
+        <v>10.43013848037756</v>
+      </c>
+      <c r="U93">
+        <v>0.2088</v>
+      </c>
+      <c r="V93">
+        <v>0.107172978920881</v>
+      </c>
+      <c r="W93">
+        <v>0.18642228200132</v>
+      </c>
+      <c r="X93" t="inlineStr">
+        <is>
+          <t>C2/C</t>
+        </is>
+      </c>
+      <c r="Y93">
+        <v>0.535864894604405</v>
+      </c>
+      <c r="Z93">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94">
+        <v>0.92</v>
+      </c>
+      <c r="B94">
+        <v>0.2593245408018644</v>
+      </c>
+      <c r="C94">
+        <v>-11.60793205981033</v>
+      </c>
+      <c r="D94">
+        <v>10.65326794018967</v>
+      </c>
+      <c r="E94">
+        <v>18.7712</v>
+      </c>
+      <c r="F94">
+        <v>25.6312</v>
+      </c>
+      <c r="G94">
+        <v>3.37</v>
+      </c>
+      <c r="H94">
+        <v>21</v>
+      </c>
+      <c r="I94">
+        <v>0</v>
+      </c>
+      <c r="J94">
+        <v>3.716666666666667</v>
+      </c>
+      <c r="K94">
+        <v>0.8799999999999999</v>
+      </c>
+      <c r="L94">
+        <v>2.836666666666667</v>
+      </c>
+      <c r="M94">
+        <v>5.35179456</v>
+      </c>
+      <c r="N94">
+        <v>-2.515127893333333</v>
+      </c>
+      <c r="O94">
+        <v>-0.5030255786666666</v>
+      </c>
+      <c r="P94">
+        <v>-2.012102314666667</v>
+      </c>
+      <c r="Q94">
+        <v>-1.132102314666667</v>
+      </c>
+      <c r="R94">
+        <v>11.50000000000001</v>
+      </c>
+      <c r="S94">
+        <v>1.09490330225829</v>
+      </c>
+      <c r="T94">
+        <v>11.73390579042476</v>
+      </c>
+      <c r="U94">
+        <v>0.2088</v>
+      </c>
+      <c r="V94">
+        <v>0.1060080552369584</v>
+      </c>
+      <c r="W94">
+        <v>0.1866655180665231</v>
+      </c>
+      <c r="X94" t="inlineStr">
+        <is>
+          <t>C2/C</t>
+        </is>
+      </c>
+      <c r="Y94">
+        <v>0.5300402761847919</v>
+      </c>
+      <c r="Z94">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95">
+        <v>0.93</v>
+      </c>
+      <c r="B95">
+        <v>0.2610245408018644</v>
+      </c>
+      <c r="C95">
+        <v>-11.96802870924866</v>
+      </c>
+      <c r="D95">
+        <v>10.57177129075134</v>
+      </c>
+      <c r="E95">
+        <v>19.0498</v>
+      </c>
+      <c r="F95">
+        <v>25.9098</v>
+      </c>
+      <c r="G95">
+        <v>3.37</v>
+      </c>
+      <c r="H95">
+        <v>21</v>
+      </c>
+      <c r="I95">
+        <v>0</v>
+      </c>
+      <c r="J95">
+        <v>3.716666666666667</v>
+      </c>
+      <c r="K95">
+        <v>0.8799999999999999</v>
+      </c>
+      <c r="L95">
+        <v>2.836666666666667</v>
+      </c>
+      <c r="M95">
+        <v>5.40996624</v>
+      </c>
+      <c r="N95">
+        <v>-2.573299573333333</v>
+      </c>
+      <c r="O95">
+        <v>-0.5146599146666667</v>
+      </c>
+      <c r="P95">
+        <v>-2.058639658666666</v>
+      </c>
+      <c r="Q95">
+        <v>-1.178639658666667</v>
+      </c>
+      <c r="R95">
+        <v>13.2857142857143</v>
+      </c>
+      <c r="S95">
+        <v>1.245775202580903</v>
+      </c>
+      <c r="T95">
+        <v>13.41017804619972</v>
+      </c>
+      <c r="U95">
+        <v>0.2088</v>
+      </c>
+      <c r="V95">
+        <v>0.1048681836752707</v>
+      </c>
+      <c r="W95">
+        <v>0.1869035232486035</v>
+      </c>
+      <c r="X95" t="inlineStr">
+        <is>
+          <t>C2/C</t>
+        </is>
+      </c>
+      <c r="Y95">
+        <v>0.5243409183763532</v>
+      </c>
+      <c r="Z95">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96">
+        <v>0.9400000000000001</v>
+      </c>
+      <c r="B96">
+        <v>0.2627245408018644</v>
+      </c>
+      <c r="C96">
+        <v>-12.32688793912101</v>
+      </c>
+      <c r="D96">
+        <v>10.49151206087899</v>
+      </c>
+      <c r="E96">
+        <v>19.3284</v>
+      </c>
+      <c r="F96">
+        <v>26.1884</v>
+      </c>
+      <c r="G96">
+        <v>3.37</v>
+      </c>
+      <c r="H96">
+        <v>21</v>
+      </c>
+      <c r="I96">
+        <v>0</v>
+      </c>
+      <c r="J96">
+        <v>3.716666666666667</v>
+      </c>
+      <c r="K96">
+        <v>0.8799999999999999</v>
+      </c>
+      <c r="L96">
+        <v>2.836666666666667</v>
+      </c>
+      <c r="M96">
+        <v>5.468137920000001</v>
+      </c>
+      <c r="N96">
+        <v>-2.631471253333334</v>
+      </c>
+      <c r="O96">
+        <v>-0.5262942506666669</v>
+      </c>
+      <c r="P96">
+        <v>-2.105177002666667</v>
+      </c>
+      <c r="Q96">
+        <v>-1.225177002666667</v>
+      </c>
+      <c r="R96">
+        <v>15.66666666666668</v>
+      </c>
+      <c r="S96">
+        <v>1.446937736344387</v>
+      </c>
+      <c r="T96">
+        <v>15.64520772056635</v>
+      </c>
+      <c r="U96">
+        <v>0.2088</v>
+      </c>
+      <c r="V96">
+        <v>0.1037525647000018</v>
+      </c>
+      <c r="W96">
+        <v>0.1871364644906396</v>
+      </c>
+      <c r="X96" t="inlineStr">
+        <is>
+          <t>C2/C</t>
+        </is>
+      </c>
+      <c r="Y96">
+        <v>0.518762823500009</v>
+      </c>
+      <c r="Z96">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97">
+        <v>0.9500000000000001</v>
+      </c>
+      <c r="B97">
+        <v>0.2644245408018644</v>
+      </c>
+      <c r="C97">
+        <v>-12.68453771996536</v>
+      </c>
+      <c r="D97">
+        <v>10.41246228003464</v>
+      </c>
+      <c r="E97">
+        <v>19.607</v>
+      </c>
+      <c r="F97">
+        <v>26.467</v>
+      </c>
+      <c r="G97">
+        <v>3.37</v>
+      </c>
+      <c r="H97">
+        <v>21</v>
+      </c>
+      <c r="I97">
+        <v>0</v>
+      </c>
+      <c r="J97">
+        <v>3.716666666666667</v>
+      </c>
+      <c r="K97">
+        <v>0.8799999999999999</v>
+      </c>
+      <c r="L97">
+        <v>2.836666666666667</v>
+      </c>
+      <c r="M97">
+        <v>5.526309600000001</v>
+      </c>
+      <c r="N97">
+        <v>-2.689642933333334</v>
+      </c>
+      <c r="O97">
+        <v>-0.5379285866666669</v>
+      </c>
+      <c r="P97">
+        <v>-2.151714346666667</v>
+      </c>
+      <c r="Q97">
+        <v>-1.271714346666668</v>
+      </c>
+      <c r="R97">
+        <v>19.00000000000003</v>
+      </c>
+      <c r="S97">
+        <v>1.728565283613266</v>
+      </c>
+      <c r="T97">
+        <v>18.77424926467963</v>
+      </c>
+      <c r="U97">
+        <v>0.2088</v>
+      </c>
+      <c r="V97">
+        <v>0.1026604324400018</v>
+      </c>
+      <c r="W97">
+        <v>0.1873645017065276</v>
+      </c>
+      <c r="X97" t="inlineStr">
+        <is>
+          <t>C2/C</t>
+        </is>
+      </c>
+      <c r="Y97">
+        <v>0.5133021622000089</v>
+      </c>
+      <c r="Z97">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98">
+        <v>0.96</v>
+      </c>
+      <c r="B98">
+        <v>0.2661245408018644</v>
+      </c>
+      <c r="C98">
+        <v>-13.04100518563193</v>
+      </c>
+      <c r="D98">
+        <v>10.33459481436807</v>
+      </c>
+      <c r="E98">
+        <v>19.8856</v>
+      </c>
+      <c r="F98">
+        <v>26.7456</v>
+      </c>
+      <c r="G98">
+        <v>3.37</v>
+      </c>
+      <c r="H98">
+        <v>21</v>
+      </c>
+      <c r="I98">
+        <v>0</v>
+      </c>
+      <c r="J98">
+        <v>3.716666666666667</v>
+      </c>
+      <c r="K98">
+        <v>0.8799999999999999</v>
+      </c>
+      <c r="L98">
+        <v>2.836666666666667</v>
+      </c>
+      <c r="M98">
+        <v>5.58448128</v>
+      </c>
+      <c r="N98">
+        <v>-2.747814613333333</v>
+      </c>
+      <c r="O98">
+        <v>-0.5495629226666667</v>
+      </c>
+      <c r="P98">
+        <v>-2.198251690666667</v>
+      </c>
+      <c r="Q98">
+        <v>-1.318251690666667</v>
+      </c>
+      <c r="R98">
+        <v>23.99999999999998</v>
+      </c>
+      <c r="S98">
+        <v>2.151006604516577</v>
+      </c>
+      <c r="T98">
+        <v>23.46781158084948</v>
+      </c>
+      <c r="U98">
+        <v>0.2088</v>
+      </c>
+      <c r="V98">
+        <v>0.1015910529354184</v>
+      </c>
+      <c r="W98">
+        <v>0.1875877881470846</v>
+      </c>
+      <c r="X98" t="inlineStr">
+        <is>
+          <t>C2/C</t>
+        </is>
+      </c>
+      <c r="Y98">
+        <v>0.5079552646770922</v>
+      </c>
+      <c r="Z98">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99">
+        <v>0.97</v>
+      </c>
+      <c r="B99">
+        <v>0.2678245408018644</v>
+      </c>
+      <c r="C99">
+        <v>-13.39631666433598</v>
+      </c>
+      <c r="D99">
+        <v>10.25788333566402</v>
+      </c>
+      <c r="E99">
+        <v>20.1642</v>
+      </c>
+      <c r="F99">
+        <v>27.0242</v>
+      </c>
+      <c r="G99">
+        <v>3.37</v>
+      </c>
+      <c r="H99">
+        <v>21</v>
+      </c>
+      <c r="I99">
+        <v>0</v>
+      </c>
+      <c r="J99">
+        <v>3.716666666666667</v>
+      </c>
+      <c r="K99">
+        <v>0.8799999999999999</v>
+      </c>
+      <c r="L99">
+        <v>2.836666666666667</v>
+      </c>
+      <c r="M99">
+        <v>5.64265296</v>
+      </c>
+      <c r="N99">
+        <v>-2.805986293333333</v>
+      </c>
+      <c r="O99">
+        <v>-0.5611972586666667</v>
+      </c>
+      <c r="P99">
+        <v>-2.244789034666667</v>
+      </c>
+      <c r="Q99">
+        <v>-1.364789034666667</v>
+      </c>
+      <c r="R99">
+        <v>32.33333333333331</v>
+      </c>
+      <c r="S99">
+        <v>2.85507547268877</v>
+      </c>
+      <c r="T99">
+        <v>31.29041544113264</v>
+      </c>
+      <c r="U99">
+        <v>0.2088</v>
+      </c>
+      <c r="V99">
+        <v>0.1005437224927853</v>
+      </c>
+      <c r="W99">
+        <v>0.1878064707435064</v>
+      </c>
+      <c r="X99" t="inlineStr">
+        <is>
+          <t>C2/C</t>
+        </is>
+      </c>
+      <c r="Y99">
+        <v>0.5027186124639262</v>
+      </c>
+      <c r="Z99">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100">
+        <v>0.98</v>
+      </c>
+      <c r="B100">
+        <v>0.3000715740179939</v>
+      </c>
+      <c r="C100">
+        <v>-14.94097978618771</v>
+      </c>
+      <c r="D100">
+        <v>8.991820213812284</v>
+      </c>
+      <c r="E100">
+        <v>20.4428</v>
+      </c>
+      <c r="F100">
+        <v>27.3028</v>
+      </c>
+      <c r="G100">
+        <v>3.37</v>
+      </c>
+      <c r="H100">
+        <v>21</v>
+      </c>
+      <c r="I100">
+        <v>0</v>
+      </c>
+      <c r="J100">
+        <v>3.716666666666667</v>
+      </c>
+      <c r="K100">
+        <v>0.8799999999999999</v>
+      </c>
+      <c r="L100">
+        <v>2.836666666666667</v>
+      </c>
+      <c r="M100">
+        <v>6.51990864</v>
+      </c>
+      <c r="N100">
+        <v>-3.683241973333333</v>
+      </c>
+      <c r="O100">
+        <v>-0.7366483946666667</v>
+      </c>
+      <c r="P100">
+        <v>-2.946593578666666</v>
+      </c>
+      <c r="Q100">
+        <v>-2.066593578666666</v>
+      </c>
+      <c r="R100">
+        <v>48.99999999999996</v>
+      </c>
+      <c r="S100">
+        <v>4.320564869839628</v>
+      </c>
+      <c r="T100">
+        <v>47.57283259318975</v>
+      </c>
+      <c r="U100">
+        <v>0.2388</v>
+      </c>
+      <c r="V100">
+        <v>0.08701553421357963</v>
+      </c>
+      <c r="W100">
+        <v>0.2180206904297972</v>
+      </c>
+      <c r="X100" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y100">
+        <v>0.4350776710678981</v>
+      </c>
+      <c r="Z100">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101">
+        <v>0.99</v>
+      </c>
+      <c r="B101">
+        <v>0.3020715740179939</v>
+      </c>
+      <c r="C101">
+        <v>-15.28788811189551</v>
+      </c>
+      <c r="D101">
+        <v>8.923511888104493</v>
+      </c>
+      <c r="E101">
+        <v>20.7214</v>
+      </c>
+      <c r="F101">
+        <v>27.5814</v>
+      </c>
+      <c r="G101">
+        <v>3.37</v>
+      </c>
+      <c r="H101">
+        <v>21</v>
+      </c>
+      <c r="I101">
+        <v>0</v>
+      </c>
+      <c r="J101">
+        <v>3.716666666666667</v>
+      </c>
+      <c r="K101">
+        <v>0.8799999999999999</v>
+      </c>
+      <c r="L101">
+        <v>2.836666666666667</v>
+      </c>
+      <c r="M101">
+        <v>6.58643832</v>
+      </c>
+      <c r="N101">
+        <v>-3.749771653333333</v>
+      </c>
+      <c r="O101">
+        <v>-0.7499543306666667</v>
+      </c>
+      <c r="P101">
+        <v>-2.999817322666666</v>
+      </c>
+      <c r="Q101">
+        <v>-2.119817322666667</v>
+      </c>
+      <c r="R101">
+        <v>98.99999999999991</v>
+      </c>
+      <c r="S101">
+        <v>8.602329739679256</v>
+      </c>
+      <c r="T101">
+        <v>95.1456651863795</v>
+      </c>
+      <c r="U101">
+        <v>0.2388</v>
+      </c>
+      <c r="V101">
+        <v>0.08613658942354346</v>
+      </c>
+      <c r="W101">
+        <v>0.2182305824456578</v>
+      </c>
+      <c r="X101" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y101">
+        <v>0.4306829471177173</v>
+      </c>
+      <c r="Z101">
+        <v>0</v>
       </c>
     </row>
   </sheetData>
